--- a/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
+++ b/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="82">
+  <fonts count="83">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -571,6 +571,12 @@
       <name val="Arial"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="42">
     <fill>
@@ -947,7 +953,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="56" fillId="28" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1305,6 +1311,12 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="82" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -28887,7 +28899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="3" customWidth="1" style="104" min="1" max="1"/>
@@ -29310,7 +29322,32 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="4.2" customHeight="1" s="104"/>
+    <row r="36" ht="4.2" customHeight="1" s="104">
+      <c r="B36" s="125">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"CAB",'ASF Tracker'!E4:E1002,"Closed")/C35,0)</f>
+        <v/>
+      </c>
+      <c r="C36" s="126">
+        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"CAB",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(C35,"0")</f>
+        <v/>
+      </c>
+      <c r="E36" s="125">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"SEAT",'ASF Tracker'!E4:E1002,"Closed")/F35,0)</f>
+        <v/>
+      </c>
+      <c r="F36" s="126">
+        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"SEAT",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(F35,"0")</f>
+        <v/>
+      </c>
+      <c r="H36" s="125">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AV",'ASF Tracker'!E4:E1002,"Closed")/I35,0)</f>
+        <v/>
+      </c>
+      <c r="I36" s="126">
+        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AV",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(I35,"0")</f>
+        <v/>
+      </c>
+    </row>
     <row r="37" ht="32.1" customHeight="1" s="104">
       <c r="B37" s="43" t="inlineStr">
         <is>
@@ -29340,7 +29377,32 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="4.2" customHeight="1" s="104"/>
+    <row r="38" ht="4.2" customHeight="1" s="104">
+      <c r="B38" s="125">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/W",'ASF Tracker'!E4:E1002,"Closed")/C37,0)</f>
+        <v/>
+      </c>
+      <c r="C38" s="126">
+        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/W",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(C37,"0")</f>
+        <v/>
+      </c>
+      <c r="E38" s="125">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/M",'ASF Tracker'!E4:E1002,"Closed")/F37,0)</f>
+        <v/>
+      </c>
+      <c r="F38" s="126">
+        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/M",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(F37,"0")</f>
+        <v/>
+      </c>
+      <c r="H38" s="125">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"PAINT",'ASF Tracker'!E4:E1002,"Closed")/I37,0)</f>
+        <v/>
+      </c>
+      <c r="I38" s="126">
+        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"PAINT",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(I37,"0")</f>
+        <v/>
+      </c>
+    </row>
     <row r="39" ht="32.1" customHeight="1" s="104">
       <c r="B39" s="55" t="inlineStr">
         <is>
@@ -29370,7 +29432,32 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="4.2" customHeight="1" s="104"/>
+    <row r="40" ht="4.2" customHeight="1" s="104">
+      <c r="B40" s="125">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"JOINT",'ASF Tracker'!E4:E1002,"Closed")/C39,0)</f>
+        <v/>
+      </c>
+      <c r="C40" s="126">
+        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"JOINT",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(C39,"0")</f>
+        <v/>
+      </c>
+      <c r="E40" s="125">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"INSP",'ASF Tracker'!E4:E1002,"Closed")/F39,0)</f>
+        <v/>
+      </c>
+      <c r="F40" s="126">
+        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"INSP",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(F39,"0")</f>
+        <v/>
+      </c>
+      <c r="H40" s="125">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AP",'ASF Tracker'!E4:E1002,"Closed")/I39,0)</f>
+        <v/>
+      </c>
+      <c r="I40" s="126">
+        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AP",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(I39,"0")</f>
+        <v/>
+      </c>
+    </row>
     <row r="41" ht="32.1" customHeight="1" s="104"/>
   </sheetData>
   <mergeCells count="18">

--- a/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
+++ b/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
@@ -574,11 +574,11 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00555555"/>
+      <color rgb="00666666"/>
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="43">
     <fill>
       <patternFill/>
     </fill>
@@ -795,6 +795,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -953,7 +958,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="56" fillId="28" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1313,10 +1318,7 @@
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="82" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="82" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -29322,29 +29324,17 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="4.2" customHeight="1" s="104">
-      <c r="B36" s="125">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"CAB",'ASF Tracker'!E4:E1002,"Closed")/C35,0)</f>
+    <row r="36" ht="14" customHeight="1" s="104">
+      <c r="C36" s="125">
+        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"CAB",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"CAB"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"CAB",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"CAB"),0),"0%")&amp;")","-")</f>
         <v/>
       </c>
-      <c r="C36" s="126">
-        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"CAB",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(C35,"0")</f>
+      <c r="F36" s="125">
+        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"SEAT",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"SEAT"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"SEAT",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"SEAT"),0),"0%")&amp;")","-")</f>
         <v/>
       </c>
-      <c r="E36" s="125">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"SEAT",'ASF Tracker'!E4:E1002,"Closed")/F35,0)</f>
-        <v/>
-      </c>
-      <c r="F36" s="126">
-        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"SEAT",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(F35,"0")</f>
-        <v/>
-      </c>
-      <c r="H36" s="125">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AV",'ASF Tracker'!E4:E1002,"Closed")/I35,0)</f>
-        <v/>
-      </c>
-      <c r="I36" s="126">
-        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AV",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(I35,"0")</f>
+      <c r="I36" s="125">
+        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AV",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AV"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AV",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AV"),0),"0%")&amp;")","-")</f>
         <v/>
       </c>
     </row>
@@ -29377,29 +29367,17 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="4.2" customHeight="1" s="104">
-      <c r="B38" s="125">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/W",'ASF Tracker'!E4:E1002,"Closed")/C37,0)</f>
+    <row r="38" ht="14" customHeight="1" s="104">
+      <c r="C38" s="125">
+        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/W",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/W"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/W",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/W"),0),"0%")&amp;")","-")</f>
         <v/>
       </c>
-      <c r="C38" s="126">
-        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/W",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(C37,"0")</f>
+      <c r="F38" s="125">
+        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/M",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/M"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/M",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/M"),0),"0%")&amp;")","-")</f>
         <v/>
       </c>
-      <c r="E38" s="125">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/M",'ASF Tracker'!E4:E1002,"Closed")/F37,0)</f>
-        <v/>
-      </c>
-      <c r="F38" s="126">
-        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/M",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(F37,"0")</f>
-        <v/>
-      </c>
-      <c r="H38" s="125">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"PAINT",'ASF Tracker'!E4:E1002,"Closed")/I37,0)</f>
-        <v/>
-      </c>
-      <c r="I38" s="126">
-        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"PAINT",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(I37,"0")</f>
+      <c r="I38" s="125">
+        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"PAINT",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"PAINT"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"PAINT",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"PAINT"),0),"0%")&amp;")","-")</f>
         <v/>
       </c>
     </row>
@@ -29432,29 +29410,17 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="4.2" customHeight="1" s="104">
-      <c r="B40" s="125">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"JOINT",'ASF Tracker'!E4:E1002,"Closed")/C39,0)</f>
+    <row r="40" ht="14" customHeight="1" s="104">
+      <c r="C40" s="125">
+        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"JOINT",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"JOINT"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"JOINT",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"JOINT"),0),"0%")&amp;")","-")</f>
         <v/>
       </c>
-      <c r="C40" s="126">
-        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"JOINT",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(C39,"0")</f>
+      <c r="F40" s="125">
+        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"INSP",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"INSP"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"INSP",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"INSP"),0),"0%")&amp;")","-")</f>
         <v/>
       </c>
-      <c r="E40" s="125">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"INSP",'ASF Tracker'!E4:E1002,"Closed")/F39,0)</f>
-        <v/>
-      </c>
-      <c r="F40" s="126">
-        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"INSP",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(F39,"0")</f>
-        <v/>
-      </c>
-      <c r="H40" s="125">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AP",'ASF Tracker'!E4:E1002,"Closed")/I39,0)</f>
-        <v/>
-      </c>
-      <c r="I40" s="126">
-        <f>TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AP",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(I39,"0")</f>
+      <c r="I40" s="125">
+        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AP",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AP"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AP",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AP"),0),"0%")&amp;")","-")</f>
         <v/>
       </c>
     </row>

--- a/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
+++ b/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="83">
+  <fonts count="84">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -577,6 +577,12 @@
       <color rgb="00666666"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF555555"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="43">
     <fill>
@@ -958,7 +964,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="56" fillId="28" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1319,6 +1325,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="82" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -29324,17 +29336,29 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="14" customHeight="1" s="104">
-      <c r="C36" s="125">
-        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"CAB",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"CAB"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"CAB",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"CAB"),0),"0%")&amp;")","-")</f>
+    <row r="36" ht="14.4" customHeight="1" s="104">
+      <c r="B36" s="126">
+        <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"CAB",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"CAB"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="F36" s="125">
-        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"SEAT",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"SEAT"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"SEAT",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"SEAT"),0),"0%")&amp;")","-")</f>
+      <c r="C36" s="127">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"CAB",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"CAB"),"-")</f>
         <v/>
       </c>
-      <c r="I36" s="125">
-        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AV",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AV"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AV",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AV"),0),"0%")&amp;")","-")</f>
+      <c r="E36" s="126">
+        <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"SEAT"),"0%"),"-")</f>
+        <v/>
+      </c>
+      <c r="F36" s="127">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"SEAT"),"-")</f>
+        <v/>
+      </c>
+      <c r="H36" s="126">
+        <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AV",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AV"),"0%"),"-")</f>
+        <v/>
+      </c>
+      <c r="I36" s="127">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AV",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AV"),"-")</f>
         <v/>
       </c>
     </row>
@@ -29367,17 +29391,29 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="14" customHeight="1" s="104">
-      <c r="C38" s="125">
-        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/W",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/W"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/W",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/W"),0),"0%")&amp;")","-")</f>
+    <row r="38" ht="14.4" customHeight="1" s="104">
+      <c r="B38" s="126">
+        <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/W",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/W"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="F38" s="125">
-        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/M",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/M"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/M",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/M"),0),"0%")&amp;")","-")</f>
+      <c r="C38" s="127">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/W",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/W"),"-")</f>
         <v/>
       </c>
-      <c r="I38" s="125">
-        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"PAINT",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"PAINT"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"PAINT",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"PAINT"),0),"0%")&amp;")","-")</f>
+      <c r="E38" s="126">
+        <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/M",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/M"),"0%"),"-")</f>
+        <v/>
+      </c>
+      <c r="F38" s="127">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/M",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/M"),"-")</f>
+        <v/>
+      </c>
+      <c r="H38" s="126">
+        <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"PAINT",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"PAINT"),"0%"),"-")</f>
+        <v/>
+      </c>
+      <c r="I38" s="127">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"PAINT",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"PAINT"),"-")</f>
         <v/>
       </c>
     </row>
@@ -29410,17 +29446,29 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="14" customHeight="1" s="104">
-      <c r="C40" s="125">
-        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"JOINT",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"JOINT"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"JOINT",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"JOINT"),0),"0%")&amp;")","-")</f>
+    <row r="40" ht="14.4" customHeight="1" s="104">
+      <c r="B40" s="126">
+        <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"JOINT",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"JOINT"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="F40" s="125">
-        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"INSP",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"INSP"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"INSP",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"INSP"),0),"0%")&amp;")","-")</f>
+      <c r="C40" s="127">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"JOINT",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"JOINT"),"-")</f>
         <v/>
       </c>
-      <c r="I40" s="125">
-        <f>IFERROR(TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AP",'ASF Tracker'!E4:E1002,"Closed"),"0")&amp;" / "&amp;TEXT(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AP"),"0")&amp;"  ("&amp;TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AP",'ASF Tracker'!E4:E1002,"Closed")/COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AP"),0),"0%")&amp;")","-")</f>
+      <c r="E40" s="126">
+        <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"INSP",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"INSP"),"0%"),"-")</f>
+        <v/>
+      </c>
+      <c r="F40" s="127">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"INSP",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"INSP"),"-")</f>
+        <v/>
+      </c>
+      <c r="H40" s="126">
+        <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AP",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AP"),"0%"),"-")</f>
+        <v/>
+      </c>
+      <c r="I40" s="127">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AP",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AP"),"-")</f>
         <v/>
       </c>
     </row>

--- a/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
+++ b/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="84">
+  <fonts count="91">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -578,13 +578,53 @@
       <sz val="8"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="FF555555"/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF1565C0"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF6A1B9A"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF37474F"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF2E7D32"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF4E342E"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFB71C1C"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFE65100"/>
+      <sz val="16"/>
+    </font>
   </fonts>
-  <fills count="43">
+  <fills count="50">
     <fill>
       <patternFill/>
     </fill>
@@ -806,6 +846,41 @@
         <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE8F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEADAF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0E6EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EED9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DCD9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD8DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD9AD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -964,7 +1039,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="56" fillId="28" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1327,10 +1402,52 @@
     <xf numFmtId="0" fontId="82" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="83" fillId="23" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="85" fillId="24" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="25" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="26" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="27" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="33" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="46" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="47" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="27" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="28" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="34" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -29313,8 +29430,8 @@
           <t>CAB</t>
         </is>
       </c>
-      <c r="C35" s="38">
-        <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"CAB")</f>
+      <c r="C35" s="126">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"CAB",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"CAB"),"-")</f>
         <v/>
       </c>
       <c r="E35" s="46" t="inlineStr">
@@ -29322,8 +29439,8 @@
           <t>SEAT</t>
         </is>
       </c>
-      <c r="F35" s="47">
-        <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"SEAT")</f>
+      <c r="F35" s="127">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"SEAT"),"-")</f>
         <v/>
       </c>
       <c r="H35" s="30" t="inlineStr">
@@ -29331,36 +29448,27 @@
           <t>AV</t>
         </is>
       </c>
-      <c r="I35" s="52">
-        <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AV")</f>
+      <c r="I35" s="128">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AV",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AV"),"-")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="14.4" customHeight="1" s="104">
-      <c r="B36" s="126">
+      <c r="B36" s="129">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"CAB",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"CAB"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="C36" s="127">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"CAB",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"CAB"),"-")</f>
-        <v/>
-      </c>
-      <c r="E36" s="126">
+      <c r="C36" s="125" t="n"/>
+      <c r="E36" s="130">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"SEAT"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="F36" s="127">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"SEAT"),"-")</f>
-        <v/>
-      </c>
-      <c r="H36" s="126">
+      <c r="F36" s="125" t="n"/>
+      <c r="H36" s="131">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AV",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AV"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="I36" s="127">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AV",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AV"),"-")</f>
-        <v/>
-      </c>
+      <c r="I36" s="125" t="n"/>
     </row>
     <row r="37" ht="32.1" customHeight="1" s="104">
       <c r="B37" s="43" t="inlineStr">
@@ -29368,8 +29476,8 @@
           <t>S/W</t>
         </is>
       </c>
-      <c r="C37" s="44">
-        <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/W")</f>
+      <c r="C37" s="132">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/W",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/W"),"-")</f>
         <v/>
       </c>
       <c r="E37" s="53" t="inlineStr">
@@ -29377,8 +29485,8 @@
           <t>S/M</t>
         </is>
       </c>
-      <c r="F37" s="54">
-        <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"S/M")</f>
+      <c r="F37" s="133">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/M",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/M"),"-")</f>
         <v/>
       </c>
       <c r="H37" s="61" t="inlineStr">
@@ -29386,36 +29494,27 @@
           <t>PAINT</t>
         </is>
       </c>
-      <c r="I37" s="62">
-        <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"PAINT")</f>
+      <c r="I37" s="134">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"PAINT",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"PAINT"),"-")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="14.4" customHeight="1" s="104">
-      <c r="B38" s="126">
+      <c r="B38" s="135">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/W",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/W"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="C38" s="127">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/W",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/W"),"-")</f>
-        <v/>
-      </c>
-      <c r="E38" s="126">
+      <c r="C38" s="125" t="n"/>
+      <c r="E38" s="136">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/M",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/M"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="F38" s="127">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/M",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/M"),"-")</f>
-        <v/>
-      </c>
-      <c r="H38" s="126">
+      <c r="F38" s="125" t="n"/>
+      <c r="H38" s="137">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"PAINT",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"PAINT"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="I38" s="127">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"PAINT",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"PAINT"),"-")</f>
-        <v/>
-      </c>
+      <c r="I38" s="125" t="n"/>
     </row>
     <row r="39" ht="32.1" customHeight="1" s="104">
       <c r="B39" s="55" t="inlineStr">
@@ -29423,8 +29522,8 @@
           <t>JOINT</t>
         </is>
       </c>
-      <c r="C39" s="56">
-        <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"JOINT")</f>
+      <c r="C39" s="138">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"JOINT",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"JOINT"),"-")</f>
         <v/>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -29432,8 +29531,8 @@
           <t>INSP</t>
         </is>
       </c>
-      <c r="F39" s="3">
-        <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"INSP")</f>
+      <c r="F39" s="139">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"INSP",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"INSP"),"-")</f>
         <v/>
       </c>
       <c r="H39" s="63" t="inlineStr">
@@ -29441,36 +29540,27 @@
           <t>AP</t>
         </is>
       </c>
-      <c r="I39" s="64">
-        <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!G4:G1002,"AP")</f>
+      <c r="I39" s="140">
+        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AP",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AP"),"-")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="14.4" customHeight="1" s="104">
-      <c r="B40" s="126">
+      <c r="B40" s="141">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"JOINT",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"JOINT"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="C40" s="127">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"JOINT",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"JOINT"),"-")</f>
-        <v/>
-      </c>
-      <c r="E40" s="126">
+      <c r="C40" s="125" t="n"/>
+      <c r="E40" s="129">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"INSP",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"INSP"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="F40" s="127">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"INSP",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"INSP"),"-")</f>
-        <v/>
-      </c>
-      <c r="H40" s="126">
+      <c r="F40" s="125" t="n"/>
+      <c r="H40" s="131">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AP",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AP"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="I40" s="127">
-        <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AP",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AP"),"-")</f>
-        <v/>
-      </c>
+      <c r="I40" s="125" t="n"/>
     </row>
     <row r="41" ht="32.1" customHeight="1" s="104"/>
   </sheetData>

--- a/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
+++ b/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="84">
+  <fonts count="85">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -578,8 +578,14 @@
       <color rgb="FFE65100"/>
       <sz val="16"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="42">
+  <fills count="43">
     <fill>
       <patternFill/>
     </fill>
@@ -796,6 +802,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B5E20"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -954,7 +965,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="54" fillId="28" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1338,12 +1349,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
     <cellStyle name="ارتباط تشعبي" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="101">
+  <dxfs count="104">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2667,6 +2681,39 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB71C1C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE65100"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF1B5E20"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -29074,7 +29121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="129" min="1" max="1"/>
@@ -29089,7 +29136,7 @@
     <col width="3" customWidth="1" style="129" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="129">
+    <row r="1" ht="28" customHeight="1" s="129">
       <c r="A1" s="121" t="inlineStr">
         <is>
           <t>📊  ASF C3-CHECK — WORK PACKAGE DASHBOARD</t>
@@ -29097,6 +29144,10 @@
       </c>
       <c r="I1" s="116">
         <f>"Day "&amp;TEXT(MAX(1,MIN(TODAY()-DATE(2026,6,8)+1,36)),"0")&amp;"/36"</f>
+        <v/>
+      </c>
+      <c r="K1" s="133">
+        <f>LET(days_left, MAX(0, 36 - MAX(1, MIN(TODAY()-DATE(2026,6,8)+1,36))),open_count, COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!E4:E1002,"Open"),IF(TODAY()&gt;DATE(2026,7,14),"❌  C-CHECK ENDED — "&amp;open_count&amp;" Open remaining",IF(days_left&lt;5,"🔴  CRITICAL — "&amp;days_left&amp;" days left, "&amp;open_count&amp;" Open",IF(days_left&lt;10,"⚠️  WARNING — "&amp;days_left&amp;" days left, "&amp;open_count&amp;" Open","✅  ON TRACK — "&amp;days_left&amp;" days left, "&amp;open_count&amp;" Open"))))</f>
         <v/>
       </c>
     </row>
@@ -29618,7 +29669,7 @@
     </row>
     <row r="43" ht="32.1" customHeight="1" s="129"/>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E42:F42"/>
     <mergeCell ref="B22:C22"/>
@@ -29630,6 +29681,7 @@
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="H39:I39"/>
     <mergeCell ref="H25:I25"/>
+    <mergeCell ref="K1:O1"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="E28:F28"/>
@@ -29647,6 +29699,17 @@
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A33:J33"/>
   </mergeCells>
+  <conditionalFormatting sqref="K1:O1">
+    <cfRule type="expression" priority="1" dxfId="101">
+      <formula>OR(ISNUMBER(SEARCH("CRITICAL",K1)),ISNUMBER(SEARCH("ENDED",K1)))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="102">
+      <formula>ISNUMBER(SEARCH("WARNING",K1))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="103">
+      <formula>ISNUMBER(SEARCH("ON TRACK",K1))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>

--- a/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
+++ b/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="85">
+  <fonts count="86">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -584,6 +584,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="43">
     <fill>
@@ -965,7 +971,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="54" fillId="28" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1352,12 +1358,15 @@
     <xf numFmtId="0" fontId="84" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="85" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
     <cellStyle name="ارتباط تشعبي" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="104">
+  <dxfs count="108">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2714,6 +2723,58 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB71C1C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF880000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE65100"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF1B5E20"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -29121,7 +29182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="129" min="1" max="1"/>
@@ -29146,528 +29207,530 @@
         <f>"Day "&amp;TEXT(MAX(1,MIN(TODAY()-DATE(2026,6,8)+1,36)),"0")&amp;"/36"</f>
         <v/>
       </c>
-      <c r="K1" s="133">
-        <f>LET(days_left, MAX(0, 36 - MAX(1, MIN(TODAY()-DATE(2026,6,8)+1,36))),open_count, COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!E4:E1002,"Open"),IF(TODAY()&gt;DATE(2026,7,14),"❌  C-CHECK ENDED — "&amp;open_count&amp;" Open remaining",IF(days_left&lt;5,"🔴  CRITICAL — "&amp;days_left&amp;" days left, "&amp;open_count&amp;" Open",IF(days_left&lt;10,"⚠️  WARNING — "&amp;days_left&amp;" days left, "&amp;open_count&amp;" Open","✅  ON TRACK — "&amp;days_left&amp;" days left, "&amp;open_count&amp;" Open"))))</f>
+      <c r="K1" s="133" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1" s="129">
+      <c r="A2" s="134">
+        <f>IF(TODAY()&gt;DATE(2026,7,14),"❌  C-CHECK ENDED  —  "&amp;COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!E4:E1002,"Open")&amp;" Open remaining",IF(MAX(0,36-MAX(1,MIN(TODAY()-DATE(2026,6,8)+1,36)))&lt;5,"🔴  CRITICAL  —  "&amp;MAX(0,36-MAX(1,MIN(TODAY()-DATE(2026,6,8)+1,36)))&amp;" days left  |  "&amp;COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!E4:E1002,"Open")&amp;" Open",IF(MAX(0,36-MAX(1,MIN(TODAY()-DATE(2026,6,8)+1,36)))&lt;10,"⚠️  WARNING  —  "&amp;MAX(0,36-MAX(1,MIN(TODAY()-DATE(2026,6,8)+1,36)))&amp;" days left  |  "&amp;COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!E4:E1002,"Open")&amp;" Open","✅  ON TRACK  —  "&amp;MAX(0,36-MAX(1,MIN(TODAY()-DATE(2026,6,8)+1,36)))&amp;" days left  |  "&amp;COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!E4:E1002,"Open")&amp;" Open")))</f>
         <v/>
       </c>
     </row>
-    <row r="2" ht="13.9" customHeight="1" s="129">
-      <c r="A2" s="111" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="129">
+      <c r="A3" s="111" t="inlineStr">
         <is>
           <t>All figures update automatically from ASF Tracker</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="129">
-      <c r="A3" s="109" t="inlineStr">
+    <row r="4" ht="4.15" customHeight="1" s="129">
+      <c r="A4" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">  STATUS OVERVIEW</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="4.15" customHeight="1" s="129"/>
-    <row r="5" ht="31.9" customHeight="1" s="129">
-      <c r="B5" s="64" t="inlineStr">
+    <row r="5" ht="31.9" customHeight="1" s="129"/>
+    <row r="6" ht="4.15" customHeight="1" s="129">
+      <c r="B6" s="64" t="inlineStr">
         <is>
           <t>Total Items/WOs</t>
         </is>
       </c>
-      <c r="C5" s="12">
+      <c r="C6" s="12">
         <f>COUNTIF('ASF Tracker'!B4:B1002,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F5" s="14">
+      <c r="F6" s="14">
         <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!E4:E1002,"Closed")</f>
         <v/>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>Completion</t>
         </is>
       </c>
-      <c r="I5" s="16">
+      <c r="I6" s="16">
         <f>TEXT(IFERROR(COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!E4:E1002,"Closed")/COUNTIF('ASF Tracker'!B4:B1002,"&lt;&gt;"),0),"0%")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="4.15" customHeight="1" s="129"/>
-    <row r="7" ht="31.9" customHeight="1" s="129">
-      <c r="B7" s="65" t="inlineStr">
+    <row r="7" ht="31.9" customHeight="1" s="129"/>
+    <row r="8" ht="4.15" customHeight="1" s="129">
+      <c r="B8" s="65" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="C7" s="17">
+      <c r="C8" s="17">
         <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!E4:E1002,"Open")</f>
         <v/>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F7" s="19">
+      <c r="F8" s="19">
         <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!E4:E1002,"In Progress")</f>
         <v/>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>Deferred / Hold</t>
         </is>
       </c>
-      <c r="I7" s="21">
+      <c r="I8" s="21">
         <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!E4:E1002,"Deferred")+COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!E4:E1002,"On Hold")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="4.15" customHeight="1" s="129"/>
-    <row r="9" ht="18" customHeight="1" s="129">
-      <c r="A9" s="124" t="inlineStr">
+    <row r="9" ht="18" customHeight="1" s="129"/>
+    <row r="10" ht="4.15" customHeight="1" s="129">
+      <c r="A10" s="124" t="inlineStr">
         <is>
           <t xml:space="preserve">  PRIORITY ALERTS</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="4.15" customHeight="1" s="129"/>
-    <row r="11" ht="31.9" customHeight="1" s="129">
-      <c r="B11" s="66" t="inlineStr">
+    <row r="11" ht="31.9" customHeight="1" s="129"/>
+    <row r="12" ht="4.15" customHeight="1" s="129">
+      <c r="B12" s="66" t="inlineStr">
         <is>
           <t>AOG</t>
         </is>
       </c>
-      <c r="C11" s="22">
+      <c r="C12" s="22">
         <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!F4:F1002,"AOG")</f>
         <v/>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F11" s="19">
+      <c r="F12" s="19">
         <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!F4:F1002,"Critical")</f>
         <v/>
       </c>
-      <c r="H11" s="23" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I11" s="24">
+      <c r="I12" s="24">
         <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!F4:F1002,"High")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="4.15" customHeight="1" s="129"/>
-    <row r="13" ht="18" customHeight="1" s="129">
-      <c r="A13" s="109" t="inlineStr">
+    <row r="13" ht="18" customHeight="1" s="129"/>
+    <row r="14" ht="4.15" customHeight="1" s="129">
+      <c r="A14" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">  PARTS REQUIREMENTS  (count of WOs with each status)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="4.15" customHeight="1" s="129"/>
-    <row r="15" ht="31.9" customHeight="1" s="129">
-      <c r="B15" s="25" t="inlineStr">
+    <row r="15" ht="31.9" customHeight="1" s="129"/>
+    <row r="16" ht="4.15" customHeight="1" s="129">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Requested</t>
         </is>
       </c>
-      <c r="C15" s="26">
+      <c r="C16" s="26">
         <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!H4:H1002,"Requested")</f>
         <v/>
       </c>
-      <c r="E15" s="27" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>Requested – CR</t>
         </is>
       </c>
-      <c r="F15" s="28">
+      <c r="F16" s="28">
         <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!H4:H1002,"Requested - CR")</f>
         <v/>
       </c>
-      <c r="H15" s="29" t="inlineStr">
+      <c r="H16" s="29" t="inlineStr">
         <is>
           <t>Requested – R</t>
         </is>
       </c>
-      <c r="I15" s="30">
+      <c r="I16" s="30">
         <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!H4:H1002,"Requested - R")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="4.15" customHeight="1" s="129"/>
-    <row r="17" ht="31.9" customHeight="1" s="129">
-      <c r="B17" s="69" t="inlineStr">
+    <row r="17" ht="31.9" customHeight="1" s="129"/>
+    <row r="18" ht="4.15" customHeight="1" s="129">
+      <c r="B18" s="69" t="inlineStr">
         <is>
           <t>Pending - Require Evaluation</t>
         </is>
       </c>
-      <c r="C17" s="31">
+      <c r="C18" s="31">
         <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!H4:H1002,"Pending EVAL")</f>
         <v/>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>N/R  (not required)</t>
         </is>
       </c>
-      <c r="F17" s="14">
+      <c r="F18" s="14">
         <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!H4:H1002,"N/R")</f>
         <v/>
       </c>
-      <c r="H17" s="32" t="inlineStr">
+      <c r="H18" s="32" t="inlineStr">
         <is>
           <t>N/A (Not available)</t>
         </is>
       </c>
-      <c r="I17" s="33">
+      <c r="I18" s="33">
         <f>COUNTIFS('ASF Tracker'!B4:B1002,"&lt;&gt;",'ASF Tracker'!H4:H1002,"N/A")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="4.15" customHeight="1" s="129"/>
-    <row r="19" ht="18" customHeight="1" s="129">
-      <c r="A19" s="109" t="inlineStr">
+    <row r="19" ht="18" customHeight="1" s="129"/>
+    <row r="20" ht="4.15" customHeight="1" s="129">
+      <c r="A20" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">  BY CATEGORY</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="4.15" customHeight="1" s="129"/>
-    <row r="21" ht="31.9" customHeight="1" s="129">
-      <c r="B21" s="34" t="inlineStr">
+    <row r="21" ht="31.9" customHeight="1" s="129"/>
+    <row r="22" ht="14.45" customHeight="1" s="129">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>TASK CARD</t>
         </is>
       </c>
-      <c r="C21" s="35">
+      <c r="C22" s="35">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TASK CARD",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TASK CARD"),"-")</f>
         <v/>
       </c>
-      <c r="E21" s="36" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>LAVATORY</t>
         </is>
       </c>
-      <c r="F21" s="37">
+      <c r="F22" s="37">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"LAVATORY",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"LAVATORY"),"-")</f>
         <v/>
       </c>
-      <c r="H21" s="38" t="inlineStr">
+      <c r="H22" s="38" t="inlineStr">
         <is>
           <t>GALLEY</t>
         </is>
       </c>
-      <c r="I21" s="39">
+      <c r="I22" s="39">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"GALLEY",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"GALLEY"),"-")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="14.45" customHeight="1" s="129">
-      <c r="B22" s="119">
+    <row r="23" ht="4.15" customHeight="1" s="129">
+      <c r="B23" s="119">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TASK CARD",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TASK CARD"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="C22" s="132" t="n"/>
-      <c r="E22" s="110">
+      <c r="C23" s="132" t="n"/>
+      <c r="E23" s="110">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"LAVATORY",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"LAVATORY"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="F22" s="132" t="n"/>
-      <c r="H22" s="113">
+      <c r="F23" s="132" t="n"/>
+      <c r="H23" s="113">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"GALLEY",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"GALLEY"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="I22" s="132" t="n"/>
-    </row>
-    <row r="23" ht="4.15" customHeight="1" s="129">
-      <c r="B23" s="54" t="n"/>
-      <c r="E23" s="54" t="n"/>
-      <c r="H23" s="54" t="n"/>
+      <c r="I23" s="132" t="n"/>
     </row>
     <row r="24" ht="31.9" customHeight="1" s="129">
-      <c r="B24" s="40" t="inlineStr">
+      <c r="B24" s="54" t="n"/>
+      <c r="E24" s="54" t="n"/>
+      <c r="H24" s="54" t="n"/>
+    </row>
+    <row r="25" ht="14.45" customHeight="1" s="129">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>GENERAL CABIN</t>
         </is>
       </c>
-      <c r="C24" s="41">
+      <c r="C25" s="41">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$D$4:$D$1002,"GENERAL CABIN",'ASF Tracker'!$E$4:$E$1002,"Closed",'ASF Tracker'!$B$4:$B$1002,"&lt;&gt;")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$D$4:$D$1002,"GENERAL CABIN",'ASF Tracker'!$B$4:$B$1002,"&lt;&gt;"),"-")</f>
         <v/>
       </c>
-      <c r="E24" s="42" t="inlineStr">
+      <c r="E25" s="42" t="inlineStr">
         <is>
           <t>TEDLAR/SIDEWALL</t>
         </is>
       </c>
-      <c r="F24" s="43">
+      <c r="F25" s="43">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TEDLAR/SIDEWALL",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TEDLAR/SIDEWALL"),"-")</f>
         <v/>
       </c>
-      <c r="H24" s="67" t="inlineStr">
+      <c r="H25" s="67" t="inlineStr">
         <is>
           <t>PAX SEAT</t>
         </is>
       </c>
-      <c r="I24" s="44">
+      <c r="I25" s="44">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX SEAT"),"-")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="14.45" customHeight="1" s="129">
-      <c r="B25" s="115">
+    <row r="26" ht="4.15" customHeight="1" s="129">
+      <c r="B26" s="115">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$D$4:$D$1002,"GENERAL CABIN",'ASF Tracker'!$E$4:$E$1002,"Closed",'ASF Tracker'!$B$4:$B$1002,"&lt;&gt;")/COUNTIFS('ASF Tracker'!$D$4:$D$1002,"GENERAL CABIN",'ASF Tracker'!$B$4:$B$1002,"&lt;&gt;"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="C25" s="132" t="n"/>
-      <c r="E25" s="117">
+      <c r="C26" s="132" t="n"/>
+      <c r="E26" s="117">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TEDLAR/SIDEWALL",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TEDLAR/SIDEWALL"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="F25" s="132" t="n"/>
-      <c r="H25" s="120">
+      <c r="F26" s="132" t="n"/>
+      <c r="H26" s="120">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX SEAT"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="I25" s="132" t="n"/>
-    </row>
-    <row r="26" ht="4.15" customHeight="1" s="129">
-      <c r="B26" s="54" t="n"/>
-      <c r="E26" s="54" t="n"/>
-      <c r="H26" s="54" t="n"/>
+      <c r="I26" s="132" t="n"/>
     </row>
     <row r="27" ht="31.9" customHeight="1" s="129">
-      <c r="B27" s="45" t="inlineStr">
+      <c r="B27" s="54" t="n"/>
+      <c r="E27" s="54" t="n"/>
+      <c r="H27" s="54" t="n"/>
+    </row>
+    <row r="28" ht="14.45" customHeight="1" s="129">
+      <c r="B28" s="45" t="inlineStr">
         <is>
           <t>PAX DOORS</t>
         </is>
       </c>
-      <c r="C27" s="46">
+      <c r="C28" s="46">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX DOORS",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX DOORS"),"-")</f>
         <v/>
       </c>
-      <c r="E27" s="47" t="inlineStr">
+      <c r="E28" s="47" t="inlineStr">
         <is>
           <t>F/A SEAT</t>
         </is>
       </c>
-      <c r="F27" s="48">
+      <c r="F28" s="48">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"F/A SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"F/A SEAT"),"-")</f>
         <v/>
       </c>
-      <c r="H27" s="55" t="inlineStr">
+      <c r="H28" s="55" t="inlineStr">
         <is>
           <t>OTHERS</t>
         </is>
       </c>
-      <c r="I27" s="56">
+      <c r="I28" s="56">
         <f>IFERROR((COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$E$4:$E$1002,"Closed")-(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TASK CARD",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"LAVATORY",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"GALLEY",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"GENERAL CABIN",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TEDLAR/SIDEWALL",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX DOORS",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"F/A SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"OFAR/OFCR",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"FLIGHT DECK",'ASF Tracker'!$E$4:$E$1002,"Closed")))&amp;" / "&amp;(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;")-(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TASK CARD")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"LAVATORY")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"GALLEY")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"GENERAL CABIN")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TEDLAR/SIDEWALL")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX SEAT")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX DOORS")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"F/A SEAT")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"OFAR/OFCR")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"FLIGHT DECK"))),"-")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="14.45" customHeight="1" s="129">
-      <c r="B28" s="112">
+    <row r="29" ht="4.15" customHeight="1" s="129">
+      <c r="B29" s="112">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX DOORS",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX DOORS"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="C28" s="132" t="n"/>
-      <c r="E28" s="125">
+      <c r="C29" s="132" t="n"/>
+      <c r="E29" s="125">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"F/A SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"F/A SEAT"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="F28" s="132" t="n"/>
-      <c r="H28" s="114">
+      <c r="F29" s="132" t="n"/>
+      <c r="H29" s="114">
         <f>IFERROR("Completion: "&amp;TEXT(((COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$E$4:$E$1002,"Closed")-(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TASK CARD",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"LAVATORY",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"GALLEY",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"GENERAL CABIN",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TEDLAR/SIDEWALL",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX DOORS",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"F/A SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"OFAR/OFCR",'ASF Tracker'!$E$4:$E$1002,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"FLIGHT DECK",'ASF Tracker'!$E$4:$E$1002,"Closed"))))/((COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;")-(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TASK CARD")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"LAVATORY")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"GALLEY")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"GENERAL CABIN")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"TEDLAR/SIDEWALL")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX SEAT")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"PAX DOORS")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"F/A SEAT")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"OFAR/OFCR")+COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"FLIGHT DECK")))),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="I28" s="132" t="n"/>
-    </row>
-    <row r="29" ht="4.15" customHeight="1" s="129">
-      <c r="B29" s="54" t="n"/>
-      <c r="E29" s="54" t="n"/>
+      <c r="I29" s="132" t="n"/>
     </row>
     <row r="30" ht="31.9" customHeight="1" s="129">
-      <c r="B30" s="49" t="inlineStr">
+      <c r="B30" s="54" t="n"/>
+      <c r="E30" s="54" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="49" t="inlineStr">
         <is>
           <t>FLIGHT DECK</t>
         </is>
       </c>
-      <c r="C30" s="50">
+      <c r="C31" s="50">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"FLIGHT DECK",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"FLIGHT DECK"),"-")</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="120">
+    <row r="32" ht="4.15" customHeight="1" s="129">
+      <c r="B32" s="120">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"FLIGHT DECK",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1002,"FLIGHT DECK"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="C31" s="132" t="n"/>
-    </row>
-    <row r="32" ht="4.15" customHeight="1" s="129"/>
-    <row r="33" ht="18" customHeight="1" s="129">
-      <c r="A33" s="109" t="inlineStr">
+      <c r="C32" s="132" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="129"/>
+    <row r="34" ht="4.15" customHeight="1" s="129">
+      <c r="A34" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">  SPECIALTY</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="4.15" customHeight="1" s="129"/>
-    <row r="35" ht="32.1" customHeight="1" s="129">
-      <c r="B35" s="36" t="inlineStr">
+    <row r="35" ht="32.1" customHeight="1" s="129"/>
+    <row r="36" ht="14.45" customHeight="1" s="129">
+      <c r="B36" s="36" t="inlineStr">
         <is>
           <t>CABIN</t>
         </is>
       </c>
-      <c r="C35" s="92">
+      <c r="C36" s="92">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"CAB",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"CAB"),"-")</f>
         <v/>
       </c>
-      <c r="E35" s="45" t="inlineStr">
+      <c r="E36" s="45" t="inlineStr">
         <is>
           <t>SEAT SHOP</t>
         </is>
       </c>
-      <c r="F35" s="93">
+      <c r="F36" s="93">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"SEAT"),"-")</f>
         <v/>
       </c>
-      <c r="H35" s="29" t="inlineStr">
+      <c r="H36" s="29" t="inlineStr">
         <is>
           <t>AV/FOMAX</t>
         </is>
       </c>
-      <c r="I35" s="94">
+      <c r="I36" s="94">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AV",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AV"),"-")</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="14.45" customHeight="1" s="129">
-      <c r="B36" s="110">
+    <row r="37" ht="3.75" customHeight="1" s="129">
+      <c r="B37" s="110">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"CAB",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"CAB"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="C36" s="132" t="n"/>
-      <c r="E36" s="112">
+      <c r="C37" s="132" t="n"/>
+      <c r="E37" s="112">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"SEAT",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"SEAT"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="F36" s="132" t="n"/>
-      <c r="H36" s="115">
+      <c r="F37" s="132" t="n"/>
+      <c r="H37" s="115">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AV",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AV"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="I36" s="132" t="n"/>
-    </row>
-    <row r="37" ht="3.75" customHeight="1" s="129">
-      <c r="B37" s="54" t="n"/>
-      <c r="E37" s="54" t="n"/>
-      <c r="H37" s="54" t="n"/>
+      <c r="I37" s="132" t="n"/>
     </row>
     <row r="38" ht="32.1" customHeight="1" s="129">
-      <c r="B38" s="42" t="inlineStr">
+      <c r="B38" s="54" t="n"/>
+      <c r="E38" s="54" t="n"/>
+      <c r="H38" s="54" t="n"/>
+    </row>
+    <row r="39" ht="14.45" customHeight="1" s="129">
+      <c r="B39" s="42" t="inlineStr">
         <is>
           <t>SIDEWALL</t>
         </is>
       </c>
-      <c r="C38" s="95">
+      <c r="C39" s="95">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/W",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/W"),"-")</f>
         <v/>
       </c>
-      <c r="E38" s="51" t="inlineStr">
+      <c r="E39" s="51" t="inlineStr">
         <is>
           <t>S/M</t>
         </is>
       </c>
-      <c r="F38" s="96">
+      <c r="F39" s="96">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/M",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/M"),"-")</f>
         <v/>
       </c>
-      <c r="H38" s="57" t="inlineStr">
+      <c r="H39" s="57" t="inlineStr">
         <is>
           <t>PAINT</t>
         </is>
       </c>
-      <c r="I38" s="97">
+      <c r="I39" s="97">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"PAINT",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"PAINT"),"-")</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="14.45" customHeight="1" s="129">
-      <c r="B39" s="117">
+    <row r="40" ht="3.75" customHeight="1" s="129">
+      <c r="B40" s="117">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/W",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/W"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="C39" s="132" t="n"/>
-      <c r="E39" s="122">
+      <c r="C40" s="132" t="n"/>
+      <c r="E40" s="122">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/M",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"S/M"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="F39" s="132" t="n"/>
-      <c r="H39" s="123">
+      <c r="F40" s="132" t="n"/>
+      <c r="H40" s="123">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"PAINT",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"PAINT"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="I39" s="132" t="n"/>
-    </row>
-    <row r="40" ht="3.75" customHeight="1" s="129">
-      <c r="B40" s="54" t="n"/>
-      <c r="E40" s="54" t="n"/>
-      <c r="H40" s="54" t="n"/>
+      <c r="I40" s="132" t="n"/>
     </row>
     <row r="41" ht="32.1" customHeight="1" s="129">
-      <c r="B41" s="52" t="inlineStr">
+      <c r="B41" s="54" t="n"/>
+      <c r="E41" s="54" t="n"/>
+      <c r="H41" s="54" t="n"/>
+    </row>
+    <row r="42" ht="14.45" customHeight="1" s="129">
+      <c r="B42" s="52" t="inlineStr">
         <is>
           <t>JOINT</t>
         </is>
       </c>
-      <c r="C41" s="98">
+      <c r="C42" s="98">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"JOINT",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"JOINT"),"-")</f>
         <v/>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>INSP</t>
         </is>
       </c>
-      <c r="F41" s="99">
+      <c r="F42" s="99">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"INSP",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"INSP"),"-")</f>
         <v/>
       </c>
-      <c r="H41" s="58" t="inlineStr">
+      <c r="H42" s="58" t="inlineStr">
         <is>
           <t>A/P</t>
         </is>
       </c>
-      <c r="I41" s="100">
+      <c r="I42" s="100">
         <f>IFERROR(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AP",'ASF Tracker'!$E$4:$E$1002,"Closed")&amp;" / "&amp;COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AP"),"-")</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="14.45" customHeight="1" s="129">
-      <c r="B42" s="122">
+    <row r="43" ht="32.1" customHeight="1" s="129">
+      <c r="B43" s="122">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"JOINT",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"JOINT"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="C42" s="132" t="n"/>
-      <c r="E42" s="118">
+      <c r="C43" s="132" t="n"/>
+      <c r="E43" s="118">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"INSP",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"INSP"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="F42" s="132" t="n"/>
-      <c r="H42" s="108">
+      <c r="F43" s="132" t="n"/>
+      <c r="H43" s="108">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AP",'ASF Tracker'!$E$4:$E$1002,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1002,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1002,"AP"),"0%"),"-")</f>
         <v/>
       </c>
-      <c r="I42" s="132" t="n"/>
-    </row>
-    <row r="43" ht="32.1" customHeight="1" s="129"/>
+      <c r="I43" s="132" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="28">
     <mergeCell ref="B25:C25"/>
@@ -29708,6 +29771,20 @@
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="103">
       <formula>ISNUMBER(SEARCH("ON TRACK",K1))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:J2">
+    <cfRule type="expression" priority="4" dxfId="104">
+      <formula>ISNUMBER(SEARCH("CRITICAL",A2))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="105">
+      <formula>ISNUMBER(SEARCH("ENDED",A2))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="106">
+      <formula>ISNUMBER(SEARCH("WARNING",A2))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="107">
+      <formula>ISNUMBER(SEARCH("ON TRACK",A2))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
+++ b/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="25095" windowHeight="12045" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17610" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASF Tracker" sheetId="1" state="visible" r:id="rId1"/>
@@ -1246,13 +1246,34 @@
     <xf numFmtId="0" fontId="71" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="34" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="23" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="24" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="22" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="32" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="25" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="64" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="26" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="28" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1270,9 +1291,6 @@
     <xf numFmtId="0" fontId="56" fillId="27" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="56" fillId="33" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1280,24 +1298,6 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="34" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="23" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="24" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="22" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="32" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2761,9 +2761,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrackerTable13" displayName="TrackerTable13" ref="A3:K1004" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A3:K1004">
     <filterColumn colId="4" hiddenButton="0" showButton="1">
-      <filters blank="1">
+      <filters>
         <filter val="In Progress"/>
         <filter val="Open"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="CAB"/>
+        <filter val="JOINT"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3027,7 +3033,7 @@
     <row r="2" ht="19.9" customHeight="1" s="125">
       <c r="A2" s="103" t="inlineStr">
         <is>
-          <t xml:space="preserve">UPDATED: 06 JULY -- DAY SHIFT </t>
+          <t xml:space="preserve">UPDATED: 07 JULY -- DAY SHIFT </t>
         </is>
       </c>
       <c r="B2" s="126" t="n"/>
@@ -3104,7 +3110,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="125">
+    <row r="4" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A4" s="68" t="n">
         <v>1</v>
       </c>
@@ -3149,7 +3155,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="125">
+    <row r="5" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A5" s="68" t="n">
         <v>2</v>
       </c>
@@ -3196,7 +3202,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" s="125">
+    <row r="6" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A6" s="68" t="n">
         <v>3</v>
       </c>
@@ -3264,7 +3270,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -3421,7 +3427,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -3439,7 +3445,11 @@
           <t>Requested</t>
         </is>
       </c>
-      <c r="I10" s="9" t="n"/>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>C/W</t>
+        </is>
+      </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -3655,7 +3665,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" s="125">
+    <row r="15" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A15" s="68" t="n">
         <v>32</v>
       </c>
@@ -4649,7 +4659,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1" s="125">
+    <row r="37" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A37" s="68" t="n">
         <v>139</v>
       </c>
@@ -4670,7 +4680,7 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
@@ -5157,7 +5167,7 @@
       </c>
       <c r="K48" s="9" t="n"/>
     </row>
-    <row r="49" ht="18" customHeight="1" s="125">
+    <row r="49" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A49" s="68" t="n">
         <v>274</v>
       </c>
@@ -5198,7 +5208,7 @@
       </c>
       <c r="K49" s="9" t="n"/>
     </row>
-    <row r="50" ht="18" customHeight="1" s="125">
+    <row r="50" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A50" s="68" t="n">
         <v>275</v>
       </c>
@@ -5239,7 +5249,7 @@
       </c>
       <c r="K50" s="9" t="n"/>
     </row>
-    <row r="51" ht="18" customHeight="1" s="125">
+    <row r="51" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A51" s="68" t="n">
         <v>276</v>
       </c>
@@ -5485,7 +5495,7 @@
       </c>
       <c r="K56" s="9" t="n"/>
     </row>
-    <row r="57" ht="18" customHeight="1" s="125">
+    <row r="57" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A57" s="68" t="n">
         <v>287</v>
       </c>
@@ -5526,7 +5536,7 @@
       </c>
       <c r="K57" s="9" t="n"/>
     </row>
-    <row r="58" ht="18" customHeight="1" s="125">
+    <row r="58" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A58" s="68" t="n">
         <v>296</v>
       </c>
@@ -5747,7 +5757,7 @@
       </c>
       <c r="K62" s="9" t="n"/>
     </row>
-    <row r="63" ht="18" customHeight="1" s="125">
+    <row r="63" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A63" s="68" t="n">
         <v>303</v>
       </c>
@@ -5792,7 +5802,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1" s="125">
+    <row r="64" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A64" s="68" t="n">
         <v>304</v>
       </c>
@@ -6087,7 +6097,7 @@
       </c>
       <c r="K70" s="9" t="n"/>
     </row>
-    <row r="71" ht="18" customHeight="1" s="125">
+    <row r="71" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A71" s="68" t="n">
         <v>316</v>
       </c>
@@ -6318,7 +6328,7 @@
       </c>
       <c r="K75" s="9" t="n"/>
     </row>
-    <row r="76" ht="18" customHeight="1" s="125">
+    <row r="76" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A76" s="68" t="n">
         <v>323</v>
       </c>
@@ -6361,7 +6371,7 @@
       </c>
       <c r="K76" s="9" t="n"/>
     </row>
-    <row r="77" ht="18" customHeight="1" s="125">
+    <row r="77" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A77" s="68" t="n">
         <v>324</v>
       </c>
@@ -6404,7 +6414,7 @@
       </c>
       <c r="K77" s="9" t="n"/>
     </row>
-    <row r="78" ht="18" customHeight="1" s="125">
+    <row r="78" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A78" s="68" t="n">
         <v>325</v>
       </c>
@@ -6490,7 +6500,7 @@
       </c>
       <c r="K79" s="9" t="n"/>
     </row>
-    <row r="80" ht="18" customHeight="1" s="125">
+    <row r="80" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A80" s="68" t="n">
         <v>327</v>
       </c>
@@ -6576,7 +6586,7 @@
       </c>
       <c r="K81" s="9" t="n"/>
     </row>
-    <row r="82" ht="18" customHeight="1" s="125">
+    <row r="82" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A82" s="68" t="n">
         <v>329</v>
       </c>
@@ -6619,7 +6629,7 @@
       </c>
       <c r="K82" s="9" t="n"/>
     </row>
-    <row r="83" ht="18" customHeight="1" s="125">
+    <row r="83" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A83" s="68" t="n">
         <v>330</v>
       </c>
@@ -6662,7 +6672,7 @@
       </c>
       <c r="K83" s="9" t="n"/>
     </row>
-    <row r="84" ht="18" customHeight="1" s="125">
+    <row r="84" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A84" s="68" t="n">
         <v>339</v>
       </c>
@@ -6705,7 +6715,7 @@
       </c>
       <c r="K84" s="9" t="n"/>
     </row>
-    <row r="85" ht="18" customHeight="1" s="125">
+    <row r="85" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A85" s="68" t="n">
         <v>341</v>
       </c>
@@ -7008,7 +7018,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="18" customHeight="1" s="125">
+    <row r="92" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A92" s="68" t="n">
         <v>373</v>
       </c>
@@ -7497,7 +7507,7 @@
       </c>
       <c r="K102" s="9" t="n"/>
     </row>
-    <row r="103" ht="18" customHeight="1" s="125">
+    <row r="103" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A103" s="68" t="n">
         <v>389</v>
       </c>
@@ -7540,7 +7550,7 @@
       </c>
       <c r="K103" s="9" t="n"/>
     </row>
-    <row r="104" ht="18" customHeight="1" s="125">
+    <row r="104" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A104" s="68" t="n">
         <v>390</v>
       </c>
@@ -7822,7 +7832,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1" s="125">
+    <row r="110" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A110" s="68" t="n">
         <v>396</v>
       </c>
@@ -7831,7 +7841,7 @@
           <t>25-32-00-00-SVA</t>
         </is>
       </c>
-      <c r="C110" s="81" t="inlineStr">
+      <c r="C110" s="7" t="inlineStr">
         <is>
           <t>25-32-00-00-SVA (00) / GALLEY CHECK</t>
         </is>
@@ -7857,11 +7867,7 @@
         </is>
       </c>
       <c r="H110" s="10" t="n"/>
-      <c r="I110" s="9" t="inlineStr">
-        <is>
-          <t>TO BE CLOSED</t>
-        </is>
-      </c>
+      <c r="I110" s="9" t="n"/>
       <c r="J110" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -8409,7 +8415,7 @@
       </c>
       <c r="K122" s="9" t="n"/>
     </row>
-    <row r="123" ht="18" customHeight="1" s="125">
+    <row r="123" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A123" s="68" t="n">
         <v>454</v>
       </c>
@@ -8730,7 +8736,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="15.6" customHeight="1" s="125">
+    <row r="130" hidden="1" ht="15.6" customHeight="1" s="125">
       <c r="A130" s="68" t="inlineStr">
         <is>
           <t>501</t>
@@ -9049,7 +9055,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="15.6" customHeight="1" s="125">
+    <row r="137" hidden="1" ht="15.6" customHeight="1" s="125">
       <c r="A137" s="68" t="inlineStr">
         <is>
           <t>506</t>
@@ -9290,7 +9296,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="18" customHeight="1" s="125">
+    <row r="142" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A142" s="68" t="n">
         <v>564</v>
       </c>
@@ -9413,7 +9419,7 @@
       </c>
       <c r="K144" s="9" t="n"/>
     </row>
-    <row r="145" ht="18" customHeight="1" s="125">
+    <row r="145" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A145" s="68" t="n">
         <v>567</v>
       </c>
@@ -9454,7 +9460,7 @@
       </c>
       <c r="K145" s="9" t="n"/>
     </row>
-    <row r="146" ht="18" customHeight="1" s="125">
+    <row r="146" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A146" s="68" t="n">
         <v>570</v>
       </c>
@@ -9855,7 +9861,7 @@
       </c>
       <c r="K154" s="9" t="n"/>
     </row>
-    <row r="155" ht="18" customHeight="1" s="125">
+    <row r="155" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A155" s="68" t="n">
         <v>587</v>
       </c>
@@ -9888,11 +9894,7 @@
         </is>
       </c>
       <c r="H155" s="10" t="n"/>
-      <c r="I155" s="9" t="inlineStr">
-        <is>
-          <t>REQ S/M</t>
-        </is>
-      </c>
+      <c r="I155" s="9" t="n"/>
       <c r="J155" s="9" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10149,7 +10151,7 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="18" customHeight="1" s="125">
+    <row r="161" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A161" s="68" t="n">
         <v>597</v>
       </c>
@@ -12857,7 +12859,7 @@
         </is>
       </c>
     </row>
-    <row r="217" ht="35.25" customHeight="1" s="125">
+    <row r="217" hidden="1" ht="35.25" customHeight="1" s="125">
       <c r="A217" s="68" t="n">
         <v>687</v>
       </c>
@@ -12890,11 +12892,7 @@
         </is>
       </c>
       <c r="H217" s="10" t="n"/>
-      <c r="I217" s="9" t="inlineStr">
-        <is>
-          <t>TO BE CLOSED</t>
-        </is>
-      </c>
+      <c r="I217" s="9" t="n"/>
       <c r="J217" s="9" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -14960,7 +14958,7 @@
         </is>
       </c>
     </row>
-    <row r="260" ht="18" customHeight="1" s="125">
+    <row r="260" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A260" s="68" t="n">
         <v>744</v>
       </c>
@@ -14997,11 +14995,7 @@
           <t>Requested</t>
         </is>
       </c>
-      <c r="I260" s="9" t="inlineStr">
-        <is>
-          <t>SEALANT EXCESS - TO DO AGAIN</t>
-        </is>
-      </c>
+      <c r="I260" s="9" t="n"/>
       <c r="J260" s="9" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -16510,7 +16504,7 @@
         </is>
       </c>
     </row>
-    <row r="290" ht="18" customHeight="1" s="125">
+    <row r="290" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A290" s="68" t="inlineStr">
         <is>
           <t>801</t>
@@ -16881,7 +16875,7 @@
         </is>
       </c>
     </row>
-    <row r="297" ht="18" customHeight="1" s="125">
+    <row r="297" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A297" s="68" t="inlineStr">
         <is>
           <t>826</t>
@@ -16930,7 +16924,7 @@
         </is>
       </c>
     </row>
-    <row r="298" ht="18" customHeight="1" s="125">
+    <row r="298" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A298" s="68" t="inlineStr">
         <is>
           <t>827</t>
@@ -16979,7 +16973,7 @@
         </is>
       </c>
     </row>
-    <row r="299" ht="18" customHeight="1" s="125">
+    <row r="299" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A299" s="68" t="inlineStr">
         <is>
           <t>828</t>
@@ -17028,7 +17022,7 @@
         </is>
       </c>
     </row>
-    <row r="300" ht="18" customHeight="1" s="125">
+    <row r="300" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A300" s="68" t="inlineStr">
         <is>
           <t>829</t>
@@ -17375,7 +17369,7 @@
         </is>
       </c>
     </row>
-    <row r="307" ht="18" customHeight="1" s="125">
+    <row r="307" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A307" s="68" t="n">
         <v>866</v>
       </c>
@@ -17420,7 +17414,7 @@
         </is>
       </c>
     </row>
-    <row r="308" ht="18" customHeight="1" s="125">
+    <row r="308" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A308" s="68" t="n">
         <v>867</v>
       </c>
@@ -17467,7 +17461,7 @@
         </is>
       </c>
     </row>
-    <row r="309" ht="18" customHeight="1" s="125">
+    <row r="309" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A309" s="68" t="n">
         <v>869</v>
       </c>
@@ -17486,7 +17480,7 @@
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
@@ -17508,7 +17502,7 @@
       </c>
       <c r="K309" s="9" t="n"/>
     </row>
-    <row r="310" ht="18" customHeight="1" s="125">
+    <row r="310" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A310" s="68" t="n">
         <v>870</v>
       </c>
@@ -17549,7 +17543,7 @@
       </c>
       <c r="K310" s="9" t="n"/>
     </row>
-    <row r="311" ht="18" customHeight="1" s="125">
+    <row r="311" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A311" s="68" t="n">
         <v>871</v>
       </c>
@@ -17680,7 +17674,7 @@
       </c>
       <c r="K313" s="9" t="n"/>
     </row>
-    <row r="314" ht="18" customHeight="1" s="125">
+    <row r="314" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A314" s="68" t="n">
         <v>877</v>
       </c>
@@ -17721,7 +17715,7 @@
       </c>
       <c r="K314" s="9" t="n"/>
     </row>
-    <row r="315" ht="18" customHeight="1" s="125">
+    <row r="315" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A315" s="68" t="n">
         <v>878</v>
       </c>
@@ -17852,7 +17846,7 @@
       </c>
       <c r="K317" s="9" t="n"/>
     </row>
-    <row r="318" ht="18" customHeight="1" s="125">
+    <row r="318" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A318" s="68" t="n">
         <v>881</v>
       </c>
@@ -17893,7 +17887,7 @@
       </c>
       <c r="K318" s="9" t="n"/>
     </row>
-    <row r="319" ht="18" customHeight="1" s="125">
+    <row r="319" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A319" s="68" t="n">
         <v>882</v>
       </c>
@@ -17934,7 +17928,7 @@
       </c>
       <c r="K319" s="9" t="n"/>
     </row>
-    <row r="320" ht="18" customHeight="1" s="125">
+    <row r="320" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A320" s="68" t="n">
         <v>883</v>
       </c>
@@ -18016,7 +18010,7 @@
       </c>
       <c r="K321" s="9" t="n"/>
     </row>
-    <row r="322" ht="18" customHeight="1" s="125">
+    <row r="322" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A322" s="68" t="n">
         <v>885</v>
       </c>
@@ -18180,7 +18174,7 @@
       </c>
       <c r="K325" s="9" t="n"/>
     </row>
-    <row r="326" ht="18" customHeight="1" s="125">
+    <row r="326" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A326" s="68" t="n">
         <v>908</v>
       </c>
@@ -18221,7 +18215,7 @@
       </c>
       <c r="K326" s="9" t="n"/>
     </row>
-    <row r="327" ht="18" customHeight="1" s="125">
+    <row r="327" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A327" s="68" t="n">
         <v>909</v>
       </c>
@@ -18262,7 +18256,7 @@
       </c>
       <c r="K327" s="9" t="n"/>
     </row>
-    <row r="328" ht="18" customHeight="1" s="125">
+    <row r="328" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A328" s="68" t="n">
         <v>913</v>
       </c>
@@ -18344,7 +18338,7 @@
       </c>
       <c r="K329" s="9" t="n"/>
     </row>
-    <row r="330" ht="18" customHeight="1" s="125">
+    <row r="330" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A330" s="68" t="n">
         <v>915</v>
       </c>
@@ -18363,7 +18357,7 @@
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F330" s="9" t="inlineStr">
@@ -18385,7 +18379,7 @@
       </c>
       <c r="K330" s="9" t="n"/>
     </row>
-    <row r="331" ht="18" customHeight="1" s="125">
+    <row r="331" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A331" s="68" t="n">
         <v>916</v>
       </c>
@@ -18426,7 +18420,7 @@
       </c>
       <c r="K331" s="9" t="n"/>
     </row>
-    <row r="332" ht="18" customHeight="1" s="125">
+    <row r="332" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A332" s="68" t="n">
         <v>917</v>
       </c>
@@ -18549,7 +18543,7 @@
       </c>
       <c r="K334" s="9" t="n"/>
     </row>
-    <row r="335" ht="18" customHeight="1" s="125">
+    <row r="335" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A335" s="68" t="n">
         <v>920</v>
       </c>
@@ -18635,7 +18629,7 @@
         </is>
       </c>
     </row>
-    <row r="337" ht="34.5" customHeight="1" s="125">
+    <row r="337" hidden="1" ht="34.5" customHeight="1" s="125">
       <c r="A337" s="68" t="n">
         <v>922</v>
       </c>
@@ -18725,7 +18719,7 @@
       </c>
       <c r="K338" s="9" t="n"/>
     </row>
-    <row r="339" ht="18" customHeight="1" s="125">
+    <row r="339" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A339" s="68" t="n">
         <v>924</v>
       </c>
@@ -18946,7 +18940,7 @@
       </c>
       <c r="K343" s="9" t="n"/>
     </row>
-    <row r="344" ht="18" customHeight="1" s="125">
+    <row r="344" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A344" s="68" t="n">
         <v>933</v>
       </c>
@@ -20427,7 +20421,7 @@
       </c>
       <c r="K376" s="9" t="n"/>
     </row>
-    <row r="377" ht="18" customHeight="1" s="125">
+    <row r="377" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A377" s="68" t="n">
         <v>1010</v>
       </c>
@@ -20446,7 +20440,7 @@
       </c>
       <c r="E377" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F377" s="9" t="inlineStr">
@@ -20734,7 +20728,7 @@
       </c>
       <c r="K383" s="9" t="n"/>
     </row>
-    <row r="384" ht="18" customHeight="1" s="125">
+    <row r="384" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A384" s="68" t="n">
         <v>1017</v>
       </c>
@@ -20748,7 +20742,7 @@
       </c>
       <c r="D384" s="8" t="inlineStr">
         <is>
-          <t>GENERAL CABIN</t>
+          <t>TEDLAR/SIDEWALL</t>
         </is>
       </c>
       <c r="E384" s="9" t="inlineStr">
@@ -20763,7 +20757,7 @@
       </c>
       <c r="G384" s="8" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>S/W</t>
         </is>
       </c>
       <c r="H384" s="10" t="n"/>
@@ -20804,7 +20798,7 @@
       </c>
       <c r="G385" s="8" t="inlineStr">
         <is>
-          <t>PAINT</t>
+          <t>JOINT</t>
         </is>
       </c>
       <c r="H385" s="10" t="n"/>
@@ -20857,7 +20851,7 @@
       <c r="J386" s="9" t="n"/>
       <c r="K386" s="9" t="n"/>
     </row>
-    <row r="387" ht="18" customHeight="1" s="125">
+    <row r="387" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A387" s="5" t="n"/>
       <c r="B387" s="6" t="n"/>
       <c r="D387" s="8" t="n"/>
@@ -20877,7 +20871,7 @@
       <c r="J387" s="9" t="n"/>
       <c r="K387" s="9" t="n"/>
     </row>
-    <row r="388" ht="18" customHeight="1" s="125">
+    <row r="388" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A388" s="5" t="n"/>
       <c r="B388" s="6" t="n"/>
       <c r="C388" s="7" t="n"/>
@@ -20898,7 +20892,7 @@
       <c r="J388" s="9" t="n"/>
       <c r="K388" s="9" t="n"/>
     </row>
-    <row r="389" ht="18" customHeight="1" s="125">
+    <row r="389" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A389" s="5" t="n"/>
       <c r="B389" s="6" t="n"/>
       <c r="C389" s="7" t="n"/>
@@ -20919,7 +20913,7 @@
       <c r="J389" s="9" t="n"/>
       <c r="K389" s="9" t="n"/>
     </row>
-    <row r="390" ht="18" customHeight="1" s="125">
+    <row r="390" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A390" s="5" t="n"/>
       <c r="B390" s="6" t="n"/>
       <c r="C390" s="7" t="n"/>
@@ -20940,7 +20934,7 @@
       <c r="J390" s="9" t="n"/>
       <c r="K390" s="9" t="n"/>
     </row>
-    <row r="391" ht="18" customHeight="1" s="125">
+    <row r="391" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A391" s="5" t="n"/>
       <c r="B391" s="6" t="n"/>
       <c r="C391" s="7" t="n"/>
@@ -20961,7 +20955,7 @@
       <c r="J391" s="9" t="n"/>
       <c r="K391" s="9" t="n"/>
     </row>
-    <row r="392" ht="18" customHeight="1" s="125">
+    <row r="392" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A392" s="5" t="n"/>
       <c r="B392" s="6" t="n"/>
       <c r="C392" s="7" t="n"/>
@@ -20982,7 +20976,7 @@
       <c r="J392" s="9" t="n"/>
       <c r="K392" s="9" t="n"/>
     </row>
-    <row r="393" ht="18" customHeight="1" s="125">
+    <row r="393" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A393" s="5" t="n"/>
       <c r="B393" s="6" t="n"/>
       <c r="C393" s="7" t="n"/>
@@ -21003,7 +20997,7 @@
       <c r="J393" s="9" t="n"/>
       <c r="K393" s="9" t="n"/>
     </row>
-    <row r="394" ht="18" customHeight="1" s="125">
+    <row r="394" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A394" s="5" t="n"/>
       <c r="B394" s="6" t="n"/>
       <c r="C394" s="7" t="n"/>
@@ -21024,7 +21018,7 @@
       <c r="J394" s="9" t="n"/>
       <c r="K394" s="9" t="n"/>
     </row>
-    <row r="395" ht="18" customHeight="1" s="125">
+    <row r="395" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A395" s="5" t="n"/>
       <c r="B395" s="6" t="n"/>
       <c r="C395" s="7" t="n"/>
@@ -21045,7 +21039,7 @@
       <c r="J395" s="9" t="n"/>
       <c r="K395" s="9" t="n"/>
     </row>
-    <row r="396" ht="18" customHeight="1" s="125">
+    <row r="396" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A396" s="5" t="n"/>
       <c r="B396" s="6" t="n"/>
       <c r="C396" s="7" t="n"/>
@@ -21066,7 +21060,7 @@
       <c r="J396" s="9" t="n"/>
       <c r="K396" s="9" t="n"/>
     </row>
-    <row r="397" ht="18" customHeight="1" s="125">
+    <row r="397" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A397" s="5" t="n"/>
       <c r="B397" s="6" t="n"/>
       <c r="C397" s="7" t="n"/>
@@ -21087,7 +21081,7 @@
       <c r="J397" s="9" t="n"/>
       <c r="K397" s="9" t="n"/>
     </row>
-    <row r="398" ht="18" customHeight="1" s="125">
+    <row r="398" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A398" s="5" t="n"/>
       <c r="B398" s="6" t="n"/>
       <c r="C398" s="7" t="n"/>
@@ -21108,7 +21102,7 @@
       <c r="J398" s="9" t="n"/>
       <c r="K398" s="9" t="n"/>
     </row>
-    <row r="399" ht="18" customHeight="1" s="125">
+    <row r="399" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A399" s="5" t="n"/>
       <c r="B399" s="6" t="n"/>
       <c r="C399" s="7" t="n"/>
@@ -21129,7 +21123,7 @@
       <c r="J399" s="9" t="n"/>
       <c r="K399" s="9" t="n"/>
     </row>
-    <row r="400" ht="18" customHeight="1" s="125">
+    <row r="400" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A400" s="5" t="n"/>
       <c r="B400" s="6" t="n"/>
       <c r="C400" s="7" t="n"/>
@@ -21150,7 +21144,7 @@
       <c r="J400" s="9" t="n"/>
       <c r="K400" s="9" t="n"/>
     </row>
-    <row r="401" ht="18" customHeight="1" s="125">
+    <row r="401" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A401" s="5" t="n"/>
       <c r="B401" s="6" t="n"/>
       <c r="C401" s="7" t="n"/>
@@ -21171,7 +21165,7 @@
       <c r="J401" s="9" t="n"/>
       <c r="K401" s="9" t="n"/>
     </row>
-    <row r="402" ht="18" customHeight="1" s="125">
+    <row r="402" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A402" s="5" t="n"/>
       <c r="B402" s="6" t="n"/>
       <c r="C402" s="7" t="n"/>
@@ -21192,7 +21186,7 @@
       <c r="J402" s="9" t="n"/>
       <c r="K402" s="9" t="n"/>
     </row>
-    <row r="403" ht="18" customHeight="1" s="125">
+    <row r="403" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A403" s="5" t="n"/>
       <c r="B403" s="6" t="n"/>
       <c r="C403" s="7" t="n"/>
@@ -21213,7 +21207,7 @@
       <c r="J403" s="9" t="n"/>
       <c r="K403" s="9" t="n"/>
     </row>
-    <row r="404" ht="18" customHeight="1" s="125">
+    <row r="404" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A404" s="5" t="n"/>
       <c r="B404" s="6" t="n"/>
       <c r="C404" s="7" t="n"/>
@@ -21234,7 +21228,7 @@
       <c r="J404" s="9" t="n"/>
       <c r="K404" s="9" t="n"/>
     </row>
-    <row r="405" ht="18" customHeight="1" s="125">
+    <row r="405" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A405" s="5" t="n"/>
       <c r="B405" s="6" t="n"/>
       <c r="C405" s="7" t="n"/>
@@ -21255,7 +21249,7 @@
       <c r="J405" s="9" t="n"/>
       <c r="K405" s="9" t="n"/>
     </row>
-    <row r="406" ht="18" customHeight="1" s="125">
+    <row r="406" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A406" s="5" t="n"/>
       <c r="B406" s="6" t="n"/>
       <c r="C406" s="7" t="n"/>
@@ -21276,7 +21270,7 @@
       <c r="J406" s="9" t="n"/>
       <c r="K406" s="9" t="n"/>
     </row>
-    <row r="407" ht="18" customHeight="1" s="125">
+    <row r="407" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A407" s="5" t="n"/>
       <c r="B407" s="6" t="n"/>
       <c r="C407" s="7" t="n"/>
@@ -21297,7 +21291,7 @@
       <c r="J407" s="9" t="n"/>
       <c r="K407" s="9" t="n"/>
     </row>
-    <row r="408" ht="18" customHeight="1" s="125">
+    <row r="408" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A408" s="5" t="n"/>
       <c r="B408" s="6" t="n"/>
       <c r="C408" s="7" t="n"/>
@@ -21318,7 +21312,7 @@
       <c r="J408" s="9" t="n"/>
       <c r="K408" s="9" t="n"/>
     </row>
-    <row r="409" ht="18" customHeight="1" s="125">
+    <row r="409" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A409" s="5" t="n"/>
       <c r="B409" s="6" t="n"/>
       <c r="C409" s="7" t="n"/>
@@ -21339,7 +21333,7 @@
       <c r="J409" s="9" t="n"/>
       <c r="K409" s="9" t="n"/>
     </row>
-    <row r="410" ht="18" customHeight="1" s="125">
+    <row r="410" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A410" s="5" t="n"/>
       <c r="B410" s="6" t="n"/>
       <c r="C410" s="7" t="n"/>
@@ -21360,7 +21354,7 @@
       <c r="J410" s="9" t="n"/>
       <c r="K410" s="9" t="n"/>
     </row>
-    <row r="411" ht="18" customHeight="1" s="125">
+    <row r="411" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A411" s="5" t="n"/>
       <c r="B411" s="6" t="n"/>
       <c r="C411" s="7" t="n"/>
@@ -21381,7 +21375,7 @@
       <c r="J411" s="9" t="n"/>
       <c r="K411" s="9" t="n"/>
     </row>
-    <row r="412" ht="18" customHeight="1" s="125">
+    <row r="412" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A412" s="5" t="n"/>
       <c r="B412" s="6" t="n"/>
       <c r="C412" s="7" t="n"/>
@@ -21402,7 +21396,7 @@
       <c r="J412" s="9" t="n"/>
       <c r="K412" s="9" t="n"/>
     </row>
-    <row r="413" ht="18" customHeight="1" s="125">
+    <row r="413" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A413" s="5" t="n"/>
       <c r="B413" s="6" t="n"/>
       <c r="C413" s="7" t="n"/>
@@ -21423,7 +21417,7 @@
       <c r="J413" s="9" t="n"/>
       <c r="K413" s="9" t="n"/>
     </row>
-    <row r="414" ht="18" customHeight="1" s="125">
+    <row r="414" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A414" s="5" t="n"/>
       <c r="B414" s="6" t="n"/>
       <c r="C414" s="7" t="n"/>
@@ -21444,7 +21438,7 @@
       <c r="J414" s="9" t="n"/>
       <c r="K414" s="9" t="n"/>
     </row>
-    <row r="415" ht="18" customHeight="1" s="125">
+    <row r="415" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A415" s="5" t="n"/>
       <c r="B415" s="6" t="n"/>
       <c r="C415" s="7" t="n"/>
@@ -21465,7 +21459,7 @@
       <c r="J415" s="9" t="n"/>
       <c r="K415" s="9" t="n"/>
     </row>
-    <row r="416" ht="18" customHeight="1" s="125">
+    <row r="416" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A416" s="5" t="n"/>
       <c r="B416" s="6" t="n"/>
       <c r="C416" s="7" t="n"/>
@@ -21486,7 +21480,7 @@
       <c r="J416" s="9" t="n"/>
       <c r="K416" s="9" t="n"/>
     </row>
-    <row r="417" ht="18" customHeight="1" s="125">
+    <row r="417" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A417" s="5" t="n"/>
       <c r="B417" s="6" t="n"/>
       <c r="C417" s="7" t="n"/>
@@ -21507,7 +21501,7 @@
       <c r="J417" s="9" t="n"/>
       <c r="K417" s="9" t="n"/>
     </row>
-    <row r="418" ht="18" customHeight="1" s="125">
+    <row r="418" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A418" s="5" t="n"/>
       <c r="B418" s="6" t="n"/>
       <c r="C418" s="7" t="n"/>
@@ -21528,7 +21522,7 @@
       <c r="J418" s="9" t="n"/>
       <c r="K418" s="9" t="n"/>
     </row>
-    <row r="419" ht="18" customHeight="1" s="125">
+    <row r="419" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A419" s="5" t="n"/>
       <c r="B419" s="6" t="n"/>
       <c r="C419" s="7" t="n"/>
@@ -21549,7 +21543,7 @@
       <c r="J419" s="9" t="n"/>
       <c r="K419" s="9" t="n"/>
     </row>
-    <row r="420" ht="18" customHeight="1" s="125">
+    <row r="420" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A420" s="5" t="n"/>
       <c r="B420" s="6" t="n"/>
       <c r="C420" s="7" t="n"/>
@@ -21570,7 +21564,7 @@
       <c r="J420" s="9" t="n"/>
       <c r="K420" s="9" t="n"/>
     </row>
-    <row r="421" ht="18" customHeight="1" s="125">
+    <row r="421" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A421" s="5" t="n"/>
       <c r="B421" s="6" t="n"/>
       <c r="C421" s="7" t="n"/>
@@ -21591,7 +21585,7 @@
       <c r="J421" s="9" t="n"/>
       <c r="K421" s="9" t="n"/>
     </row>
-    <row r="422" ht="18" customHeight="1" s="125">
+    <row r="422" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A422" s="5" t="n"/>
       <c r="B422" s="6" t="n"/>
       <c r="C422" s="7" t="n"/>
@@ -21612,7 +21606,7 @@
       <c r="J422" s="9" t="n"/>
       <c r="K422" s="9" t="n"/>
     </row>
-    <row r="423" ht="18" customHeight="1" s="125">
+    <row r="423" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A423" s="5" t="n"/>
       <c r="B423" s="6" t="n"/>
       <c r="C423" s="7" t="n"/>
@@ -21633,7 +21627,7 @@
       <c r="J423" s="9" t="n"/>
       <c r="K423" s="9" t="n"/>
     </row>
-    <row r="424" ht="18" customHeight="1" s="125">
+    <row r="424" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A424" s="5" t="n"/>
       <c r="B424" s="6" t="n"/>
       <c r="C424" s="7" t="n"/>
@@ -21654,7 +21648,7 @@
       <c r="J424" s="9" t="n"/>
       <c r="K424" s="9" t="n"/>
     </row>
-    <row r="425" ht="18" customHeight="1" s="125">
+    <row r="425" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A425" s="5" t="n"/>
       <c r="B425" s="6" t="n"/>
       <c r="C425" s="7" t="n"/>
@@ -21675,7 +21669,7 @@
       <c r="J425" s="9" t="n"/>
       <c r="K425" s="9" t="n"/>
     </row>
-    <row r="426" ht="18" customHeight="1" s="125">
+    <row r="426" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A426" s="5" t="n"/>
       <c r="B426" s="6" t="n"/>
       <c r="C426" s="7" t="n"/>
@@ -21696,7 +21690,7 @@
       <c r="J426" s="9" t="n"/>
       <c r="K426" s="9" t="n"/>
     </row>
-    <row r="427" ht="18" customHeight="1" s="125">
+    <row r="427" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A427" s="5" t="n"/>
       <c r="B427" s="6" t="n"/>
       <c r="C427" s="7" t="n"/>
@@ -21717,7 +21711,7 @@
       <c r="J427" s="9" t="n"/>
       <c r="K427" s="9" t="n"/>
     </row>
-    <row r="428" ht="18" customHeight="1" s="125">
+    <row r="428" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A428" s="5" t="n"/>
       <c r="B428" s="6" t="n"/>
       <c r="C428" s="7" t="n"/>
@@ -21738,7 +21732,7 @@
       <c r="J428" s="9" t="n"/>
       <c r="K428" s="9" t="n"/>
     </row>
-    <row r="429" ht="18" customHeight="1" s="125">
+    <row r="429" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A429" s="5" t="n"/>
       <c r="B429" s="6" t="n"/>
       <c r="C429" s="7" t="n"/>
@@ -21759,7 +21753,7 @@
       <c r="J429" s="9" t="n"/>
       <c r="K429" s="9" t="n"/>
     </row>
-    <row r="430" ht="18" customHeight="1" s="125">
+    <row r="430" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A430" s="5" t="n"/>
       <c r="B430" s="6" t="n"/>
       <c r="C430" s="7" t="n"/>
@@ -21780,7 +21774,7 @@
       <c r="J430" s="9" t="n"/>
       <c r="K430" s="9" t="n"/>
     </row>
-    <row r="431" ht="18" customHeight="1" s="125">
+    <row r="431" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A431" s="5" t="n"/>
       <c r="B431" s="6" t="n"/>
       <c r="C431" s="7" t="n"/>
@@ -21801,7 +21795,7 @@
       <c r="J431" s="9" t="n"/>
       <c r="K431" s="9" t="n"/>
     </row>
-    <row r="432" ht="18" customHeight="1" s="125">
+    <row r="432" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A432" s="5" t="n"/>
       <c r="B432" s="6" t="n"/>
       <c r="C432" s="7" t="n"/>
@@ -21822,7 +21816,7 @@
       <c r="J432" s="9" t="n"/>
       <c r="K432" s="9" t="n"/>
     </row>
-    <row r="433" ht="18" customHeight="1" s="125">
+    <row r="433" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A433" s="5" t="n"/>
       <c r="B433" s="6" t="n"/>
       <c r="C433" s="7" t="n"/>
@@ -21843,7 +21837,7 @@
       <c r="J433" s="9" t="n"/>
       <c r="K433" s="9" t="n"/>
     </row>
-    <row r="434" ht="18" customHeight="1" s="125">
+    <row r="434" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A434" s="5" t="n"/>
       <c r="B434" s="6" t="n"/>
       <c r="C434" s="7" t="n"/>
@@ -21864,7 +21858,7 @@
       <c r="J434" s="9" t="n"/>
       <c r="K434" s="9" t="n"/>
     </row>
-    <row r="435" ht="18" customHeight="1" s="125">
+    <row r="435" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A435" s="5" t="n"/>
       <c r="B435" s="6" t="n"/>
       <c r="C435" s="7" t="n"/>
@@ -21885,7 +21879,7 @@
       <c r="J435" s="9" t="n"/>
       <c r="K435" s="9" t="n"/>
     </row>
-    <row r="436" ht="18" customHeight="1" s="125">
+    <row r="436" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A436" s="5" t="n"/>
       <c r="B436" s="6" t="n"/>
       <c r="C436" s="7" t="n"/>
@@ -21906,7 +21900,7 @@
       <c r="J436" s="9" t="n"/>
       <c r="K436" s="9" t="n"/>
     </row>
-    <row r="437" ht="18" customHeight="1" s="125">
+    <row r="437" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A437" s="5" t="n"/>
       <c r="B437" s="6" t="n"/>
       <c r="C437" s="7" t="n"/>
@@ -21927,7 +21921,7 @@
       <c r="J437" s="9" t="n"/>
       <c r="K437" s="9" t="n"/>
     </row>
-    <row r="438" ht="18" customHeight="1" s="125">
+    <row r="438" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A438" s="5" t="n"/>
       <c r="B438" s="6" t="n"/>
       <c r="C438" s="7" t="n"/>
@@ -21948,7 +21942,7 @@
       <c r="J438" s="9" t="n"/>
       <c r="K438" s="9" t="n"/>
     </row>
-    <row r="439" ht="18" customHeight="1" s="125">
+    <row r="439" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A439" s="5" t="n"/>
       <c r="B439" s="6" t="n"/>
       <c r="C439" s="7" t="n"/>
@@ -21969,7 +21963,7 @@
       <c r="J439" s="9" t="n"/>
       <c r="K439" s="9" t="n"/>
     </row>
-    <row r="440" ht="18" customHeight="1" s="125">
+    <row r="440" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A440" s="5" t="n"/>
       <c r="B440" s="6" t="n"/>
       <c r="C440" s="7" t="n"/>
@@ -21990,7 +21984,7 @@
       <c r="J440" s="9" t="n"/>
       <c r="K440" s="9" t="n"/>
     </row>
-    <row r="441" ht="18" customHeight="1" s="125">
+    <row r="441" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A441" s="5" t="n"/>
       <c r="B441" s="6" t="n"/>
       <c r="C441" s="7" t="n"/>
@@ -22011,7 +22005,7 @@
       <c r="J441" s="9" t="n"/>
       <c r="K441" s="9" t="n"/>
     </row>
-    <row r="442" ht="18" customHeight="1" s="125">
+    <row r="442" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A442" s="5" t="n"/>
       <c r="B442" s="6" t="n"/>
       <c r="C442" s="7" t="n"/>
@@ -22032,7 +22026,7 @@
       <c r="J442" s="9" t="n"/>
       <c r="K442" s="9" t="n"/>
     </row>
-    <row r="443" ht="18" customHeight="1" s="125">
+    <row r="443" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A443" s="5" t="n"/>
       <c r="B443" s="6" t="n"/>
       <c r="C443" s="7" t="n"/>
@@ -22053,7 +22047,7 @@
       <c r="J443" s="9" t="n"/>
       <c r="K443" s="9" t="n"/>
     </row>
-    <row r="444" ht="18" customHeight="1" s="125">
+    <row r="444" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A444" s="5" t="n"/>
       <c r="B444" s="6" t="n"/>
       <c r="C444" s="7" t="n"/>
@@ -22074,7 +22068,7 @@
       <c r="J444" s="9" t="n"/>
       <c r="K444" s="9" t="n"/>
     </row>
-    <row r="445" ht="18" customHeight="1" s="125">
+    <row r="445" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A445" s="5" t="n"/>
       <c r="B445" s="6" t="n"/>
       <c r="C445" s="7" t="n"/>
@@ -22095,7 +22089,7 @@
       <c r="J445" s="9" t="n"/>
       <c r="K445" s="9" t="n"/>
     </row>
-    <row r="446" ht="18" customHeight="1" s="125">
+    <row r="446" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A446" s="5" t="n"/>
       <c r="B446" s="6" t="n"/>
       <c r="C446" s="7" t="n"/>
@@ -22116,7 +22110,7 @@
       <c r="J446" s="9" t="n"/>
       <c r="K446" s="9" t="n"/>
     </row>
-    <row r="447" ht="18" customHeight="1" s="125">
+    <row r="447" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A447" s="5" t="n"/>
       <c r="B447" s="6" t="n"/>
       <c r="C447" s="7" t="n"/>
@@ -22137,7 +22131,7 @@
       <c r="J447" s="9" t="n"/>
       <c r="K447" s="9" t="n"/>
     </row>
-    <row r="448" ht="18" customHeight="1" s="125">
+    <row r="448" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A448" s="5" t="n"/>
       <c r="B448" s="6" t="n"/>
       <c r="C448" s="7" t="n"/>
@@ -22158,7 +22152,7 @@
       <c r="J448" s="9" t="n"/>
       <c r="K448" s="9" t="n"/>
     </row>
-    <row r="449" ht="18" customHeight="1" s="125">
+    <row r="449" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A449" s="5" t="n"/>
       <c r="B449" s="6" t="n"/>
       <c r="C449" s="7" t="n"/>
@@ -22179,7 +22173,7 @@
       <c r="J449" s="9" t="n"/>
       <c r="K449" s="9" t="n"/>
     </row>
-    <row r="450" ht="18" customHeight="1" s="125">
+    <row r="450" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A450" s="5" t="n"/>
       <c r="B450" s="6" t="n"/>
       <c r="C450" s="7" t="n"/>
@@ -22200,7 +22194,7 @@
       <c r="J450" s="9" t="n"/>
       <c r="K450" s="9" t="n"/>
     </row>
-    <row r="451" ht="18" customHeight="1" s="125">
+    <row r="451" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A451" s="5" t="n"/>
       <c r="B451" s="6" t="n"/>
       <c r="C451" s="7" t="n"/>
@@ -22221,7 +22215,7 @@
       <c r="J451" s="9" t="n"/>
       <c r="K451" s="9" t="n"/>
     </row>
-    <row r="452" ht="18" customHeight="1" s="125">
+    <row r="452" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A452" s="5" t="n"/>
       <c r="B452" s="6" t="n"/>
       <c r="C452" s="7" t="n"/>
@@ -22242,7 +22236,7 @@
       <c r="J452" s="9" t="n"/>
       <c r="K452" s="9" t="n"/>
     </row>
-    <row r="453" ht="18" customHeight="1" s="125">
+    <row r="453" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A453" s="5" t="n"/>
       <c r="B453" s="6" t="n"/>
       <c r="C453" s="7" t="n"/>
@@ -22263,7 +22257,7 @@
       <c r="J453" s="9" t="n"/>
       <c r="K453" s="9" t="n"/>
     </row>
-    <row r="454" ht="18" customHeight="1" s="125">
+    <row r="454" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A454" s="5" t="n"/>
       <c r="B454" s="6" t="n"/>
       <c r="C454" s="7" t="n"/>
@@ -22284,7 +22278,7 @@
       <c r="J454" s="9" t="n"/>
       <c r="K454" s="9" t="n"/>
     </row>
-    <row r="455" ht="18" customHeight="1" s="125">
+    <row r="455" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A455" s="5" t="n"/>
       <c r="B455" s="6" t="n"/>
       <c r="C455" s="7" t="n"/>
@@ -22305,7 +22299,7 @@
       <c r="J455" s="9" t="n"/>
       <c r="K455" s="9" t="n"/>
     </row>
-    <row r="456" ht="18" customHeight="1" s="125">
+    <row r="456" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A456" s="5" t="n"/>
       <c r="B456" s="6" t="n"/>
       <c r="C456" s="7" t="n"/>
@@ -22326,7 +22320,7 @@
       <c r="J456" s="9" t="n"/>
       <c r="K456" s="9" t="n"/>
     </row>
-    <row r="457" ht="18" customHeight="1" s="125">
+    <row r="457" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A457" s="5" t="n"/>
       <c r="B457" s="6" t="n"/>
       <c r="C457" s="7" t="n"/>
@@ -22347,7 +22341,7 @@
       <c r="J457" s="9" t="n"/>
       <c r="K457" s="9" t="n"/>
     </row>
-    <row r="458" ht="18" customHeight="1" s="125">
+    <row r="458" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A458" s="5" t="n"/>
       <c r="B458" s="6" t="n"/>
       <c r="C458" s="7" t="n"/>
@@ -22368,7 +22362,7 @@
       <c r="J458" s="9" t="n"/>
       <c r="K458" s="9" t="n"/>
     </row>
-    <row r="459" ht="18" customHeight="1" s="125">
+    <row r="459" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A459" s="5" t="n"/>
       <c r="B459" s="6" t="n"/>
       <c r="C459" s="7" t="n"/>
@@ -22389,7 +22383,7 @@
       <c r="J459" s="9" t="n"/>
       <c r="K459" s="9" t="n"/>
     </row>
-    <row r="460" ht="18" customHeight="1" s="125">
+    <row r="460" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A460" s="5" t="n"/>
       <c r="B460" s="6" t="n"/>
       <c r="C460" s="7" t="n"/>
@@ -22410,7 +22404,7 @@
       <c r="J460" s="9" t="n"/>
       <c r="K460" s="9" t="n"/>
     </row>
-    <row r="461" ht="18" customHeight="1" s="125">
+    <row r="461" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A461" s="5" t="n"/>
       <c r="B461" s="63" t="n"/>
       <c r="C461" s="7" t="n"/>
@@ -22431,7 +22425,7 @@
       <c r="J461" s="9" t="n"/>
       <c r="K461" s="9" t="n"/>
     </row>
-    <row r="462" ht="18" customHeight="1" s="125">
+    <row r="462" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A462" s="5" t="n"/>
       <c r="B462" s="6" t="n"/>
       <c r="C462" s="7" t="n"/>
@@ -22452,7 +22446,7 @@
       <c r="J462" s="9" t="n"/>
       <c r="K462" s="9" t="n"/>
     </row>
-    <row r="463" ht="18" customHeight="1" s="125">
+    <row r="463" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A463" s="5" t="n"/>
       <c r="B463" s="6" t="n"/>
       <c r="C463" s="7" t="n"/>
@@ -22473,7 +22467,7 @@
       <c r="J463" s="9" t="n"/>
       <c r="K463" s="9" t="n"/>
     </row>
-    <row r="464" ht="18" customHeight="1" s="125">
+    <row r="464" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A464" s="5" t="n"/>
       <c r="B464" s="6" t="n"/>
       <c r="C464" s="7" t="n"/>
@@ -22494,7 +22488,7 @@
       <c r="J464" s="9" t="n"/>
       <c r="K464" s="9" t="n"/>
     </row>
-    <row r="465" ht="18" customHeight="1" s="125">
+    <row r="465" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A465" s="5" t="n"/>
       <c r="B465" s="6" t="n"/>
       <c r="C465" s="7" t="n"/>
@@ -22515,7 +22509,7 @@
       <c r="J465" s="9" t="n"/>
       <c r="K465" s="9" t="n"/>
     </row>
-    <row r="466" ht="18" customHeight="1" s="125">
+    <row r="466" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A466" s="5" t="n"/>
       <c r="B466" s="6" t="n"/>
       <c r="C466" s="7" t="n"/>
@@ -22536,7 +22530,7 @@
       <c r="J466" s="9" t="n"/>
       <c r="K466" s="9" t="n"/>
     </row>
-    <row r="467" ht="18" customHeight="1" s="125">
+    <row r="467" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A467" s="5" t="n"/>
       <c r="B467" s="6" t="n"/>
       <c r="C467" s="7" t="n"/>
@@ -22557,7 +22551,7 @@
       <c r="J467" s="9" t="n"/>
       <c r="K467" s="9" t="n"/>
     </row>
-    <row r="468" ht="18" customHeight="1" s="125">
+    <row r="468" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A468" s="5" t="n"/>
       <c r="B468" s="6" t="n"/>
       <c r="C468" s="7" t="n"/>
@@ -22578,7 +22572,7 @@
       <c r="J468" s="9" t="n"/>
       <c r="K468" s="9" t="n"/>
     </row>
-    <row r="469" ht="18" customHeight="1" s="125">
+    <row r="469" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A469" s="5" t="n"/>
       <c r="B469" s="6" t="n"/>
       <c r="C469" s="7" t="n"/>
@@ -22599,7 +22593,7 @@
       <c r="J469" s="9" t="n"/>
       <c r="K469" s="9" t="n"/>
     </row>
-    <row r="470" ht="18" customHeight="1" s="125">
+    <row r="470" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A470" s="5" t="n"/>
       <c r="B470" s="6" t="n"/>
       <c r="C470" s="7" t="n"/>
@@ -22620,7 +22614,7 @@
       <c r="J470" s="9" t="n"/>
       <c r="K470" s="9" t="n"/>
     </row>
-    <row r="471" ht="18" customHeight="1" s="125">
+    <row r="471" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A471" s="5" t="n"/>
       <c r="B471" s="6" t="n"/>
       <c r="C471" s="7" t="n"/>
@@ -22641,7 +22635,7 @@
       <c r="J471" s="9" t="n"/>
       <c r="K471" s="9" t="n"/>
     </row>
-    <row r="472" ht="18" customHeight="1" s="125">
+    <row r="472" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A472" s="5" t="n"/>
       <c r="B472" s="6" t="n"/>
       <c r="C472" s="7" t="n"/>
@@ -22662,7 +22656,7 @@
       <c r="J472" s="9" t="n"/>
       <c r="K472" s="9" t="n"/>
     </row>
-    <row r="473" ht="18" customHeight="1" s="125">
+    <row r="473" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A473" s="5" t="n"/>
       <c r="B473" s="6" t="n"/>
       <c r="C473" s="7" t="n"/>
@@ -22683,7 +22677,7 @@
       <c r="J473" s="9" t="n"/>
       <c r="K473" s="9" t="n"/>
     </row>
-    <row r="474" ht="18" customHeight="1" s="125">
+    <row r="474" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A474" s="5" t="n"/>
       <c r="B474" s="6" t="n"/>
       <c r="C474" s="7" t="n"/>
@@ -22704,7 +22698,7 @@
       <c r="J474" s="9" t="n"/>
       <c r="K474" s="9" t="n"/>
     </row>
-    <row r="475" ht="18" customHeight="1" s="125">
+    <row r="475" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A475" s="5" t="n"/>
       <c r="B475" s="6" t="n"/>
       <c r="C475" s="7" t="n"/>
@@ -22725,7 +22719,7 @@
       <c r="J475" s="9" t="n"/>
       <c r="K475" s="9" t="n"/>
     </row>
-    <row r="476" ht="18" customHeight="1" s="125">
+    <row r="476" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A476" s="5" t="n"/>
       <c r="B476" s="6" t="n"/>
       <c r="C476" s="7" t="n"/>
@@ -22746,7 +22740,7 @@
       <c r="J476" s="9" t="n"/>
       <c r="K476" s="9" t="n"/>
     </row>
-    <row r="477" ht="18" customHeight="1" s="125">
+    <row r="477" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A477" s="5" t="n"/>
       <c r="B477" s="6" t="n"/>
       <c r="C477" s="7" t="n"/>
@@ -22767,7 +22761,7 @@
       <c r="J477" s="9" t="n"/>
       <c r="K477" s="9" t="n"/>
     </row>
-    <row r="478" ht="18" customHeight="1" s="125">
+    <row r="478" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A478" s="5" t="n"/>
       <c r="B478" s="6" t="n"/>
       <c r="C478" s="7" t="n"/>
@@ -22788,7 +22782,7 @@
       <c r="J478" s="9" t="n"/>
       <c r="K478" s="9" t="n"/>
     </row>
-    <row r="479" ht="18" customHeight="1" s="125">
+    <row r="479" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A479" s="5" t="n"/>
       <c r="B479" s="6" t="n"/>
       <c r="C479" s="7" t="n"/>
@@ -22809,7 +22803,7 @@
       <c r="J479" s="9" t="n"/>
       <c r="K479" s="9" t="n"/>
     </row>
-    <row r="480" ht="18" customHeight="1" s="125">
+    <row r="480" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A480" s="5" t="n"/>
       <c r="B480" s="6" t="n"/>
       <c r="C480" s="7" t="n"/>
@@ -22830,7 +22824,7 @@
       <c r="J480" s="9" t="n"/>
       <c r="K480" s="9" t="n"/>
     </row>
-    <row r="481" ht="18" customHeight="1" s="125">
+    <row r="481" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A481" s="5" t="n"/>
       <c r="B481" s="6" t="n"/>
       <c r="C481" s="7" t="n"/>
@@ -22851,7 +22845,7 @@
       <c r="J481" s="9" t="n"/>
       <c r="K481" s="9" t="n"/>
     </row>
-    <row r="482" ht="18" customHeight="1" s="125">
+    <row r="482" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A482" s="5" t="n"/>
       <c r="B482" s="6" t="n"/>
       <c r="C482" s="7" t="n"/>
@@ -22872,7 +22866,7 @@
       <c r="J482" s="9" t="n"/>
       <c r="K482" s="9" t="n"/>
     </row>
-    <row r="483" ht="18" customHeight="1" s="125">
+    <row r="483" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A483" s="5" t="n"/>
       <c r="B483" s="6" t="n"/>
       <c r="C483" s="7" t="n"/>
@@ -22893,7 +22887,7 @@
       <c r="J483" s="9" t="n"/>
       <c r="K483" s="9" t="n"/>
     </row>
-    <row r="484" ht="18" customHeight="1" s="125">
+    <row r="484" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A484" s="5" t="n"/>
       <c r="B484" s="6" t="n"/>
       <c r="C484" s="7" t="n"/>
@@ -22914,7 +22908,7 @@
       <c r="J484" s="9" t="n"/>
       <c r="K484" s="9" t="n"/>
     </row>
-    <row r="485" ht="18" customHeight="1" s="125">
+    <row r="485" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A485" s="5" t="n"/>
       <c r="B485" s="6" t="n"/>
       <c r="C485" s="7" t="n"/>
@@ -22935,7 +22929,7 @@
       <c r="J485" s="9" t="n"/>
       <c r="K485" s="9" t="n"/>
     </row>
-    <row r="486" ht="18" customHeight="1" s="125">
+    <row r="486" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A486" s="5" t="n"/>
       <c r="B486" s="6" t="n"/>
       <c r="C486" s="7" t="n"/>
@@ -22956,7 +22950,7 @@
       <c r="J486" s="9" t="n"/>
       <c r="K486" s="9" t="n"/>
     </row>
-    <row r="487" ht="18" customHeight="1" s="125">
+    <row r="487" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A487" s="5" t="n"/>
       <c r="B487" s="6" t="n"/>
       <c r="C487" s="7" t="n"/>
@@ -22977,7 +22971,7 @@
       <c r="J487" s="9" t="n"/>
       <c r="K487" s="9" t="n"/>
     </row>
-    <row r="488" ht="18" customHeight="1" s="125">
+    <row r="488" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A488" s="5" t="n"/>
       <c r="B488" s="6" t="n"/>
       <c r="C488" s="7" t="n"/>
@@ -22998,7 +22992,7 @@
       <c r="J488" s="9" t="n"/>
       <c r="K488" s="9" t="n"/>
     </row>
-    <row r="489" ht="18" customHeight="1" s="125">
+    <row r="489" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A489" s="5" t="n"/>
       <c r="B489" s="6" t="n"/>
       <c r="C489" s="7" t="n"/>
@@ -23019,7 +23013,7 @@
       <c r="J489" s="9" t="n"/>
       <c r="K489" s="9" t="n"/>
     </row>
-    <row r="490" ht="18" customHeight="1" s="125">
+    <row r="490" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A490" s="5" t="n"/>
       <c r="B490" s="6" t="n"/>
       <c r="C490" s="7" t="n"/>
@@ -23040,7 +23034,7 @@
       <c r="J490" s="9" t="n"/>
       <c r="K490" s="9" t="n"/>
     </row>
-    <row r="491" ht="18" customHeight="1" s="125">
+    <row r="491" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A491" s="5" t="n"/>
       <c r="B491" s="6" t="n"/>
       <c r="C491" s="7" t="n"/>
@@ -23061,7 +23055,7 @@
       <c r="J491" s="9" t="n"/>
       <c r="K491" s="9" t="n"/>
     </row>
-    <row r="492" ht="18" customHeight="1" s="125">
+    <row r="492" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A492" s="5" t="n"/>
       <c r="B492" s="6" t="n"/>
       <c r="C492" s="7" t="n"/>
@@ -23082,7 +23076,7 @@
       <c r="J492" s="9" t="n"/>
       <c r="K492" s="9" t="n"/>
     </row>
-    <row r="493" ht="18" customHeight="1" s="125">
+    <row r="493" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A493" s="5" t="n"/>
       <c r="B493" s="6" t="n"/>
       <c r="C493" s="7" t="n"/>
@@ -23103,7 +23097,7 @@
       <c r="J493" s="9" t="n"/>
       <c r="K493" s="9" t="n"/>
     </row>
-    <row r="494" ht="18" customHeight="1" s="125">
+    <row r="494" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A494" s="5" t="n"/>
       <c r="B494" s="6" t="n"/>
       <c r="C494" s="7" t="n"/>
@@ -23124,7 +23118,7 @@
       <c r="J494" s="9" t="n"/>
       <c r="K494" s="9" t="n"/>
     </row>
-    <row r="495" ht="18" customHeight="1" s="125">
+    <row r="495" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A495" s="5" t="n"/>
       <c r="B495" s="6" t="n"/>
       <c r="C495" s="7" t="n"/>
@@ -23145,7 +23139,7 @@
       <c r="J495" s="9" t="n"/>
       <c r="K495" s="9" t="n"/>
     </row>
-    <row r="496" ht="18" customHeight="1" s="125">
+    <row r="496" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A496" s="5" t="n"/>
       <c r="B496" s="6" t="n"/>
       <c r="C496" s="7" t="n"/>
@@ -23166,7 +23160,7 @@
       <c r="J496" s="9" t="n"/>
       <c r="K496" s="9" t="n"/>
     </row>
-    <row r="497" ht="18" customHeight="1" s="125">
+    <row r="497" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A497" s="5" t="n"/>
       <c r="B497" s="6" t="n"/>
       <c r="C497" s="7" t="n"/>
@@ -23187,7 +23181,7 @@
       <c r="J497" s="9" t="n"/>
       <c r="K497" s="9" t="n"/>
     </row>
-    <row r="498" ht="18" customHeight="1" s="125">
+    <row r="498" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A498" s="5" t="n"/>
       <c r="B498" s="6" t="n"/>
       <c r="C498" s="7" t="n"/>
@@ -23208,7 +23202,7 @@
       <c r="J498" s="9" t="n"/>
       <c r="K498" s="9" t="n"/>
     </row>
-    <row r="499" ht="18" customHeight="1" s="125">
+    <row r="499" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A499" s="5" t="n"/>
       <c r="B499" s="6" t="n"/>
       <c r="C499" s="7" t="n"/>
@@ -23229,7 +23223,7 @@
       <c r="J499" s="9" t="n"/>
       <c r="K499" s="9" t="n"/>
     </row>
-    <row r="500" ht="18" customHeight="1" s="125">
+    <row r="500" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A500" s="5" t="n"/>
       <c r="B500" s="6" t="n"/>
       <c r="C500" s="7" t="n"/>
@@ -23250,7 +23244,7 @@
       <c r="J500" s="9" t="n"/>
       <c r="K500" s="9" t="n"/>
     </row>
-    <row r="501" ht="18" customHeight="1" s="125">
+    <row r="501" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A501" s="5" t="n"/>
       <c r="B501" s="6" t="n"/>
       <c r="C501" s="7" t="n"/>
@@ -23271,7 +23265,7 @@
       <c r="J501" s="9" t="n"/>
       <c r="K501" s="9" t="n"/>
     </row>
-    <row r="502" ht="18" customHeight="1" s="125">
+    <row r="502" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A502" s="5" t="n"/>
       <c r="B502" s="6" t="n"/>
       <c r="C502" s="7" t="n"/>
@@ -23292,7 +23286,7 @@
       <c r="J502" s="9" t="n"/>
       <c r="K502" s="9" t="n"/>
     </row>
-    <row r="503" ht="18" customHeight="1" s="125">
+    <row r="503" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A503" s="5" t="n"/>
       <c r="B503" s="6" t="n"/>
       <c r="C503" s="7" t="n"/>
@@ -23313,7 +23307,7 @@
       <c r="J503" s="9" t="n"/>
       <c r="K503" s="9" t="n"/>
     </row>
-    <row r="504" ht="18" customHeight="1" s="125">
+    <row r="504" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A504" s="5" t="n"/>
       <c r="B504" s="6" t="n"/>
       <c r="C504" s="7" t="n"/>
@@ -23334,7 +23328,7 @@
       <c r="J504" s="9" t="n"/>
       <c r="K504" s="9" t="n"/>
     </row>
-    <row r="505" ht="18" customHeight="1" s="125">
+    <row r="505" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A505" s="5" t="n"/>
       <c r="B505" s="6" t="n"/>
       <c r="C505" s="7" t="n"/>
@@ -23347,7 +23341,7 @@
       <c r="J505" s="9" t="n"/>
       <c r="K505" s="9" t="n"/>
     </row>
-    <row r="506" ht="18" customHeight="1" s="125">
+    <row r="506" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A506" s="5" t="n"/>
       <c r="B506" s="6" t="n"/>
       <c r="C506" s="7" t="n"/>
@@ -23360,7 +23354,7 @@
       <c r="J506" s="9" t="n"/>
       <c r="K506" s="9" t="n"/>
     </row>
-    <row r="507" ht="18" customHeight="1" s="125">
+    <row r="507" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A507" s="5" t="n"/>
       <c r="B507" s="6" t="n"/>
       <c r="C507" s="7" t="n"/>
@@ -23373,7 +23367,7 @@
       <c r="J507" s="9" t="n"/>
       <c r="K507" s="9" t="n"/>
     </row>
-    <row r="508" ht="18" customHeight="1" s="125">
+    <row r="508" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A508" s="5" t="n"/>
       <c r="B508" s="6" t="n"/>
       <c r="C508" s="7" t="n"/>
@@ -23386,7 +23380,7 @@
       <c r="J508" s="9" t="n"/>
       <c r="K508" s="9" t="n"/>
     </row>
-    <row r="509" ht="18" customHeight="1" s="125">
+    <row r="509" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A509" s="5" t="n"/>
       <c r="B509" s="6" t="n"/>
       <c r="C509" s="7" t="n"/>
@@ -23399,7 +23393,7 @@
       <c r="J509" s="9" t="n"/>
       <c r="K509" s="9" t="n"/>
     </row>
-    <row r="510" ht="18" customHeight="1" s="125">
+    <row r="510" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A510" s="5" t="n"/>
       <c r="B510" s="6" t="n"/>
       <c r="C510" s="7" t="n"/>
@@ -23412,7 +23406,7 @@
       <c r="J510" s="9" t="n"/>
       <c r="K510" s="9" t="n"/>
     </row>
-    <row r="511" ht="18" customHeight="1" s="125">
+    <row r="511" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A511" s="5" t="n"/>
       <c r="B511" s="6" t="n"/>
       <c r="C511" s="7" t="n"/>
@@ -23425,7 +23419,7 @@
       <c r="J511" s="9" t="n"/>
       <c r="K511" s="9" t="n"/>
     </row>
-    <row r="512" ht="18" customHeight="1" s="125">
+    <row r="512" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A512" s="5" t="n"/>
       <c r="B512" s="6" t="n"/>
       <c r="C512" s="7" t="n"/>
@@ -23438,7 +23432,7 @@
       <c r="J512" s="9" t="n"/>
       <c r="K512" s="9" t="n"/>
     </row>
-    <row r="513" ht="18" customHeight="1" s="125">
+    <row r="513" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A513" s="5" t="n"/>
       <c r="B513" s="6" t="n"/>
       <c r="C513" s="7" t="n"/>
@@ -23451,7 +23445,7 @@
       <c r="J513" s="9" t="n"/>
       <c r="K513" s="9" t="n"/>
     </row>
-    <row r="514" ht="18" customHeight="1" s="125">
+    <row r="514" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A514" s="5" t="n"/>
       <c r="B514" s="6" t="n"/>
       <c r="C514" s="7" t="n"/>
@@ -23464,7 +23458,7 @@
       <c r="J514" s="9" t="n"/>
       <c r="K514" s="9" t="n"/>
     </row>
-    <row r="515" ht="18" customHeight="1" s="125">
+    <row r="515" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A515" s="5" t="n"/>
       <c r="B515" s="6" t="n"/>
       <c r="C515" s="7" t="n"/>
@@ -23477,7 +23471,7 @@
       <c r="J515" s="9" t="n"/>
       <c r="K515" s="9" t="n"/>
     </row>
-    <row r="516" ht="18" customHeight="1" s="125">
+    <row r="516" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A516" s="5" t="n"/>
       <c r="B516" s="6" t="n"/>
       <c r="C516" s="7" t="n"/>
@@ -23490,7 +23484,7 @@
       <c r="J516" s="9" t="n"/>
       <c r="K516" s="9" t="n"/>
     </row>
-    <row r="517" ht="18" customHeight="1" s="125">
+    <row r="517" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A517" s="5" t="n"/>
       <c r="B517" s="6" t="n"/>
       <c r="C517" s="7" t="n"/>
@@ -23503,7 +23497,7 @@
       <c r="J517" s="9" t="n"/>
       <c r="K517" s="9" t="n"/>
     </row>
-    <row r="518" ht="18" customHeight="1" s="125">
+    <row r="518" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A518" s="5" t="n"/>
       <c r="B518" s="6" t="n"/>
       <c r="C518" s="7" t="n"/>
@@ -23516,7 +23510,7 @@
       <c r="J518" s="9" t="n"/>
       <c r="K518" s="9" t="n"/>
     </row>
-    <row r="519" ht="18" customHeight="1" s="125">
+    <row r="519" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A519" s="5" t="n"/>
       <c r="B519" s="6" t="n"/>
       <c r="C519" s="7" t="n"/>
@@ -23529,7 +23523,7 @@
       <c r="J519" s="9" t="n"/>
       <c r="K519" s="9" t="n"/>
     </row>
-    <row r="520" ht="18" customHeight="1" s="125">
+    <row r="520" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A520" s="5" t="n"/>
       <c r="B520" s="6" t="n"/>
       <c r="C520" s="7" t="n"/>
@@ -23542,7 +23536,7 @@
       <c r="J520" s="9" t="n"/>
       <c r="K520" s="9" t="n"/>
     </row>
-    <row r="521" ht="18" customHeight="1" s="125">
+    <row r="521" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A521" s="5" t="n"/>
       <c r="B521" s="6" t="n"/>
       <c r="C521" s="7" t="n"/>
@@ -23555,7 +23549,7 @@
       <c r="J521" s="9" t="n"/>
       <c r="K521" s="9" t="n"/>
     </row>
-    <row r="522" ht="18" customHeight="1" s="125">
+    <row r="522" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A522" s="5" t="n"/>
       <c r="B522" s="6" t="n"/>
       <c r="C522" s="7" t="n"/>
@@ -23568,7 +23562,7 @@
       <c r="J522" s="9" t="n"/>
       <c r="K522" s="9" t="n"/>
     </row>
-    <row r="523" ht="18" customHeight="1" s="125">
+    <row r="523" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A523" s="5" t="n"/>
       <c r="B523" s="6" t="n"/>
       <c r="C523" s="7" t="n"/>
@@ -23581,7 +23575,7 @@
       <c r="J523" s="9" t="n"/>
       <c r="K523" s="9" t="n"/>
     </row>
-    <row r="524" ht="18" customHeight="1" s="125">
+    <row r="524" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A524" s="5" t="n"/>
       <c r="B524" s="6" t="n"/>
       <c r="C524" s="7" t="n"/>
@@ -23594,7 +23588,7 @@
       <c r="J524" s="9" t="n"/>
       <c r="K524" s="9" t="n"/>
     </row>
-    <row r="525" ht="18" customHeight="1" s="125">
+    <row r="525" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A525" s="5" t="n"/>
       <c r="B525" s="6" t="n"/>
       <c r="C525" s="7" t="n"/>
@@ -23607,7 +23601,7 @@
       <c r="J525" s="9" t="n"/>
       <c r="K525" s="9" t="n"/>
     </row>
-    <row r="526" ht="18" customHeight="1" s="125">
+    <row r="526" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A526" s="5" t="n"/>
       <c r="B526" s="6" t="n"/>
       <c r="C526" s="7" t="n"/>
@@ -23620,7 +23614,7 @@
       <c r="J526" s="9" t="n"/>
       <c r="K526" s="9" t="n"/>
     </row>
-    <row r="527" ht="18" customHeight="1" s="125">
+    <row r="527" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A527" s="5" t="n"/>
       <c r="B527" s="6" t="n"/>
       <c r="C527" s="7" t="n"/>
@@ -23633,7 +23627,7 @@
       <c r="J527" s="9" t="n"/>
       <c r="K527" s="9" t="n"/>
     </row>
-    <row r="528" ht="18" customHeight="1" s="125">
+    <row r="528" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A528" s="5" t="n"/>
       <c r="B528" s="6" t="n"/>
       <c r="C528" s="7" t="n"/>
@@ -23646,7 +23640,7 @@
       <c r="J528" s="9" t="n"/>
       <c r="K528" s="9" t="n"/>
     </row>
-    <row r="529" ht="18" customHeight="1" s="125">
+    <row r="529" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A529" s="5" t="n"/>
       <c r="B529" s="6" t="n"/>
       <c r="C529" s="7" t="n"/>
@@ -23659,7 +23653,7 @@
       <c r="J529" s="9" t="n"/>
       <c r="K529" s="9" t="n"/>
     </row>
-    <row r="530" ht="18" customHeight="1" s="125">
+    <row r="530" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A530" s="5" t="n"/>
       <c r="B530" s="6" t="n"/>
       <c r="C530" s="7" t="n"/>
@@ -23672,7 +23666,7 @@
       <c r="J530" s="9" t="n"/>
       <c r="K530" s="9" t="n"/>
     </row>
-    <row r="531" ht="18" customHeight="1" s="125">
+    <row r="531" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A531" s="5" t="n"/>
       <c r="B531" s="6" t="n"/>
       <c r="C531" s="7" t="n"/>
@@ -23685,7 +23679,7 @@
       <c r="J531" s="9" t="n"/>
       <c r="K531" s="9" t="n"/>
     </row>
-    <row r="532" ht="18" customHeight="1" s="125">
+    <row r="532" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A532" s="5" t="n"/>
       <c r="B532" s="6" t="n"/>
       <c r="C532" s="7" t="n"/>
@@ -23698,7 +23692,7 @@
       <c r="J532" s="9" t="n"/>
       <c r="K532" s="9" t="n"/>
     </row>
-    <row r="533" ht="18" customHeight="1" s="125">
+    <row r="533" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A533" s="5" t="n"/>
       <c r="B533" s="6" t="n"/>
       <c r="C533" s="7" t="n"/>
@@ -23711,7 +23705,7 @@
       <c r="J533" s="9" t="n"/>
       <c r="K533" s="9" t="n"/>
     </row>
-    <row r="534" ht="18" customHeight="1" s="125">
+    <row r="534" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A534" s="5" t="n"/>
       <c r="B534" s="6" t="n"/>
       <c r="C534" s="7" t="n"/>
@@ -23724,7 +23718,7 @@
       <c r="J534" s="9" t="n"/>
       <c r="K534" s="9" t="n"/>
     </row>
-    <row r="535" ht="18" customHeight="1" s="125">
+    <row r="535" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A535" s="5" t="n"/>
       <c r="B535" s="6" t="n"/>
       <c r="C535" s="7" t="n"/>
@@ -23737,7 +23731,7 @@
       <c r="J535" s="9" t="n"/>
       <c r="K535" s="9" t="n"/>
     </row>
-    <row r="536" ht="18" customHeight="1" s="125">
+    <row r="536" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A536" s="5" t="n"/>
       <c r="B536" s="6" t="n"/>
       <c r="C536" s="7" t="n"/>
@@ -23750,7 +23744,7 @@
       <c r="J536" s="9" t="n"/>
       <c r="K536" s="9" t="n"/>
     </row>
-    <row r="537" ht="18" customHeight="1" s="125">
+    <row r="537" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A537" s="5" t="n"/>
       <c r="B537" s="6" t="n"/>
       <c r="C537" s="7" t="n"/>
@@ -23763,7 +23757,7 @@
       <c r="J537" s="9" t="n"/>
       <c r="K537" s="9" t="n"/>
     </row>
-    <row r="538" ht="18" customHeight="1" s="125">
+    <row r="538" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A538" s="5" t="n"/>
       <c r="B538" s="6" t="n"/>
       <c r="C538" s="7" t="n"/>
@@ -23776,7 +23770,7 @@
       <c r="J538" s="9" t="n"/>
       <c r="K538" s="9" t="n"/>
     </row>
-    <row r="539" ht="18" customHeight="1" s="125">
+    <row r="539" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A539" s="5" t="n"/>
       <c r="B539" s="6" t="n"/>
       <c r="C539" s="7" t="n"/>
@@ -23789,7 +23783,7 @@
       <c r="J539" s="9" t="n"/>
       <c r="K539" s="9" t="n"/>
     </row>
-    <row r="540" ht="18" customHeight="1" s="125">
+    <row r="540" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A540" s="5" t="n"/>
       <c r="B540" s="6" t="n"/>
       <c r="C540" s="7" t="n"/>
@@ -23802,7 +23796,7 @@
       <c r="J540" s="9" t="n"/>
       <c r="K540" s="9" t="n"/>
     </row>
-    <row r="541" ht="18" customHeight="1" s="125">
+    <row r="541" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A541" s="5" t="n"/>
       <c r="B541" s="6" t="n"/>
       <c r="C541" s="7" t="n"/>
@@ -23815,7 +23809,7 @@
       <c r="J541" s="9" t="n"/>
       <c r="K541" s="9" t="n"/>
     </row>
-    <row r="542" ht="18" customHeight="1" s="125">
+    <row r="542" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A542" s="5" t="n"/>
       <c r="B542" s="6" t="n"/>
       <c r="C542" s="7" t="n"/>
@@ -23828,7 +23822,7 @@
       <c r="J542" s="9" t="n"/>
       <c r="K542" s="9" t="n"/>
     </row>
-    <row r="543" ht="18" customHeight="1" s="125">
+    <row r="543" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A543" s="5" t="n"/>
       <c r="B543" s="6" t="n"/>
       <c r="C543" s="7" t="n"/>
@@ -23841,7 +23835,7 @@
       <c r="J543" s="9" t="n"/>
       <c r="K543" s="9" t="n"/>
     </row>
-    <row r="544" ht="18" customHeight="1" s="125">
+    <row r="544" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A544" s="5" t="n"/>
       <c r="B544" s="6" t="n"/>
       <c r="C544" s="7" t="n"/>
@@ -23854,7 +23848,7 @@
       <c r="J544" s="9" t="n"/>
       <c r="K544" s="9" t="n"/>
     </row>
-    <row r="545" ht="18" customHeight="1" s="125">
+    <row r="545" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A545" s="5" t="n"/>
       <c r="B545" s="6" t="n"/>
       <c r="C545" s="7" t="n"/>
@@ -23867,7 +23861,7 @@
       <c r="J545" s="9" t="n"/>
       <c r="K545" s="9" t="n"/>
     </row>
-    <row r="546" ht="18" customHeight="1" s="125">
+    <row r="546" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A546" s="5" t="n"/>
       <c r="B546" s="6" t="n"/>
       <c r="C546" s="7" t="n"/>
@@ -23880,7 +23874,7 @@
       <c r="J546" s="9" t="n"/>
       <c r="K546" s="9" t="n"/>
     </row>
-    <row r="547" ht="18" customHeight="1" s="125">
+    <row r="547" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A547" s="5" t="n"/>
       <c r="B547" s="6" t="n"/>
       <c r="C547" s="7" t="n"/>
@@ -23893,7 +23887,7 @@
       <c r="J547" s="9" t="n"/>
       <c r="K547" s="9" t="n"/>
     </row>
-    <row r="548" ht="18" customHeight="1" s="125">
+    <row r="548" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A548" s="5" t="n"/>
       <c r="B548" s="6" t="n"/>
       <c r="C548" s="7" t="n"/>
@@ -23906,7 +23900,7 @@
       <c r="J548" s="9" t="n"/>
       <c r="K548" s="9" t="n"/>
     </row>
-    <row r="549" ht="18" customHeight="1" s="125">
+    <row r="549" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A549" s="5" t="n"/>
       <c r="B549" s="6" t="n"/>
       <c r="C549" s="7" t="n"/>
@@ -23919,7 +23913,7 @@
       <c r="J549" s="9" t="n"/>
       <c r="K549" s="9" t="n"/>
     </row>
-    <row r="550" ht="18" customHeight="1" s="125">
+    <row r="550" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A550" s="5" t="n"/>
       <c r="B550" s="6" t="n"/>
       <c r="C550" s="7" t="n"/>
@@ -23932,7 +23926,7 @@
       <c r="J550" s="9" t="n"/>
       <c r="K550" s="9" t="n"/>
     </row>
-    <row r="551" ht="18" customHeight="1" s="125">
+    <row r="551" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A551" s="5" t="n"/>
       <c r="B551" s="6" t="n"/>
       <c r="C551" s="7" t="n"/>
@@ -23945,7 +23939,7 @@
       <c r="J551" s="9" t="n"/>
       <c r="K551" s="9" t="n"/>
     </row>
-    <row r="552" ht="18" customHeight="1" s="125">
+    <row r="552" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A552" s="5" t="n"/>
       <c r="B552" s="6" t="n"/>
       <c r="C552" s="7" t="n"/>
@@ -23958,7 +23952,7 @@
       <c r="J552" s="9" t="n"/>
       <c r="K552" s="9" t="n"/>
     </row>
-    <row r="553" ht="18" customHeight="1" s="125">
+    <row r="553" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A553" s="5" t="n"/>
       <c r="B553" s="6" t="n"/>
       <c r="C553" s="7" t="n"/>
@@ -23971,7 +23965,7 @@
       <c r="J553" s="9" t="n"/>
       <c r="K553" s="9" t="n"/>
     </row>
-    <row r="554" ht="18" customHeight="1" s="125">
+    <row r="554" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A554" s="5" t="n"/>
       <c r="B554" s="6" t="n"/>
       <c r="C554" s="7" t="n"/>
@@ -23984,7 +23978,7 @@
       <c r="J554" s="9" t="n"/>
       <c r="K554" s="9" t="n"/>
     </row>
-    <row r="555" ht="18" customHeight="1" s="125">
+    <row r="555" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A555" s="5" t="n"/>
       <c r="B555" s="6" t="n"/>
       <c r="C555" s="7" t="n"/>
@@ -23997,7 +23991,7 @@
       <c r="J555" s="9" t="n"/>
       <c r="K555" s="9" t="n"/>
     </row>
-    <row r="556" ht="18" customHeight="1" s="125">
+    <row r="556" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A556" s="5" t="n"/>
       <c r="B556" s="6" t="n"/>
       <c r="C556" s="7" t="n"/>
@@ -24010,7 +24004,7 @@
       <c r="J556" s="9" t="n"/>
       <c r="K556" s="9" t="n"/>
     </row>
-    <row r="557" ht="18" customHeight="1" s="125">
+    <row r="557" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A557" s="5" t="n"/>
       <c r="B557" s="6" t="n"/>
       <c r="C557" s="7" t="n"/>
@@ -24023,7 +24017,7 @@
       <c r="J557" s="9" t="n"/>
       <c r="K557" s="9" t="n"/>
     </row>
-    <row r="558" ht="18" customHeight="1" s="125">
+    <row r="558" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A558" s="5" t="n"/>
       <c r="B558" s="6" t="n"/>
       <c r="C558" s="7" t="n"/>
@@ -24036,7 +24030,7 @@
       <c r="J558" s="9" t="n"/>
       <c r="K558" s="9" t="n"/>
     </row>
-    <row r="559" ht="18" customHeight="1" s="125">
+    <row r="559" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A559" s="5" t="n"/>
       <c r="B559" s="6" t="n"/>
       <c r="C559" s="7" t="n"/>
@@ -24049,7 +24043,7 @@
       <c r="J559" s="9" t="n"/>
       <c r="K559" s="9" t="n"/>
     </row>
-    <row r="560" ht="18" customHeight="1" s="125">
+    <row r="560" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A560" s="5" t="n"/>
       <c r="B560" s="6" t="n"/>
       <c r="C560" s="7" t="n"/>
@@ -24062,7 +24056,7 @@
       <c r="J560" s="9" t="n"/>
       <c r="K560" s="9" t="n"/>
     </row>
-    <row r="561" ht="18" customHeight="1" s="125">
+    <row r="561" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A561" s="5" t="n"/>
       <c r="B561" s="6" t="n"/>
       <c r="C561" s="7" t="n"/>
@@ -24075,7 +24069,7 @@
       <c r="J561" s="9" t="n"/>
       <c r="K561" s="9" t="n"/>
     </row>
-    <row r="562" ht="18" customHeight="1" s="125">
+    <row r="562" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A562" s="5" t="n"/>
       <c r="B562" s="6" t="n"/>
       <c r="C562" s="7" t="n"/>
@@ -24088,7 +24082,7 @@
       <c r="J562" s="9" t="n"/>
       <c r="K562" s="9" t="n"/>
     </row>
-    <row r="563" ht="18" customHeight="1" s="125">
+    <row r="563" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A563" s="5" t="n"/>
       <c r="B563" s="6" t="n"/>
       <c r="C563" s="7" t="n"/>
@@ -24101,7 +24095,7 @@
       <c r="J563" s="9" t="n"/>
       <c r="K563" s="9" t="n"/>
     </row>
-    <row r="564" ht="18" customHeight="1" s="125">
+    <row r="564" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A564" s="5" t="n"/>
       <c r="B564" s="6" t="n"/>
       <c r="C564" s="7" t="n"/>
@@ -24114,7 +24108,7 @@
       <c r="J564" s="9" t="n"/>
       <c r="K564" s="9" t="n"/>
     </row>
-    <row r="565" ht="18" customHeight="1" s="125">
+    <row r="565" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A565" s="5" t="n"/>
       <c r="B565" s="6" t="n"/>
       <c r="C565" s="7" t="n"/>
@@ -24127,7 +24121,7 @@
       <c r="J565" s="9" t="n"/>
       <c r="K565" s="9" t="n"/>
     </row>
-    <row r="566" ht="18" customHeight="1" s="125">
+    <row r="566" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A566" s="5" t="n"/>
       <c r="B566" s="63" t="n"/>
       <c r="C566" s="7" t="n"/>
@@ -24140,7 +24134,7 @@
       <c r="J566" s="9" t="n"/>
       <c r="K566" s="9" t="n"/>
     </row>
-    <row r="567" ht="18" customHeight="1" s="125">
+    <row r="567" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A567" s="5" t="n"/>
       <c r="B567" s="6" t="n"/>
       <c r="C567" s="7" t="n"/>
@@ -24153,7 +24147,7 @@
       <c r="J567" s="9" t="n"/>
       <c r="K567" s="9" t="n"/>
     </row>
-    <row r="568" ht="18" customHeight="1" s="125">
+    <row r="568" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A568" s="5" t="n"/>
       <c r="B568" s="6" t="n"/>
       <c r="C568" s="7" t="n"/>
@@ -24166,7 +24160,7 @@
       <c r="J568" s="9" t="n"/>
       <c r="K568" s="9" t="n"/>
     </row>
-    <row r="569" ht="18" customHeight="1" s="125">
+    <row r="569" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A569" s="5" t="n"/>
       <c r="B569" s="6" t="n"/>
       <c r="C569" s="7" t="n"/>
@@ -24179,7 +24173,7 @@
       <c r="J569" s="9" t="n"/>
       <c r="K569" s="9" t="n"/>
     </row>
-    <row r="570" ht="18" customHeight="1" s="125">
+    <row r="570" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A570" s="5" t="n"/>
       <c r="B570" s="6" t="n"/>
       <c r="C570" s="7" t="n"/>
@@ -24192,7 +24186,7 @@
       <c r="J570" s="9" t="n"/>
       <c r="K570" s="9" t="n"/>
     </row>
-    <row r="571" ht="18" customHeight="1" s="125">
+    <row r="571" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A571" s="5" t="n"/>
       <c r="B571" s="6" t="n"/>
       <c r="C571" s="7" t="n"/>
@@ -24205,7 +24199,7 @@
       <c r="J571" s="9" t="n"/>
       <c r="K571" s="9" t="n"/>
     </row>
-    <row r="572" ht="18" customHeight="1" s="125">
+    <row r="572" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A572" s="5" t="n"/>
       <c r="B572" s="6" t="n"/>
       <c r="C572" s="7" t="n"/>
@@ -24218,7 +24212,7 @@
       <c r="J572" s="9" t="n"/>
       <c r="K572" s="9" t="n"/>
     </row>
-    <row r="573" ht="18" customHeight="1" s="125">
+    <row r="573" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A573" s="5" t="n"/>
       <c r="B573" s="6" t="n"/>
       <c r="C573" s="7" t="n"/>
@@ -24231,7 +24225,7 @@
       <c r="J573" s="9" t="n"/>
       <c r="K573" s="9" t="n"/>
     </row>
-    <row r="574" ht="18" customHeight="1" s="125">
+    <row r="574" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A574" s="5" t="n"/>
       <c r="B574" s="6" t="n"/>
       <c r="C574" s="7" t="n"/>
@@ -24244,7 +24238,7 @@
       <c r="J574" s="9" t="n"/>
       <c r="K574" s="9" t="n"/>
     </row>
-    <row r="575" ht="18" customHeight="1" s="125">
+    <row r="575" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A575" s="5" t="n"/>
       <c r="B575" s="6" t="n"/>
       <c r="C575" s="7" t="n"/>
@@ -24257,7 +24251,7 @@
       <c r="J575" s="9" t="n"/>
       <c r="K575" s="9" t="n"/>
     </row>
-    <row r="576" ht="18" customHeight="1" s="125">
+    <row r="576" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A576" s="5" t="n"/>
       <c r="B576" s="6" t="n"/>
       <c r="C576" s="7" t="n"/>
@@ -24270,7 +24264,7 @@
       <c r="J576" s="9" t="n"/>
       <c r="K576" s="9" t="n"/>
     </row>
-    <row r="577" ht="18" customHeight="1" s="125">
+    <row r="577" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A577" s="5" t="n"/>
       <c r="B577" s="6" t="n"/>
       <c r="C577" s="7" t="n"/>
@@ -24283,7 +24277,7 @@
       <c r="J577" s="9" t="n"/>
       <c r="K577" s="9" t="n"/>
     </row>
-    <row r="578" ht="18" customHeight="1" s="125">
+    <row r="578" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A578" s="5" t="n"/>
       <c r="B578" s="6" t="n"/>
       <c r="C578" s="7" t="n"/>
@@ -24296,7 +24290,7 @@
       <c r="J578" s="9" t="n"/>
       <c r="K578" s="9" t="n"/>
     </row>
-    <row r="579" ht="18" customHeight="1" s="125">
+    <row r="579" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A579" s="5" t="n"/>
       <c r="B579" s="6" t="n"/>
       <c r="C579" s="7" t="n"/>
@@ -24309,7 +24303,7 @@
       <c r="J579" s="9" t="n"/>
       <c r="K579" s="9" t="n"/>
     </row>
-    <row r="580" ht="18" customHeight="1" s="125">
+    <row r="580" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A580" s="5" t="n"/>
       <c r="B580" s="6" t="n"/>
       <c r="C580" s="7" t="n"/>
@@ -24322,7 +24316,7 @@
       <c r="J580" s="9" t="n"/>
       <c r="K580" s="9" t="n"/>
     </row>
-    <row r="581" ht="18" customHeight="1" s="125">
+    <row r="581" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A581" s="5" t="n"/>
       <c r="B581" s="6" t="n"/>
       <c r="C581" s="7" t="n"/>
@@ -24335,7 +24329,7 @@
       <c r="J581" s="9" t="n"/>
       <c r="K581" s="9" t="n"/>
     </row>
-    <row r="582" ht="18" customHeight="1" s="125">
+    <row r="582" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A582" s="5" t="n"/>
       <c r="B582" s="6" t="n"/>
       <c r="C582" s="7" t="n"/>
@@ -24348,7 +24342,7 @@
       <c r="J582" s="9" t="n"/>
       <c r="K582" s="9" t="n"/>
     </row>
-    <row r="583" ht="18" customHeight="1" s="125">
+    <row r="583" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A583" s="5" t="n"/>
       <c r="B583" s="6" t="n"/>
       <c r="C583" s="7" t="n"/>
@@ -24361,7 +24355,7 @@
       <c r="J583" s="9" t="n"/>
       <c r="K583" s="9" t="n"/>
     </row>
-    <row r="584" ht="18" customHeight="1" s="125">
+    <row r="584" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A584" s="5" t="n"/>
       <c r="B584" s="6" t="n"/>
       <c r="C584" s="7" t="n"/>
@@ -24374,7 +24368,7 @@
       <c r="J584" s="9" t="n"/>
       <c r="K584" s="9" t="n"/>
     </row>
-    <row r="585" ht="18" customHeight="1" s="125">
+    <row r="585" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A585" s="5" t="n"/>
       <c r="B585" s="6" t="n"/>
       <c r="C585" s="7" t="n"/>
@@ -24387,7 +24381,7 @@
       <c r="J585" s="9" t="n"/>
       <c r="K585" s="9" t="n"/>
     </row>
-    <row r="586" ht="18" customHeight="1" s="125">
+    <row r="586" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A586" s="5" t="n"/>
       <c r="B586" s="6" t="n"/>
       <c r="C586" s="7" t="n"/>
@@ -24400,7 +24394,7 @@
       <c r="J586" s="9" t="n"/>
       <c r="K586" s="9" t="n"/>
     </row>
-    <row r="587" ht="18" customHeight="1" s="125">
+    <row r="587" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A587" s="5" t="n"/>
       <c r="B587" s="6" t="n"/>
       <c r="C587" s="7" t="n"/>
@@ -24413,7 +24407,7 @@
       <c r="J587" s="9" t="n"/>
       <c r="K587" s="9" t="n"/>
     </row>
-    <row r="588" ht="18" customHeight="1" s="125">
+    <row r="588" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A588" s="5" t="n"/>
       <c r="B588" s="6" t="n"/>
       <c r="C588" s="7" t="n"/>
@@ -24426,7 +24420,7 @@
       <c r="J588" s="9" t="n"/>
       <c r="K588" s="9" t="n"/>
     </row>
-    <row r="589" ht="18" customHeight="1" s="125">
+    <row r="589" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A589" s="5" t="n"/>
       <c r="B589" s="6" t="n"/>
       <c r="C589" s="7" t="n"/>
@@ -24439,7 +24433,7 @@
       <c r="J589" s="9" t="n"/>
       <c r="K589" s="9" t="n"/>
     </row>
-    <row r="590" ht="18" customHeight="1" s="125">
+    <row r="590" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A590" s="5" t="n"/>
       <c r="B590" s="6" t="n"/>
       <c r="C590" s="7" t="n"/>
@@ -24452,7 +24446,7 @@
       <c r="J590" s="9" t="n"/>
       <c r="K590" s="9" t="n"/>
     </row>
-    <row r="591" ht="18" customHeight="1" s="125">
+    <row r="591" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A591" s="5" t="n"/>
       <c r="B591" s="6" t="n"/>
       <c r="C591" s="7" t="n"/>
@@ -24465,7 +24459,7 @@
       <c r="J591" s="9" t="n"/>
       <c r="K591" s="9" t="n"/>
     </row>
-    <row r="592" ht="18" customHeight="1" s="125">
+    <row r="592" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A592" s="5" t="n"/>
       <c r="B592" s="6" t="n"/>
       <c r="C592" s="7" t="n"/>
@@ -24478,7 +24472,7 @@
       <c r="J592" s="9" t="n"/>
       <c r="K592" s="9" t="n"/>
     </row>
-    <row r="593" ht="18" customHeight="1" s="125">
+    <row r="593" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A593" s="5" t="n"/>
       <c r="B593" s="6" t="n"/>
       <c r="C593" s="7" t="n"/>
@@ -24491,7 +24485,7 @@
       <c r="J593" s="9" t="n"/>
       <c r="K593" s="9" t="n"/>
     </row>
-    <row r="594" ht="18" customHeight="1" s="125">
+    <row r="594" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A594" s="5" t="n"/>
       <c r="B594" s="6" t="n"/>
       <c r="C594" s="7" t="n"/>
@@ -24504,7 +24498,7 @@
       <c r="J594" s="9" t="n"/>
       <c r="K594" s="9" t="n"/>
     </row>
-    <row r="595" ht="18" customHeight="1" s="125">
+    <row r="595" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A595" s="5" t="n"/>
       <c r="B595" s="6" t="n"/>
       <c r="C595" s="7" t="n"/>
@@ -24517,7 +24511,7 @@
       <c r="J595" s="9" t="n"/>
       <c r="K595" s="9" t="n"/>
     </row>
-    <row r="596" ht="18" customHeight="1" s="125">
+    <row r="596" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A596" s="5" t="n"/>
       <c r="B596" s="6" t="n"/>
       <c r="C596" s="7" t="n"/>
@@ -24530,7 +24524,7 @@
       <c r="J596" s="9" t="n"/>
       <c r="K596" s="9" t="n"/>
     </row>
-    <row r="597" ht="18" customHeight="1" s="125">
+    <row r="597" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A597" s="5" t="n"/>
       <c r="B597" s="6" t="n"/>
       <c r="C597" s="7" t="n"/>
@@ -24543,7 +24537,7 @@
       <c r="J597" s="9" t="n"/>
       <c r="K597" s="9" t="n"/>
     </row>
-    <row r="598" ht="18" customHeight="1" s="125">
+    <row r="598" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A598" s="5" t="n"/>
       <c r="B598" s="6" t="n"/>
       <c r="C598" s="7" t="n"/>
@@ -24556,7 +24550,7 @@
       <c r="J598" s="9" t="n"/>
       <c r="K598" s="9" t="n"/>
     </row>
-    <row r="599" ht="18" customHeight="1" s="125">
+    <row r="599" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A599" s="5" t="n"/>
       <c r="B599" s="6" t="n"/>
       <c r="C599" s="7" t="n"/>
@@ -24569,7 +24563,7 @@
       <c r="J599" s="9" t="n"/>
       <c r="K599" s="9" t="n"/>
     </row>
-    <row r="600" ht="18" customHeight="1" s="125">
+    <row r="600" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A600" s="5" t="n"/>
       <c r="B600" s="6" t="n"/>
       <c r="C600" s="7" t="n"/>
@@ -24582,7 +24576,7 @@
       <c r="J600" s="9" t="n"/>
       <c r="K600" s="9" t="n"/>
     </row>
-    <row r="601" ht="18" customHeight="1" s="125">
+    <row r="601" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A601" s="5" t="n"/>
       <c r="B601" s="6" t="n"/>
       <c r="C601" s="7" t="n"/>
@@ -24595,7 +24589,7 @@
       <c r="J601" s="9" t="n"/>
       <c r="K601" s="9" t="n"/>
     </row>
-    <row r="602" ht="18" customHeight="1" s="125">
+    <row r="602" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A602" s="5" t="n"/>
       <c r="B602" s="6" t="n"/>
       <c r="C602" s="7" t="n"/>
@@ -24608,7 +24602,7 @@
       <c r="J602" s="9" t="n"/>
       <c r="K602" s="9" t="n"/>
     </row>
-    <row r="603" ht="18" customHeight="1" s="125">
+    <row r="603" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A603" s="5" t="n"/>
       <c r="B603" s="6" t="n"/>
       <c r="C603" s="7" t="n"/>
@@ -24621,7 +24615,7 @@
       <c r="J603" s="9" t="n"/>
       <c r="K603" s="9" t="n"/>
     </row>
-    <row r="604" ht="18" customHeight="1" s="125">
+    <row r="604" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A604" s="5" t="n"/>
       <c r="B604" s="6" t="n"/>
       <c r="C604" s="7" t="n"/>
@@ -24634,7 +24628,7 @@
       <c r="J604" s="9" t="n"/>
       <c r="K604" s="9" t="n"/>
     </row>
-    <row r="605" ht="18" customHeight="1" s="125">
+    <row r="605" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A605" s="5" t="n"/>
       <c r="B605" s="6" t="n"/>
       <c r="C605" s="7" t="n"/>
@@ -24647,7 +24641,7 @@
       <c r="J605" s="9" t="n"/>
       <c r="K605" s="9" t="n"/>
     </row>
-    <row r="606" ht="18" customHeight="1" s="125">
+    <row r="606" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A606" s="5" t="n"/>
       <c r="B606" s="6" t="n"/>
       <c r="C606" s="7" t="n"/>
@@ -24660,7 +24654,7 @@
       <c r="J606" s="9" t="n"/>
       <c r="K606" s="9" t="n"/>
     </row>
-    <row r="607" ht="18" customHeight="1" s="125">
+    <row r="607" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A607" s="5" t="n"/>
       <c r="B607" s="6" t="n"/>
       <c r="C607" s="7" t="n"/>
@@ -24673,7 +24667,7 @@
       <c r="J607" s="9" t="n"/>
       <c r="K607" s="9" t="n"/>
     </row>
-    <row r="608" ht="18" customHeight="1" s="125">
+    <row r="608" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A608" s="5" t="n"/>
       <c r="B608" s="6" t="n"/>
       <c r="C608" s="7" t="n"/>
@@ -24686,7 +24680,7 @@
       <c r="J608" s="9" t="n"/>
       <c r="K608" s="9" t="n"/>
     </row>
-    <row r="609" ht="18" customHeight="1" s="125">
+    <row r="609" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A609" s="5" t="n"/>
       <c r="B609" s="6" t="n"/>
       <c r="C609" s="7" t="n"/>
@@ -24699,7 +24693,7 @@
       <c r="J609" s="9" t="n"/>
       <c r="K609" s="9" t="n"/>
     </row>
-    <row r="610" ht="18" customHeight="1" s="125">
+    <row r="610" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A610" s="5" t="n"/>
       <c r="B610" s="6" t="n"/>
       <c r="C610" s="7" t="n"/>
@@ -24712,7 +24706,7 @@
       <c r="J610" s="9" t="n"/>
       <c r="K610" s="9" t="n"/>
     </row>
-    <row r="611" ht="18" customHeight="1" s="125">
+    <row r="611" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A611" s="5" t="n"/>
       <c r="B611" s="6" t="n"/>
       <c r="C611" s="7" t="n"/>
@@ -24725,7 +24719,7 @@
       <c r="J611" s="9" t="n"/>
       <c r="K611" s="9" t="n"/>
     </row>
-    <row r="612" ht="18" customHeight="1" s="125">
+    <row r="612" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A612" s="5" t="n"/>
       <c r="B612" s="6" t="n"/>
       <c r="C612" s="7" t="n"/>
@@ -24738,7 +24732,7 @@
       <c r="J612" s="9" t="n"/>
       <c r="K612" s="9" t="n"/>
     </row>
-    <row r="613" ht="18" customHeight="1" s="125">
+    <row r="613" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A613" s="5" t="n"/>
       <c r="B613" s="6" t="n"/>
       <c r="C613" s="7" t="n"/>
@@ -24751,7 +24745,7 @@
       <c r="J613" s="9" t="n"/>
       <c r="K613" s="9" t="n"/>
     </row>
-    <row r="614" ht="18" customHeight="1" s="125">
+    <row r="614" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A614" s="5" t="n"/>
       <c r="B614" s="6" t="n"/>
       <c r="C614" s="7" t="n"/>
@@ -24764,7 +24758,7 @@
       <c r="J614" s="9" t="n"/>
       <c r="K614" s="9" t="n"/>
     </row>
-    <row r="615" ht="18" customHeight="1" s="125">
+    <row r="615" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A615" s="5" t="n"/>
       <c r="B615" s="6" t="n"/>
       <c r="C615" s="7" t="n"/>
@@ -24777,7 +24771,7 @@
       <c r="J615" s="9" t="n"/>
       <c r="K615" s="9" t="n"/>
     </row>
-    <row r="616" ht="18" customHeight="1" s="125">
+    <row r="616" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A616" s="5" t="n"/>
       <c r="B616" s="6" t="n"/>
       <c r="C616" s="7" t="n"/>
@@ -24790,7 +24784,7 @@
       <c r="J616" s="9" t="n"/>
       <c r="K616" s="9" t="n"/>
     </row>
-    <row r="617" ht="18" customHeight="1" s="125">
+    <row r="617" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A617" s="5" t="n"/>
       <c r="B617" s="6" t="n"/>
       <c r="C617" s="7" t="n"/>
@@ -24803,7 +24797,7 @@
       <c r="J617" s="9" t="n"/>
       <c r="K617" s="9" t="n"/>
     </row>
-    <row r="618" ht="18" customHeight="1" s="125">
+    <row r="618" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A618" s="5" t="n"/>
       <c r="B618" s="6" t="n"/>
       <c r="C618" s="7" t="n"/>
@@ -24816,7 +24810,7 @@
       <c r="J618" s="9" t="n"/>
       <c r="K618" s="9" t="n"/>
     </row>
-    <row r="619" ht="18" customHeight="1" s="125">
+    <row r="619" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A619" s="5" t="n"/>
       <c r="B619" s="6" t="n"/>
       <c r="C619" s="7" t="n"/>
@@ -24829,7 +24823,7 @@
       <c r="J619" s="9" t="n"/>
       <c r="K619" s="9" t="n"/>
     </row>
-    <row r="620" ht="18" customHeight="1" s="125">
+    <row r="620" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A620" s="5" t="n"/>
       <c r="B620" s="6" t="n"/>
       <c r="C620" s="7" t="n"/>
@@ -24842,7 +24836,7 @@
       <c r="J620" s="9" t="n"/>
       <c r="K620" s="9" t="n"/>
     </row>
-    <row r="621" ht="18" customHeight="1" s="125">
+    <row r="621" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A621" s="5" t="n"/>
       <c r="B621" s="6" t="n"/>
       <c r="C621" s="7" t="n"/>
@@ -24855,7 +24849,7 @@
       <c r="J621" s="9" t="n"/>
       <c r="K621" s="9" t="n"/>
     </row>
-    <row r="622" ht="18" customHeight="1" s="125">
+    <row r="622" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A622" s="5" t="n"/>
       <c r="B622" s="6" t="n"/>
       <c r="C622" s="7" t="n"/>
@@ -24868,7 +24862,7 @@
       <c r="J622" s="9" t="n"/>
       <c r="K622" s="9" t="n"/>
     </row>
-    <row r="623" ht="18" customHeight="1" s="125">
+    <row r="623" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A623" s="5" t="n"/>
       <c r="B623" s="6" t="n"/>
       <c r="C623" s="7" t="n"/>
@@ -24881,7 +24875,7 @@
       <c r="J623" s="9" t="n"/>
       <c r="K623" s="9" t="n"/>
     </row>
-    <row r="624" ht="18" customHeight="1" s="125">
+    <row r="624" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A624" s="5" t="n"/>
       <c r="B624" s="6" t="n"/>
       <c r="C624" s="7" t="n"/>
@@ -24894,7 +24888,7 @@
       <c r="J624" s="9" t="n"/>
       <c r="K624" s="9" t="n"/>
     </row>
-    <row r="625" ht="18" customHeight="1" s="125">
+    <row r="625" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A625" s="5" t="n"/>
       <c r="B625" s="6" t="n"/>
       <c r="C625" s="7" t="n"/>
@@ -24907,7 +24901,7 @@
       <c r="J625" s="9" t="n"/>
       <c r="K625" s="9" t="n"/>
     </row>
-    <row r="626" ht="18" customHeight="1" s="125">
+    <row r="626" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A626" s="5" t="n"/>
       <c r="B626" s="6" t="n"/>
       <c r="C626" s="7" t="n"/>
@@ -24920,7 +24914,7 @@
       <c r="J626" s="9" t="n"/>
       <c r="K626" s="9" t="n"/>
     </row>
-    <row r="627" ht="18" customHeight="1" s="125">
+    <row r="627" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A627" s="5" t="n"/>
       <c r="B627" s="6" t="n"/>
       <c r="C627" s="7" t="n"/>
@@ -24933,7 +24927,7 @@
       <c r="J627" s="9" t="n"/>
       <c r="K627" s="9" t="n"/>
     </row>
-    <row r="628" ht="18" customHeight="1" s="125">
+    <row r="628" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A628" s="5" t="n"/>
       <c r="B628" s="6" t="n"/>
       <c r="C628" s="7" t="n"/>
@@ -24946,7 +24940,7 @@
       <c r="J628" s="9" t="n"/>
       <c r="K628" s="9" t="n"/>
     </row>
-    <row r="629" ht="18" customHeight="1" s="125">
+    <row r="629" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A629" s="5" t="n"/>
       <c r="B629" s="6" t="n"/>
       <c r="C629" s="7" t="n"/>
@@ -24959,7 +24953,7 @@
       <c r="J629" s="9" t="n"/>
       <c r="K629" s="9" t="n"/>
     </row>
-    <row r="630" ht="18" customHeight="1" s="125">
+    <row r="630" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A630" s="5" t="n"/>
       <c r="B630" s="6" t="n"/>
       <c r="C630" s="7" t="n"/>
@@ -24972,7 +24966,7 @@
       <c r="J630" s="9" t="n"/>
       <c r="K630" s="9" t="n"/>
     </row>
-    <row r="631" ht="18" customHeight="1" s="125">
+    <row r="631" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A631" s="5" t="n"/>
       <c r="B631" s="6" t="n"/>
       <c r="C631" s="7" t="n"/>
@@ -24985,7 +24979,7 @@
       <c r="J631" s="9" t="n"/>
       <c r="K631" s="9" t="n"/>
     </row>
-    <row r="632" ht="18" customHeight="1" s="125">
+    <row r="632" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A632" s="5" t="n"/>
       <c r="B632" s="6" t="n"/>
       <c r="C632" s="7" t="n"/>
@@ -24998,7 +24992,7 @@
       <c r="J632" s="9" t="n"/>
       <c r="K632" s="9" t="n"/>
     </row>
-    <row r="633" ht="18" customHeight="1" s="125">
+    <row r="633" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A633" s="5" t="n"/>
       <c r="B633" s="6" t="n"/>
       <c r="C633" s="7" t="n"/>
@@ -25011,7 +25005,7 @@
       <c r="J633" s="9" t="n"/>
       <c r="K633" s="9" t="n"/>
     </row>
-    <row r="634" ht="18" customHeight="1" s="125">
+    <row r="634" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A634" s="5" t="n"/>
       <c r="B634" s="6" t="n"/>
       <c r="C634" s="7" t="n"/>
@@ -25024,7 +25018,7 @@
       <c r="J634" s="9" t="n"/>
       <c r="K634" s="9" t="n"/>
     </row>
-    <row r="635" ht="18" customHeight="1" s="125">
+    <row r="635" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A635" s="5" t="n"/>
       <c r="B635" s="6" t="n"/>
       <c r="C635" s="7" t="n"/>
@@ -25037,7 +25031,7 @@
       <c r="J635" s="9" t="n"/>
       <c r="K635" s="9" t="n"/>
     </row>
-    <row r="636" ht="18" customHeight="1" s="125">
+    <row r="636" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A636" s="5" t="n"/>
       <c r="B636" s="6" t="n"/>
       <c r="C636" s="7" t="n"/>
@@ -25050,7 +25044,7 @@
       <c r="J636" s="9" t="n"/>
       <c r="K636" s="9" t="n"/>
     </row>
-    <row r="637" ht="18" customHeight="1" s="125">
+    <row r="637" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A637" s="5" t="n"/>
       <c r="B637" s="6" t="n"/>
       <c r="C637" s="7" t="n"/>
@@ -25063,7 +25057,7 @@
       <c r="J637" s="9" t="n"/>
       <c r="K637" s="9" t="n"/>
     </row>
-    <row r="638" ht="18" customHeight="1" s="125">
+    <row r="638" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A638" s="5" t="n"/>
       <c r="B638" s="6" t="n"/>
       <c r="C638" s="7" t="n"/>
@@ -25076,7 +25070,7 @@
       <c r="J638" s="9" t="n"/>
       <c r="K638" s="9" t="n"/>
     </row>
-    <row r="639" ht="18" customHeight="1" s="125">
+    <row r="639" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A639" s="5" t="n"/>
       <c r="B639" s="6" t="n"/>
       <c r="C639" s="7" t="n"/>
@@ -25089,7 +25083,7 @@
       <c r="J639" s="9" t="n"/>
       <c r="K639" s="9" t="n"/>
     </row>
-    <row r="640" ht="18" customHeight="1" s="125">
+    <row r="640" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A640" s="5" t="n"/>
       <c r="B640" s="6" t="n"/>
       <c r="C640" s="7" t="n"/>
@@ -25102,7 +25096,7 @@
       <c r="J640" s="9" t="n"/>
       <c r="K640" s="9" t="n"/>
     </row>
-    <row r="641" ht="18" customHeight="1" s="125">
+    <row r="641" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A641" s="5" t="n"/>
       <c r="B641" s="6" t="n"/>
       <c r="C641" s="7" t="n"/>
@@ -25115,7 +25109,7 @@
       <c r="J641" s="9" t="n"/>
       <c r="K641" s="9" t="n"/>
     </row>
-    <row r="642" ht="18" customHeight="1" s="125">
+    <row r="642" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A642" s="5" t="n"/>
       <c r="B642" s="6" t="n"/>
       <c r="C642" s="7" t="n"/>
@@ -25128,7 +25122,7 @@
       <c r="J642" s="9" t="n"/>
       <c r="K642" s="9" t="n"/>
     </row>
-    <row r="643" ht="18" customHeight="1" s="125">
+    <row r="643" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A643" s="5" t="n"/>
       <c r="B643" s="6" t="n"/>
       <c r="C643" s="7" t="n"/>
@@ -25141,7 +25135,7 @@
       <c r="J643" s="9" t="n"/>
       <c r="K643" s="9" t="n"/>
     </row>
-    <row r="644" ht="18" customHeight="1" s="125">
+    <row r="644" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A644" s="5" t="n"/>
       <c r="B644" s="6" t="n"/>
       <c r="C644" s="7" t="n"/>
@@ -25154,7 +25148,7 @@
       <c r="J644" s="9" t="n"/>
       <c r="K644" s="9" t="n"/>
     </row>
-    <row r="645" ht="18" customHeight="1" s="125">
+    <row r="645" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A645" s="5" t="n"/>
       <c r="B645" s="6" t="n"/>
       <c r="C645" s="7" t="n"/>
@@ -25167,7 +25161,7 @@
       <c r="J645" s="9" t="n"/>
       <c r="K645" s="9" t="n"/>
     </row>
-    <row r="646" ht="18" customHeight="1" s="125">
+    <row r="646" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A646" s="5" t="n"/>
       <c r="B646" s="6" t="n"/>
       <c r="C646" s="7" t="n"/>
@@ -25180,7 +25174,7 @@
       <c r="J646" s="9" t="n"/>
       <c r="K646" s="9" t="n"/>
     </row>
-    <row r="647" ht="18" customHeight="1" s="125">
+    <row r="647" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A647" s="5" t="n"/>
       <c r="B647" s="6" t="n"/>
       <c r="C647" s="7" t="n"/>
@@ -25193,7 +25187,7 @@
       <c r="J647" s="9" t="n"/>
       <c r="K647" s="9" t="n"/>
     </row>
-    <row r="648" ht="18" customHeight="1" s="125">
+    <row r="648" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A648" s="5" t="n"/>
       <c r="B648" s="6" t="n"/>
       <c r="C648" s="7" t="n"/>
@@ -25206,7 +25200,7 @@
       <c r="J648" s="9" t="n"/>
       <c r="K648" s="9" t="n"/>
     </row>
-    <row r="649" ht="18" customHeight="1" s="125">
+    <row r="649" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A649" s="5" t="n"/>
       <c r="B649" s="6" t="n"/>
       <c r="C649" s="7" t="n"/>
@@ -25219,7 +25213,7 @@
       <c r="J649" s="9" t="n"/>
       <c r="K649" s="9" t="n"/>
     </row>
-    <row r="650" ht="18" customHeight="1" s="125">
+    <row r="650" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A650" s="5" t="n"/>
       <c r="B650" s="6" t="n"/>
       <c r="C650" s="7" t="n"/>
@@ -25232,7 +25226,7 @@
       <c r="J650" s="9" t="n"/>
       <c r="K650" s="9" t="n"/>
     </row>
-    <row r="651" ht="18" customHeight="1" s="125">
+    <row r="651" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A651" s="5" t="n"/>
       <c r="B651" s="6" t="n"/>
       <c r="C651" s="7" t="n"/>
@@ -25245,7 +25239,7 @@
       <c r="J651" s="9" t="n"/>
       <c r="K651" s="9" t="n"/>
     </row>
-    <row r="652" ht="18" customHeight="1" s="125">
+    <row r="652" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A652" s="5" t="n"/>
       <c r="B652" s="6" t="n"/>
       <c r="C652" s="7" t="n"/>
@@ -25258,7 +25252,7 @@
       <c r="J652" s="9" t="n"/>
       <c r="K652" s="9" t="n"/>
     </row>
-    <row r="653" ht="18" customHeight="1" s="125">
+    <row r="653" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A653" s="5" t="n"/>
       <c r="B653" s="6" t="n"/>
       <c r="C653" s="7" t="n"/>
@@ -25271,7 +25265,7 @@
       <c r="J653" s="9" t="n"/>
       <c r="K653" s="9" t="n"/>
     </row>
-    <row r="654" ht="18" customHeight="1" s="125">
+    <row r="654" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A654" s="5" t="n"/>
       <c r="B654" s="6" t="n"/>
       <c r="C654" s="7" t="n"/>
@@ -25284,7 +25278,7 @@
       <c r="J654" s="9" t="n"/>
       <c r="K654" s="9" t="n"/>
     </row>
-    <row r="655" ht="18" customHeight="1" s="125">
+    <row r="655" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A655" s="5" t="n"/>
       <c r="B655" s="6" t="n"/>
       <c r="C655" s="7" t="n"/>
@@ -25297,7 +25291,7 @@
       <c r="J655" s="9" t="n"/>
       <c r="K655" s="9" t="n"/>
     </row>
-    <row r="656" ht="18" customHeight="1" s="125">
+    <row r="656" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A656" s="5" t="n"/>
       <c r="B656" s="6" t="n"/>
       <c r="C656" s="7" t="n"/>
@@ -25310,7 +25304,7 @@
       <c r="J656" s="9" t="n"/>
       <c r="K656" s="9" t="n"/>
     </row>
-    <row r="657" ht="18" customHeight="1" s="125">
+    <row r="657" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A657" s="5" t="n"/>
       <c r="B657" s="6" t="n"/>
       <c r="C657" s="7" t="n"/>
@@ -25323,7 +25317,7 @@
       <c r="J657" s="9" t="n"/>
       <c r="K657" s="9" t="n"/>
     </row>
-    <row r="658" ht="18" customHeight="1" s="125">
+    <row r="658" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A658" s="5" t="n"/>
       <c r="B658" s="6" t="n"/>
       <c r="C658" s="7" t="n"/>
@@ -25336,7 +25330,7 @@
       <c r="J658" s="9" t="n"/>
       <c r="K658" s="9" t="n"/>
     </row>
-    <row r="659" ht="18" customHeight="1" s="125">
+    <row r="659" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A659" s="5" t="n"/>
       <c r="B659" s="6" t="n"/>
       <c r="C659" s="7" t="n"/>
@@ -25349,7 +25343,7 @@
       <c r="J659" s="9" t="n"/>
       <c r="K659" s="9" t="n"/>
     </row>
-    <row r="660" ht="18" customHeight="1" s="125">
+    <row r="660" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A660" s="5" t="n"/>
       <c r="B660" s="6" t="n"/>
       <c r="C660" s="7" t="n"/>
@@ -25362,7 +25356,7 @@
       <c r="J660" s="9" t="n"/>
       <c r="K660" s="9" t="n"/>
     </row>
-    <row r="661" ht="18" customHeight="1" s="125">
+    <row r="661" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A661" s="5" t="n"/>
       <c r="B661" s="6" t="n"/>
       <c r="C661" s="7" t="n"/>
@@ -25375,7 +25369,7 @@
       <c r="J661" s="9" t="n"/>
       <c r="K661" s="9" t="n"/>
     </row>
-    <row r="662" ht="18" customHeight="1" s="125">
+    <row r="662" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A662" s="5" t="n"/>
       <c r="B662" s="6" t="n"/>
       <c r="C662" s="7" t="n"/>
@@ -25388,7 +25382,7 @@
       <c r="J662" s="9" t="n"/>
       <c r="K662" s="9" t="n"/>
     </row>
-    <row r="663" ht="18" customHeight="1" s="125">
+    <row r="663" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A663" s="5" t="n"/>
       <c r="B663" s="6" t="n"/>
       <c r="C663" s="7" t="n"/>
@@ -25401,7 +25395,7 @@
       <c r="J663" s="9" t="n"/>
       <c r="K663" s="9" t="n"/>
     </row>
-    <row r="664" ht="18" customHeight="1" s="125">
+    <row r="664" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A664" s="5" t="n"/>
       <c r="B664" s="6" t="n"/>
       <c r="C664" s="7" t="n"/>
@@ -25414,7 +25408,7 @@
       <c r="J664" s="9" t="n"/>
       <c r="K664" s="9" t="n"/>
     </row>
-    <row r="665" ht="18" customHeight="1" s="125">
+    <row r="665" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A665" s="5" t="n"/>
       <c r="B665" s="6" t="n"/>
       <c r="C665" s="7" t="n"/>
@@ -25427,7 +25421,7 @@
       <c r="J665" s="9" t="n"/>
       <c r="K665" s="9" t="n"/>
     </row>
-    <row r="666" ht="18" customHeight="1" s="125">
+    <row r="666" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A666" s="5" t="n"/>
       <c r="B666" s="6" t="n"/>
       <c r="C666" s="7" t="n"/>
@@ -25440,7 +25434,7 @@
       <c r="J666" s="9" t="n"/>
       <c r="K666" s="9" t="n"/>
     </row>
-    <row r="667" ht="18" customHeight="1" s="125">
+    <row r="667" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A667" s="68" t="n"/>
       <c r="B667" s="63" t="n"/>
       <c r="C667" s="7" t="n"/>
@@ -25453,7 +25447,7 @@
       <c r="J667" s="9" t="n"/>
       <c r="K667" s="9" t="n"/>
     </row>
-    <row r="668" ht="18" customHeight="1" s="125">
+    <row r="668" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A668" s="68" t="n"/>
       <c r="B668" s="63" t="n"/>
       <c r="C668" s="7" t="n"/>
@@ -25466,7 +25460,7 @@
       <c r="J668" s="9" t="n"/>
       <c r="K668" s="9" t="n"/>
     </row>
-    <row r="669" ht="18" customHeight="1" s="125">
+    <row r="669" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A669" s="68" t="n"/>
       <c r="B669" s="63" t="n"/>
       <c r="C669" s="7" t="n"/>
@@ -25479,7 +25473,7 @@
       <c r="J669" s="9" t="n"/>
       <c r="K669" s="9" t="n"/>
     </row>
-    <row r="670" ht="18" customHeight="1" s="125">
+    <row r="670" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A670" s="68" t="n"/>
       <c r="B670" s="63" t="n"/>
       <c r="C670" s="7" t="n"/>
@@ -25492,7 +25486,7 @@
       <c r="J670" s="9" t="n"/>
       <c r="K670" s="9" t="n"/>
     </row>
-    <row r="671" ht="18" customHeight="1" s="125">
+    <row r="671" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A671" s="68" t="n"/>
       <c r="B671" s="63" t="n"/>
       <c r="C671" s="7" t="n"/>
@@ -25505,7 +25499,7 @@
       <c r="J671" s="9" t="n"/>
       <c r="K671" s="9" t="n"/>
     </row>
-    <row r="672" ht="18" customHeight="1" s="125">
+    <row r="672" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A672" s="68" t="n"/>
       <c r="B672" s="63" t="n"/>
       <c r="C672" s="7" t="n"/>
@@ -25518,7 +25512,7 @@
       <c r="J672" s="9" t="n"/>
       <c r="K672" s="9" t="n"/>
     </row>
-    <row r="673" ht="18" customHeight="1" s="125">
+    <row r="673" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A673" s="68" t="n"/>
       <c r="B673" s="63" t="n"/>
       <c r="C673" s="7" t="n"/>
@@ -25531,7 +25525,7 @@
       <c r="J673" s="9" t="n"/>
       <c r="K673" s="9" t="n"/>
     </row>
-    <row r="674" ht="18" customHeight="1" s="125">
+    <row r="674" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A674" s="68" t="n"/>
       <c r="B674" s="63" t="n"/>
       <c r="C674" s="7" t="n"/>
@@ -25544,7 +25538,7 @@
       <c r="J674" s="9" t="n"/>
       <c r="K674" s="9" t="n"/>
     </row>
-    <row r="675" ht="18" customHeight="1" s="125">
+    <row r="675" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A675" s="68" t="n"/>
       <c r="B675" s="63" t="n"/>
       <c r="C675" s="7" t="n"/>
@@ -25557,7 +25551,7 @@
       <c r="J675" s="9" t="n"/>
       <c r="K675" s="9" t="n"/>
     </row>
-    <row r="676" ht="18" customHeight="1" s="125">
+    <row r="676" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A676" s="68" t="n"/>
       <c r="B676" s="63" t="n"/>
       <c r="C676" s="7" t="n"/>
@@ -25570,7 +25564,7 @@
       <c r="J676" s="9" t="n"/>
       <c r="K676" s="9" t="n"/>
     </row>
-    <row r="677" ht="18" customHeight="1" s="125">
+    <row r="677" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A677" s="68" t="n"/>
       <c r="B677" s="63" t="n"/>
       <c r="C677" s="7" t="n"/>
@@ -25583,7 +25577,7 @@
       <c r="J677" s="9" t="n"/>
       <c r="K677" s="9" t="n"/>
     </row>
-    <row r="678" ht="18" customHeight="1" s="125">
+    <row r="678" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A678" s="68" t="n"/>
       <c r="B678" s="63" t="n"/>
       <c r="C678" s="7" t="n"/>
@@ -25596,7 +25590,7 @@
       <c r="J678" s="9" t="n"/>
       <c r="K678" s="9" t="n"/>
     </row>
-    <row r="679" ht="18" customHeight="1" s="125">
+    <row r="679" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A679" s="68" t="n"/>
       <c r="B679" s="63" t="n"/>
       <c r="C679" s="7" t="n"/>
@@ -25609,7 +25603,7 @@
       <c r="J679" s="9" t="n"/>
       <c r="K679" s="9" t="n"/>
     </row>
-    <row r="680" ht="18" customHeight="1" s="125">
+    <row r="680" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A680" s="68" t="n"/>
       <c r="B680" s="63" t="n"/>
       <c r="C680" s="7" t="n"/>
@@ -25622,7 +25616,7 @@
       <c r="J680" s="9" t="n"/>
       <c r="K680" s="9" t="n"/>
     </row>
-    <row r="681" ht="18" customHeight="1" s="125">
+    <row r="681" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A681" s="68" t="n"/>
       <c r="B681" s="63" t="n"/>
       <c r="C681" s="7" t="n"/>
@@ -25635,7 +25629,7 @@
       <c r="J681" s="9" t="n"/>
       <c r="K681" s="9" t="n"/>
     </row>
-    <row r="682" ht="18" customHeight="1" s="125">
+    <row r="682" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A682" s="68" t="n"/>
       <c r="B682" s="63" t="n"/>
       <c r="C682" s="7" t="n"/>
@@ -25648,7 +25642,7 @@
       <c r="J682" s="9" t="n"/>
       <c r="K682" s="9" t="n"/>
     </row>
-    <row r="683" ht="18" customHeight="1" s="125">
+    <row r="683" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A683" s="68" t="n"/>
       <c r="B683" s="63" t="n"/>
       <c r="C683" s="7" t="n"/>
@@ -25661,7 +25655,7 @@
       <c r="J683" s="9" t="n"/>
       <c r="K683" s="9" t="n"/>
     </row>
-    <row r="684" ht="18" customHeight="1" s="125">
+    <row r="684" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A684" s="68" t="n"/>
       <c r="B684" s="63" t="n"/>
       <c r="C684" s="7" t="n"/>
@@ -25674,7 +25668,7 @@
       <c r="J684" s="9" t="n"/>
       <c r="K684" s="9" t="n"/>
     </row>
-    <row r="685" ht="18" customHeight="1" s="125">
+    <row r="685" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A685" s="68" t="n"/>
       <c r="B685" s="63" t="n"/>
       <c r="C685" s="7" t="n"/>
@@ -25687,7 +25681,7 @@
       <c r="J685" s="9" t="n"/>
       <c r="K685" s="9" t="n"/>
     </row>
-    <row r="686" ht="18" customHeight="1" s="125">
+    <row r="686" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A686" s="68" t="n"/>
       <c r="B686" s="63" t="n"/>
       <c r="C686" s="7" t="n"/>
@@ -25700,7 +25694,7 @@
       <c r="J686" s="9" t="n"/>
       <c r="K686" s="9" t="n"/>
     </row>
-    <row r="687" ht="18" customHeight="1" s="125">
+    <row r="687" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A687" s="68" t="n"/>
       <c r="B687" s="63" t="n"/>
       <c r="C687" s="7" t="n"/>
@@ -25713,7 +25707,7 @@
       <c r="J687" s="9" t="n"/>
       <c r="K687" s="9" t="n"/>
     </row>
-    <row r="688" ht="18" customHeight="1" s="125">
+    <row r="688" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A688" s="68" t="n"/>
       <c r="B688" s="63" t="n"/>
       <c r="C688" s="7" t="n"/>
@@ -25726,7 +25720,7 @@
       <c r="J688" s="9" t="n"/>
       <c r="K688" s="9" t="n"/>
     </row>
-    <row r="689" ht="18" customHeight="1" s="125">
+    <row r="689" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A689" s="62" t="n"/>
       <c r="B689" s="62" t="n"/>
       <c r="C689" s="62" t="n"/>
@@ -25738,7 +25732,7 @@
       <c r="I689" s="61" t="n"/>
       <c r="J689" s="61" t="n"/>
     </row>
-    <row r="690" ht="18" customHeight="1" s="125">
+    <row r="690" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A690" s="62" t="n"/>
       <c r="B690" s="62" t="n"/>
       <c r="C690" s="62" t="n"/>
@@ -25750,7 +25744,7 @@
       <c r="I690" s="61" t="n"/>
       <c r="J690" s="61" t="n"/>
     </row>
-    <row r="691" ht="18" customHeight="1" s="125">
+    <row r="691" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A691" s="62" t="n"/>
       <c r="B691" s="62" t="n"/>
       <c r="C691" s="62" t="n"/>
@@ -25762,7 +25756,7 @@
       <c r="I691" s="61" t="n"/>
       <c r="J691" s="61" t="n"/>
     </row>
-    <row r="692" ht="18" customHeight="1" s="125">
+    <row r="692" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A692" s="62" t="n"/>
       <c r="B692" s="62" t="n"/>
       <c r="C692" s="62" t="n"/>
@@ -25774,7 +25768,7 @@
       <c r="I692" s="61" t="n"/>
       <c r="J692" s="61" t="n"/>
     </row>
-    <row r="693" ht="18" customHeight="1" s="125">
+    <row r="693" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A693" s="62" t="n"/>
       <c r="B693" s="62" t="n"/>
       <c r="C693" s="62" t="n"/>
@@ -25786,7 +25780,7 @@
       <c r="I693" s="61" t="n"/>
       <c r="J693" s="61" t="n"/>
     </row>
-    <row r="694" ht="18" customHeight="1" s="125">
+    <row r="694" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A694" s="62" t="n"/>
       <c r="B694" s="62" t="n"/>
       <c r="C694" s="62" t="n"/>
@@ -25798,7 +25792,7 @@
       <c r="I694" s="61" t="n"/>
       <c r="J694" s="61" t="n"/>
     </row>
-    <row r="695" ht="18" customHeight="1" s="125">
+    <row r="695" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A695" s="62" t="n"/>
       <c r="B695" s="62" t="n"/>
       <c r="C695" s="62" t="n"/>
@@ -25810,7 +25804,7 @@
       <c r="I695" s="61" t="n"/>
       <c r="J695" s="61" t="n"/>
     </row>
-    <row r="696" ht="18" customHeight="1" s="125">
+    <row r="696" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A696" s="62" t="n"/>
       <c r="B696" s="62" t="n"/>
       <c r="C696" s="62" t="n"/>
@@ -25822,7 +25816,7 @@
       <c r="I696" s="61" t="n"/>
       <c r="J696" s="61" t="n"/>
     </row>
-    <row r="697" ht="18" customHeight="1" s="125">
+    <row r="697" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A697" s="62" t="n"/>
       <c r="B697" s="62" t="n"/>
       <c r="C697" s="62" t="n"/>
@@ -25834,7 +25828,7 @@
       <c r="I697" s="61" t="n"/>
       <c r="J697" s="61" t="n"/>
     </row>
-    <row r="698" ht="18" customHeight="1" s="125">
+    <row r="698" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A698" s="62" t="n"/>
       <c r="B698" s="62" t="n"/>
       <c r="C698" s="62" t="n"/>
@@ -25846,7 +25840,7 @@
       <c r="I698" s="61" t="n"/>
       <c r="J698" s="61" t="n"/>
     </row>
-    <row r="699" ht="18" customHeight="1" s="125">
+    <row r="699" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A699" s="62" t="n"/>
       <c r="B699" s="62" t="n"/>
       <c r="C699" s="62" t="n"/>
@@ -25858,7 +25852,7 @@
       <c r="I699" s="61" t="n"/>
       <c r="J699" s="61" t="n"/>
     </row>
-    <row r="700" ht="18" customHeight="1" s="125">
+    <row r="700" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A700" s="62" t="n"/>
       <c r="B700" s="62" t="n"/>
       <c r="C700" s="62" t="n"/>
@@ -25870,7 +25864,7 @@
       <c r="I700" s="61" t="n"/>
       <c r="J700" s="61" t="n"/>
     </row>
-    <row r="701" ht="18" customHeight="1" s="125">
+    <row r="701" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A701" s="62" t="n"/>
       <c r="B701" s="62" t="n"/>
       <c r="C701" s="62" t="n"/>
@@ -25882,7 +25876,7 @@
       <c r="I701" s="61" t="n"/>
       <c r="J701" s="61" t="n"/>
     </row>
-    <row r="702" ht="18" customHeight="1" s="125">
+    <row r="702" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A702" s="62" t="n"/>
       <c r="B702" s="62" t="n"/>
       <c r="C702" s="62" t="n"/>
@@ -25894,7 +25888,7 @@
       <c r="I702" s="61" t="n"/>
       <c r="J702" s="61" t="n"/>
     </row>
-    <row r="703" ht="18" customHeight="1" s="125">
+    <row r="703" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A703" s="62" t="n"/>
       <c r="B703" s="62" t="n"/>
       <c r="C703" s="62" t="n"/>
@@ -25906,7 +25900,7 @@
       <c r="I703" s="61" t="n"/>
       <c r="J703" s="61" t="n"/>
     </row>
-    <row r="704" ht="18" customHeight="1" s="125">
+    <row r="704" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A704" s="62" t="n"/>
       <c r="B704" s="62" t="n"/>
       <c r="C704" s="62" t="n"/>
@@ -25918,7 +25912,7 @@
       <c r="I704" s="61" t="n"/>
       <c r="J704" s="61" t="n"/>
     </row>
-    <row r="705" ht="18" customHeight="1" s="125">
+    <row r="705" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A705" s="62" t="n"/>
       <c r="B705" s="62" t="n"/>
       <c r="C705" s="62" t="n"/>
@@ -25930,7 +25924,7 @@
       <c r="I705" s="61" t="n"/>
       <c r="J705" s="61" t="n"/>
     </row>
-    <row r="706" ht="18" customHeight="1" s="125">
+    <row r="706" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A706" s="62" t="n"/>
       <c r="B706" s="62" t="n"/>
       <c r="C706" s="62" t="n"/>
@@ -25942,7 +25936,7 @@
       <c r="I706" s="61" t="n"/>
       <c r="J706" s="61" t="n"/>
     </row>
-    <row r="707" ht="18" customHeight="1" s="125">
+    <row r="707" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A707" s="62" t="n"/>
       <c r="B707" s="62" t="n"/>
       <c r="C707" s="62" t="n"/>
@@ -25954,7 +25948,7 @@
       <c r="I707" s="61" t="n"/>
       <c r="J707" s="61" t="n"/>
     </row>
-    <row r="708" ht="18" customHeight="1" s="125">
+    <row r="708" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A708" s="62" t="n"/>
       <c r="B708" s="62" t="n"/>
       <c r="C708" s="62" t="n"/>
@@ -25966,7 +25960,7 @@
       <c r="I708" s="61" t="n"/>
       <c r="J708" s="61" t="n"/>
     </row>
-    <row r="709" ht="18" customHeight="1" s="125">
+    <row r="709" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A709" s="62" t="n"/>
       <c r="B709" s="62" t="n"/>
       <c r="C709" s="62" t="n"/>
@@ -25978,7 +25972,7 @@
       <c r="I709" s="61" t="n"/>
       <c r="J709" s="61" t="n"/>
     </row>
-    <row r="710" ht="18" customHeight="1" s="125">
+    <row r="710" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A710" s="62" t="n"/>
       <c r="B710" s="62" t="n"/>
       <c r="C710" s="62" t="n"/>
@@ -25990,7 +25984,7 @@
       <c r="I710" s="61" t="n"/>
       <c r="J710" s="61" t="n"/>
     </row>
-    <row r="711" ht="18" customHeight="1" s="125">
+    <row r="711" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A711" s="62" t="n"/>
       <c r="B711" s="62" t="n"/>
       <c r="C711" s="62" t="n"/>
@@ -26002,7 +25996,7 @@
       <c r="I711" s="61" t="n"/>
       <c r="J711" s="61" t="n"/>
     </row>
-    <row r="712" ht="18" customHeight="1" s="125">
+    <row r="712" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A712" s="62" t="n"/>
       <c r="B712" s="62" t="n"/>
       <c r="C712" s="62" t="n"/>
@@ -26014,7 +26008,7 @@
       <c r="I712" s="61" t="n"/>
       <c r="J712" s="61" t="n"/>
     </row>
-    <row r="713" ht="18" customHeight="1" s="125">
+    <row r="713" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A713" s="62" t="n"/>
       <c r="B713" s="62" t="n"/>
       <c r="C713" s="62" t="n"/>
@@ -26026,7 +26020,7 @@
       <c r="I713" s="61" t="n"/>
       <c r="J713" s="61" t="n"/>
     </row>
-    <row r="714" ht="18" customHeight="1" s="125">
+    <row r="714" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A714" s="62" t="n"/>
       <c r="B714" s="62" t="n"/>
       <c r="C714" s="62" t="n"/>
@@ -26038,7 +26032,7 @@
       <c r="I714" s="61" t="n"/>
       <c r="J714" s="61" t="n"/>
     </row>
-    <row r="715" ht="18" customHeight="1" s="125">
+    <row r="715" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A715" s="62" t="n"/>
       <c r="B715" s="62" t="n"/>
       <c r="C715" s="62" t="n"/>
@@ -26050,7 +26044,7 @@
       <c r="I715" s="61" t="n"/>
       <c r="J715" s="61" t="n"/>
     </row>
-    <row r="716" ht="18" customHeight="1" s="125">
+    <row r="716" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A716" s="62" t="n"/>
       <c r="B716" s="62" t="n"/>
       <c r="C716" s="62" t="n"/>
@@ -26062,7 +26056,7 @@
       <c r="I716" s="61" t="n"/>
       <c r="J716" s="61" t="n"/>
     </row>
-    <row r="717" ht="18" customHeight="1" s="125">
+    <row r="717" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A717" s="62" t="n"/>
       <c r="B717" s="62" t="n"/>
       <c r="C717" s="62" t="n"/>
@@ -26074,7 +26068,7 @@
       <c r="I717" s="61" t="n"/>
       <c r="J717" s="61" t="n"/>
     </row>
-    <row r="718" ht="18" customHeight="1" s="125">
+    <row r="718" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A718" s="62" t="n"/>
       <c r="B718" s="62" t="n"/>
       <c r="C718" s="62" t="n"/>
@@ -26086,7 +26080,7 @@
       <c r="I718" s="61" t="n"/>
       <c r="J718" s="61" t="n"/>
     </row>
-    <row r="719" ht="18" customHeight="1" s="125">
+    <row r="719" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A719" s="62" t="n"/>
       <c r="B719" s="62" t="n"/>
       <c r="C719" s="62" t="n"/>
@@ -26098,7 +26092,7 @@
       <c r="I719" s="61" t="n"/>
       <c r="J719" s="61" t="n"/>
     </row>
-    <row r="720" ht="18" customHeight="1" s="125">
+    <row r="720" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A720" s="62" t="n"/>
       <c r="B720" s="62" t="n"/>
       <c r="C720" s="62" t="n"/>
@@ -26110,7 +26104,7 @@
       <c r="I720" s="61" t="n"/>
       <c r="J720" s="61" t="n"/>
     </row>
-    <row r="721" ht="18" customHeight="1" s="125">
+    <row r="721" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A721" s="62" t="n"/>
       <c r="B721" s="62" t="n"/>
       <c r="C721" s="62" t="n"/>
@@ -26122,7 +26116,7 @@
       <c r="I721" s="61" t="n"/>
       <c r="J721" s="61" t="n"/>
     </row>
-    <row r="722" ht="18" customHeight="1" s="125">
+    <row r="722" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A722" s="62" t="n"/>
       <c r="B722" s="62" t="n"/>
       <c r="C722" s="62" t="n"/>
@@ -26134,7 +26128,7 @@
       <c r="I722" s="61" t="n"/>
       <c r="J722" s="61" t="n"/>
     </row>
-    <row r="723" ht="18" customHeight="1" s="125">
+    <row r="723" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A723" s="62" t="n"/>
       <c r="B723" s="62" t="n"/>
       <c r="C723" s="62" t="n"/>
@@ -26146,7 +26140,7 @@
       <c r="I723" s="61" t="n"/>
       <c r="J723" s="61" t="n"/>
     </row>
-    <row r="724" ht="18" customHeight="1" s="125">
+    <row r="724" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A724" s="62" t="n"/>
       <c r="B724" s="62" t="n"/>
       <c r="C724" s="62" t="n"/>
@@ -26158,7 +26152,7 @@
       <c r="I724" s="61" t="n"/>
       <c r="J724" s="61" t="n"/>
     </row>
-    <row r="725" ht="18" customHeight="1" s="125">
+    <row r="725" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A725" s="62" t="n"/>
       <c r="B725" s="62" t="n"/>
       <c r="C725" s="62" t="n"/>
@@ -26170,7 +26164,7 @@
       <c r="I725" s="61" t="n"/>
       <c r="J725" s="61" t="n"/>
     </row>
-    <row r="726" ht="18" customHeight="1" s="125">
+    <row r="726" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A726" s="62" t="n"/>
       <c r="B726" s="62" t="n"/>
       <c r="C726" s="62" t="n"/>
@@ -26182,7 +26176,7 @@
       <c r="I726" s="61" t="n"/>
       <c r="J726" s="61" t="n"/>
     </row>
-    <row r="727" ht="18" customHeight="1" s="125">
+    <row r="727" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A727" s="62" t="n"/>
       <c r="B727" s="62" t="n"/>
       <c r="C727" s="62" t="n"/>
@@ -26194,7 +26188,7 @@
       <c r="I727" s="61" t="n"/>
       <c r="J727" s="61" t="n"/>
     </row>
-    <row r="728" ht="18" customHeight="1" s="125">
+    <row r="728" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A728" s="62" t="n"/>
       <c r="B728" s="62" t="n"/>
       <c r="C728" s="62" t="n"/>
@@ -26206,7 +26200,7 @@
       <c r="I728" s="61" t="n"/>
       <c r="J728" s="61" t="n"/>
     </row>
-    <row r="729" ht="18" customHeight="1" s="125">
+    <row r="729" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A729" s="62" t="n"/>
       <c r="B729" s="62" t="n"/>
       <c r="C729" s="62" t="n"/>
@@ -26218,7 +26212,7 @@
       <c r="I729" s="61" t="n"/>
       <c r="J729" s="61" t="n"/>
     </row>
-    <row r="730" ht="18" customHeight="1" s="125">
+    <row r="730" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A730" s="62" t="n"/>
       <c r="B730" s="62" t="n"/>
       <c r="C730" s="62" t="n"/>
@@ -26230,7 +26224,7 @@
       <c r="I730" s="61" t="n"/>
       <c r="J730" s="61" t="n"/>
     </row>
-    <row r="731" ht="18" customHeight="1" s="125">
+    <row r="731" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A731" s="62" t="n"/>
       <c r="B731" s="62" t="n"/>
       <c r="C731" s="62" t="n"/>
@@ -26242,7 +26236,7 @@
       <c r="I731" s="61" t="n"/>
       <c r="J731" s="61" t="n"/>
     </row>
-    <row r="732" ht="18" customHeight="1" s="125">
+    <row r="732" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A732" s="62" t="n"/>
       <c r="B732" s="62" t="n"/>
       <c r="C732" s="62" t="n"/>
@@ -26254,7 +26248,7 @@
       <c r="I732" s="61" t="n"/>
       <c r="J732" s="61" t="n"/>
     </row>
-    <row r="733" ht="18" customHeight="1" s="125">
+    <row r="733" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A733" s="62" t="n"/>
       <c r="B733" s="62" t="n"/>
       <c r="C733" s="62" t="n"/>
@@ -26266,7 +26260,7 @@
       <c r="I733" s="61" t="n"/>
       <c r="J733" s="61" t="n"/>
     </row>
-    <row r="734" ht="18" customHeight="1" s="125">
+    <row r="734" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A734" s="62" t="n"/>
       <c r="B734" s="62" t="n"/>
       <c r="C734" s="62" t="n"/>
@@ -26278,7 +26272,7 @@
       <c r="I734" s="61" t="n"/>
       <c r="J734" s="61" t="n"/>
     </row>
-    <row r="735" ht="18" customHeight="1" s="125">
+    <row r="735" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A735" s="62" t="n"/>
       <c r="B735" s="62" t="n"/>
       <c r="C735" s="62" t="n"/>
@@ -26290,7 +26284,7 @@
       <c r="I735" s="61" t="n"/>
       <c r="J735" s="61" t="n"/>
     </row>
-    <row r="736" ht="18" customHeight="1" s="125">
+    <row r="736" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A736" s="62" t="n"/>
       <c r="B736" s="62" t="n"/>
       <c r="C736" s="62" t="n"/>
@@ -26302,7 +26296,7 @@
       <c r="I736" s="61" t="n"/>
       <c r="J736" s="61" t="n"/>
     </row>
-    <row r="737" ht="18" customHeight="1" s="125">
+    <row r="737" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A737" s="62" t="n"/>
       <c r="B737" s="62" t="n"/>
       <c r="C737" s="62" t="n"/>
@@ -26314,7 +26308,7 @@
       <c r="I737" s="61" t="n"/>
       <c r="J737" s="61" t="n"/>
     </row>
-    <row r="738" ht="18" customHeight="1" s="125">
+    <row r="738" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A738" s="62" t="n"/>
       <c r="B738" s="62" t="n"/>
       <c r="C738" s="62" t="n"/>
@@ -26326,7 +26320,7 @@
       <c r="I738" s="61" t="n"/>
       <c r="J738" s="61" t="n"/>
     </row>
-    <row r="739" ht="18" customHeight="1" s="125">
+    <row r="739" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A739" s="62" t="n"/>
       <c r="B739" s="62" t="n"/>
       <c r="C739" s="62" t="n"/>
@@ -26338,7 +26332,7 @@
       <c r="I739" s="61" t="n"/>
       <c r="J739" s="61" t="n"/>
     </row>
-    <row r="740" ht="18" customHeight="1" s="125">
+    <row r="740" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A740" s="62" t="n"/>
       <c r="B740" s="62" t="n"/>
       <c r="C740" s="62" t="n"/>
@@ -26350,7 +26344,7 @@
       <c r="I740" s="61" t="n"/>
       <c r="J740" s="61" t="n"/>
     </row>
-    <row r="741" ht="18" customHeight="1" s="125">
+    <row r="741" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A741" s="62" t="n"/>
       <c r="B741" s="62" t="n"/>
       <c r="C741" s="62" t="n"/>
@@ -26362,7 +26356,7 @@
       <c r="I741" s="61" t="n"/>
       <c r="J741" s="61" t="n"/>
     </row>
-    <row r="742" ht="18" customHeight="1" s="125">
+    <row r="742" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A742" s="62" t="n"/>
       <c r="B742" s="62" t="n"/>
       <c r="C742" s="62" t="n"/>
@@ -26374,7 +26368,7 @@
       <c r="I742" s="61" t="n"/>
       <c r="J742" s="61" t="n"/>
     </row>
-    <row r="743" ht="18" customHeight="1" s="125">
+    <row r="743" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A743" s="62" t="n"/>
       <c r="B743" s="62" t="n"/>
       <c r="C743" s="62" t="n"/>
@@ -26386,7 +26380,7 @@
       <c r="I743" s="61" t="n"/>
       <c r="J743" s="61" t="n"/>
     </row>
-    <row r="744" ht="18" customHeight="1" s="125">
+    <row r="744" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A744" s="62" t="n"/>
       <c r="B744" s="62" t="n"/>
       <c r="C744" s="62" t="n"/>
@@ -26398,7 +26392,7 @@
       <c r="I744" s="61" t="n"/>
       <c r="J744" s="61" t="n"/>
     </row>
-    <row r="745" ht="18" customHeight="1" s="125">
+    <row r="745" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A745" s="62" t="n"/>
       <c r="B745" s="62" t="n"/>
       <c r="C745" s="62" t="n"/>
@@ -26410,7 +26404,7 @@
       <c r="I745" s="61" t="n"/>
       <c r="J745" s="61" t="n"/>
     </row>
-    <row r="746" ht="18" customHeight="1" s="125">
+    <row r="746" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A746" s="62" t="n"/>
       <c r="B746" s="62" t="n"/>
       <c r="C746" s="62" t="n"/>
@@ -26422,7 +26416,7 @@
       <c r="I746" s="61" t="n"/>
       <c r="J746" s="61" t="n"/>
     </row>
-    <row r="747" ht="18" customHeight="1" s="125">
+    <row r="747" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A747" s="62" t="n"/>
       <c r="B747" s="62" t="n"/>
       <c r="C747" s="62" t="n"/>
@@ -26434,7 +26428,7 @@
       <c r="I747" s="61" t="n"/>
       <c r="J747" s="61" t="n"/>
     </row>
-    <row r="748" ht="18" customHeight="1" s="125">
+    <row r="748" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A748" s="62" t="n"/>
       <c r="B748" s="62" t="n"/>
       <c r="C748" s="62" t="n"/>
@@ -26446,7 +26440,7 @@
       <c r="I748" s="61" t="n"/>
       <c r="J748" s="61" t="n"/>
     </row>
-    <row r="749" ht="18" customHeight="1" s="125">
+    <row r="749" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A749" s="62" t="n"/>
       <c r="B749" s="62" t="n"/>
       <c r="C749" s="62" t="n"/>
@@ -26458,7 +26452,7 @@
       <c r="I749" s="61" t="n"/>
       <c r="J749" s="61" t="n"/>
     </row>
-    <row r="750" ht="18" customHeight="1" s="125">
+    <row r="750" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A750" s="62" t="n"/>
       <c r="B750" s="62" t="n"/>
       <c r="C750" s="62" t="n"/>
@@ -26470,7 +26464,7 @@
       <c r="I750" s="61" t="n"/>
       <c r="J750" s="61" t="n"/>
     </row>
-    <row r="751" ht="18" customHeight="1" s="125">
+    <row r="751" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A751" s="62" t="n"/>
       <c r="B751" s="62" t="n"/>
       <c r="C751" s="62" t="n"/>
@@ -26482,7 +26476,7 @@
       <c r="I751" s="61" t="n"/>
       <c r="J751" s="61" t="n"/>
     </row>
-    <row r="752" ht="18" customHeight="1" s="125">
+    <row r="752" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A752" s="62" t="n"/>
       <c r="B752" s="62" t="n"/>
       <c r="C752" s="62" t="n"/>
@@ -26494,7 +26488,7 @@
       <c r="I752" s="61" t="n"/>
       <c r="J752" s="61" t="n"/>
     </row>
-    <row r="753" ht="18" customHeight="1" s="125">
+    <row r="753" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A753" s="62" t="n"/>
       <c r="B753" s="62" t="n"/>
       <c r="C753" s="62" t="n"/>
@@ -26506,7 +26500,7 @@
       <c r="I753" s="61" t="n"/>
       <c r="J753" s="61" t="n"/>
     </row>
-    <row r="754" ht="18" customHeight="1" s="125">
+    <row r="754" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A754" s="62" t="n"/>
       <c r="B754" s="62" t="n"/>
       <c r="C754" s="62" t="n"/>
@@ -26518,7 +26512,7 @@
       <c r="I754" s="61" t="n"/>
       <c r="J754" s="61" t="n"/>
     </row>
-    <row r="755" ht="18" customHeight="1" s="125">
+    <row r="755" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A755" s="62" t="n"/>
       <c r="B755" s="62" t="n"/>
       <c r="C755" s="62" t="n"/>
@@ -26530,7 +26524,7 @@
       <c r="I755" s="61" t="n"/>
       <c r="J755" s="61" t="n"/>
     </row>
-    <row r="756" ht="18" customHeight="1" s="125">
+    <row r="756" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A756" s="62" t="n"/>
       <c r="B756" s="62" t="n"/>
       <c r="C756" s="62" t="n"/>
@@ -26542,7 +26536,7 @@
       <c r="I756" s="61" t="n"/>
       <c r="J756" s="61" t="n"/>
     </row>
-    <row r="757" ht="18" customHeight="1" s="125">
+    <row r="757" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A757" s="62" t="n"/>
       <c r="B757" s="62" t="n"/>
       <c r="C757" s="62" t="n"/>
@@ -26554,7 +26548,7 @@
       <c r="I757" s="61" t="n"/>
       <c r="J757" s="61" t="n"/>
     </row>
-    <row r="758" ht="18" customHeight="1" s="125">
+    <row r="758" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A758" s="62" t="n"/>
       <c r="B758" s="62" t="n"/>
       <c r="C758" s="62" t="n"/>
@@ -26566,7 +26560,7 @@
       <c r="I758" s="61" t="n"/>
       <c r="J758" s="61" t="n"/>
     </row>
-    <row r="759" ht="18" customHeight="1" s="125">
+    <row r="759" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A759" s="62" t="n"/>
       <c r="B759" s="62" t="n"/>
       <c r="C759" s="62" t="n"/>
@@ -26578,7 +26572,7 @@
       <c r="I759" s="61" t="n"/>
       <c r="J759" s="61" t="n"/>
     </row>
-    <row r="760" ht="18" customHeight="1" s="125">
+    <row r="760" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A760" s="62" t="n"/>
       <c r="B760" s="62" t="n"/>
       <c r="C760" s="62" t="n"/>
@@ -26590,7 +26584,7 @@
       <c r="I760" s="61" t="n"/>
       <c r="J760" s="61" t="n"/>
     </row>
-    <row r="761" ht="18" customHeight="1" s="125">
+    <row r="761" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A761" s="62" t="n"/>
       <c r="B761" s="62" t="n"/>
       <c r="C761" s="62" t="n"/>
@@ -26602,7 +26596,7 @@
       <c r="I761" s="61" t="n"/>
       <c r="J761" s="61" t="n"/>
     </row>
-    <row r="762" ht="18" customHeight="1" s="125">
+    <row r="762" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A762" s="62" t="n"/>
       <c r="B762" s="62" t="n"/>
       <c r="C762" s="62" t="n"/>
@@ -26614,7 +26608,7 @@
       <c r="I762" s="61" t="n"/>
       <c r="J762" s="61" t="n"/>
     </row>
-    <row r="763" ht="18" customHeight="1" s="125">
+    <row r="763" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A763" s="62" t="n"/>
       <c r="B763" s="62" t="n"/>
       <c r="C763" s="62" t="n"/>
@@ -26626,7 +26620,7 @@
       <c r="I763" s="61" t="n"/>
       <c r="J763" s="61" t="n"/>
     </row>
-    <row r="764" ht="18" customHeight="1" s="125">
+    <row r="764" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A764" s="62" t="n"/>
       <c r="B764" s="62" t="n"/>
       <c r="C764" s="62" t="n"/>
@@ -26638,7 +26632,7 @@
       <c r="I764" s="61" t="n"/>
       <c r="J764" s="61" t="n"/>
     </row>
-    <row r="765" ht="18" customHeight="1" s="125">
+    <row r="765" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A765" s="62" t="n"/>
       <c r="B765" s="62" t="n"/>
       <c r="C765" s="62" t="n"/>
@@ -26650,7 +26644,7 @@
       <c r="I765" s="61" t="n"/>
       <c r="J765" s="61" t="n"/>
     </row>
-    <row r="766" ht="18" customHeight="1" s="125">
+    <row r="766" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A766" s="62" t="n"/>
       <c r="B766" s="62" t="n"/>
       <c r="C766" s="62" t="n"/>
@@ -26662,7 +26656,7 @@
       <c r="I766" s="61" t="n"/>
       <c r="J766" s="61" t="n"/>
     </row>
-    <row r="767" ht="18" customHeight="1" s="125">
+    <row r="767" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A767" s="62" t="n"/>
       <c r="B767" s="62" t="n"/>
       <c r="C767" s="62" t="n"/>
@@ -26674,7 +26668,7 @@
       <c r="I767" s="61" t="n"/>
       <c r="J767" s="61" t="n"/>
     </row>
-    <row r="768" ht="18" customHeight="1" s="125">
+    <row r="768" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A768" s="62" t="n"/>
       <c r="B768" s="62" t="n"/>
       <c r="C768" s="62" t="n"/>
@@ -26686,7 +26680,7 @@
       <c r="I768" s="61" t="n"/>
       <c r="J768" s="61" t="n"/>
     </row>
-    <row r="769" ht="18" customHeight="1" s="125">
+    <row r="769" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A769" s="62" t="n"/>
       <c r="B769" s="62" t="n"/>
       <c r="C769" s="62" t="n"/>
@@ -26698,7 +26692,7 @@
       <c r="I769" s="61" t="n"/>
       <c r="J769" s="61" t="n"/>
     </row>
-    <row r="770" ht="18" customHeight="1" s="125">
+    <row r="770" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A770" s="62" t="n"/>
       <c r="B770" s="62" t="n"/>
       <c r="C770" s="62" t="n"/>
@@ -26710,7 +26704,7 @@
       <c r="I770" s="61" t="n"/>
       <c r="J770" s="61" t="n"/>
     </row>
-    <row r="771" ht="18" customHeight="1" s="125">
+    <row r="771" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A771" s="62" t="n"/>
       <c r="B771" s="62" t="n"/>
       <c r="C771" s="62" t="n"/>
@@ -26722,7 +26716,7 @@
       <c r="I771" s="61" t="n"/>
       <c r="J771" s="61" t="n"/>
     </row>
-    <row r="772" ht="18" customHeight="1" s="125">
+    <row r="772" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A772" s="62" t="n"/>
       <c r="B772" s="62" t="n"/>
       <c r="C772" s="62" t="n"/>
@@ -26734,7 +26728,7 @@
       <c r="I772" s="61" t="n"/>
       <c r="J772" s="61" t="n"/>
     </row>
-    <row r="773" ht="18" customHeight="1" s="125">
+    <row r="773" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A773" s="62" t="n"/>
       <c r="B773" s="62" t="n"/>
       <c r="C773" s="62" t="n"/>
@@ -26746,7 +26740,7 @@
       <c r="I773" s="61" t="n"/>
       <c r="J773" s="61" t="n"/>
     </row>
-    <row r="774" ht="18" customHeight="1" s="125">
+    <row r="774" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A774" s="62" t="n"/>
       <c r="B774" s="62" t="n"/>
       <c r="C774" s="62" t="n"/>
@@ -26758,7 +26752,7 @@
       <c r="I774" s="61" t="n"/>
       <c r="J774" s="61" t="n"/>
     </row>
-    <row r="775" ht="18" customHeight="1" s="125">
+    <row r="775" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A775" s="62" t="n"/>
       <c r="B775" s="62" t="n"/>
       <c r="C775" s="62" t="n"/>
@@ -26770,7 +26764,7 @@
       <c r="I775" s="61" t="n"/>
       <c r="J775" s="61" t="n"/>
     </row>
-    <row r="776" ht="18" customHeight="1" s="125">
+    <row r="776" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A776" s="62" t="n"/>
       <c r="B776" s="62" t="n"/>
       <c r="C776" s="62" t="n"/>
@@ -26782,7 +26776,7 @@
       <c r="I776" s="61" t="n"/>
       <c r="J776" s="61" t="n"/>
     </row>
-    <row r="777" ht="18" customHeight="1" s="125">
+    <row r="777" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A777" s="62" t="n"/>
       <c r="B777" s="62" t="n"/>
       <c r="C777" s="62" t="n"/>
@@ -26794,7 +26788,7 @@
       <c r="I777" s="61" t="n"/>
       <c r="J777" s="61" t="n"/>
     </row>
-    <row r="778" ht="18" customHeight="1" s="125">
+    <row r="778" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A778" s="62" t="n"/>
       <c r="B778" s="62" t="n"/>
       <c r="C778" s="62" t="n"/>
@@ -26806,7 +26800,7 @@
       <c r="I778" s="61" t="n"/>
       <c r="J778" s="61" t="n"/>
     </row>
-    <row r="779" ht="18" customHeight="1" s="125">
+    <row r="779" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A779" s="62" t="n"/>
       <c r="B779" s="62" t="n"/>
       <c r="C779" s="62" t="n"/>
@@ -26818,7 +26812,7 @@
       <c r="I779" s="61" t="n"/>
       <c r="J779" s="61" t="n"/>
     </row>
-    <row r="780" ht="18" customHeight="1" s="125">
+    <row r="780" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A780" s="62" t="n"/>
       <c r="B780" s="62" t="n"/>
       <c r="C780" s="62" t="n"/>
@@ -26830,7 +26824,7 @@
       <c r="I780" s="61" t="n"/>
       <c r="J780" s="61" t="n"/>
     </row>
-    <row r="781" ht="18" customHeight="1" s="125">
+    <row r="781" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A781" s="62" t="n"/>
       <c r="B781" s="62" t="n"/>
       <c r="C781" s="62" t="n"/>
@@ -26842,7 +26836,7 @@
       <c r="I781" s="61" t="n"/>
       <c r="J781" s="61" t="n"/>
     </row>
-    <row r="782" ht="18" customHeight="1" s="125">
+    <row r="782" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A782" s="62" t="n"/>
       <c r="B782" s="62" t="n"/>
       <c r="C782" s="62" t="n"/>
@@ -26854,7 +26848,7 @@
       <c r="I782" s="61" t="n"/>
       <c r="J782" s="61" t="n"/>
     </row>
-    <row r="783" ht="18" customHeight="1" s="125">
+    <row r="783" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A783" s="62" t="n"/>
       <c r="B783" s="62" t="n"/>
       <c r="C783" s="62" t="n"/>
@@ -26866,7 +26860,7 @@
       <c r="I783" s="61" t="n"/>
       <c r="J783" s="61" t="n"/>
     </row>
-    <row r="784" ht="18" customHeight="1" s="125">
+    <row r="784" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A784" s="62" t="n"/>
       <c r="B784" s="62" t="n"/>
       <c r="C784" s="62" t="n"/>
@@ -26878,7 +26872,7 @@
       <c r="I784" s="61" t="n"/>
       <c r="J784" s="61" t="n"/>
     </row>
-    <row r="785" ht="18" customHeight="1" s="125">
+    <row r="785" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A785" s="62" t="n"/>
       <c r="B785" s="62" t="n"/>
       <c r="C785" s="62" t="n"/>
@@ -26890,7 +26884,7 @@
       <c r="I785" s="61" t="n"/>
       <c r="J785" s="61" t="n"/>
     </row>
-    <row r="786" ht="18" customHeight="1" s="125">
+    <row r="786" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A786" s="62" t="n"/>
       <c r="B786" s="62" t="n"/>
       <c r="C786" s="62" t="n"/>
@@ -26902,7 +26896,7 @@
       <c r="I786" s="61" t="n"/>
       <c r="J786" s="61" t="n"/>
     </row>
-    <row r="787" ht="18" customHeight="1" s="125">
+    <row r="787" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A787" s="62" t="n"/>
       <c r="B787" s="62" t="n"/>
       <c r="C787" s="62" t="n"/>
@@ -26914,7 +26908,7 @@
       <c r="I787" s="61" t="n"/>
       <c r="J787" s="61" t="n"/>
     </row>
-    <row r="788" ht="18" customHeight="1" s="125">
+    <row r="788" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A788" s="62" t="n"/>
       <c r="B788" s="62" t="n"/>
       <c r="C788" s="62" t="n"/>
@@ -26926,7 +26920,7 @@
       <c r="I788" s="61" t="n"/>
       <c r="J788" s="61" t="n"/>
     </row>
-    <row r="789" ht="18" customHeight="1" s="125">
+    <row r="789" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A789" s="62" t="n"/>
       <c r="B789" s="62" t="n"/>
       <c r="C789" s="62" t="n"/>
@@ -26938,7 +26932,7 @@
       <c r="I789" s="61" t="n"/>
       <c r="J789" s="61" t="n"/>
     </row>
-    <row r="790" ht="18" customHeight="1" s="125">
+    <row r="790" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A790" s="62" t="n"/>
       <c r="B790" s="62" t="n"/>
       <c r="C790" s="62" t="n"/>
@@ -26950,7 +26944,7 @@
       <c r="I790" s="61" t="n"/>
       <c r="J790" s="61" t="n"/>
     </row>
-    <row r="791" ht="18" customHeight="1" s="125">
+    <row r="791" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A791" s="62" t="n"/>
       <c r="B791" s="62" t="n"/>
       <c r="C791" s="62" t="n"/>
@@ -26962,7 +26956,7 @@
       <c r="I791" s="61" t="n"/>
       <c r="J791" s="61" t="n"/>
     </row>
-    <row r="792" ht="18" customHeight="1" s="125">
+    <row r="792" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A792" s="62" t="n"/>
       <c r="B792" s="62" t="n"/>
       <c r="C792" s="62" t="n"/>
@@ -26974,7 +26968,7 @@
       <c r="I792" s="61" t="n"/>
       <c r="J792" s="61" t="n"/>
     </row>
-    <row r="793" ht="18" customHeight="1" s="125">
+    <row r="793" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A793" s="62" t="n"/>
       <c r="B793" s="62" t="n"/>
       <c r="C793" s="62" t="n"/>
@@ -26986,7 +26980,7 @@
       <c r="I793" s="61" t="n"/>
       <c r="J793" s="61" t="n"/>
     </row>
-    <row r="794" ht="18" customHeight="1" s="125">
+    <row r="794" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A794" s="62" t="n"/>
       <c r="B794" s="62" t="n"/>
       <c r="C794" s="62" t="n"/>
@@ -26998,7 +26992,7 @@
       <c r="I794" s="61" t="n"/>
       <c r="J794" s="61" t="n"/>
     </row>
-    <row r="795" ht="18" customHeight="1" s="125">
+    <row r="795" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A795" s="62" t="n"/>
       <c r="B795" s="62" t="n"/>
       <c r="C795" s="62" t="n"/>
@@ -27010,7 +27004,7 @@
       <c r="I795" s="61" t="n"/>
       <c r="J795" s="61" t="n"/>
     </row>
-    <row r="796" ht="18" customHeight="1" s="125">
+    <row r="796" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A796" s="62" t="n"/>
       <c r="B796" s="62" t="n"/>
       <c r="C796" s="62" t="n"/>
@@ -27022,7 +27016,7 @@
       <c r="I796" s="61" t="n"/>
       <c r="J796" s="61" t="n"/>
     </row>
-    <row r="797" ht="18" customHeight="1" s="125">
+    <row r="797" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A797" s="62" t="n"/>
       <c r="B797" s="62" t="n"/>
       <c r="C797" s="62" t="n"/>
@@ -27034,7 +27028,7 @@
       <c r="I797" s="61" t="n"/>
       <c r="J797" s="61" t="n"/>
     </row>
-    <row r="798" ht="18" customHeight="1" s="125">
+    <row r="798" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A798" s="62" t="n"/>
       <c r="B798" s="62" t="n"/>
       <c r="C798" s="62" t="n"/>
@@ -27046,7 +27040,7 @@
       <c r="I798" s="61" t="n"/>
       <c r="J798" s="61" t="n"/>
     </row>
-    <row r="799" ht="18" customHeight="1" s="125">
+    <row r="799" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A799" s="62" t="n"/>
       <c r="B799" s="62" t="n"/>
       <c r="C799" s="62" t="n"/>
@@ -27058,7 +27052,7 @@
       <c r="I799" s="61" t="n"/>
       <c r="J799" s="61" t="n"/>
     </row>
-    <row r="800" ht="18" customHeight="1" s="125">
+    <row r="800" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A800" s="62" t="n"/>
       <c r="B800" s="62" t="n"/>
       <c r="C800" s="62" t="n"/>
@@ -27070,7 +27064,7 @@
       <c r="I800" s="61" t="n"/>
       <c r="J800" s="61" t="n"/>
     </row>
-    <row r="801" ht="18" customHeight="1" s="125">
+    <row r="801" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A801" s="62" t="n"/>
       <c r="B801" s="62" t="n"/>
       <c r="C801" s="62" t="n"/>
@@ -27082,7 +27076,7 @@
       <c r="I801" s="61" t="n"/>
       <c r="J801" s="61" t="n"/>
     </row>
-    <row r="802" ht="18" customHeight="1" s="125">
+    <row r="802" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A802" s="62" t="n"/>
       <c r="B802" s="62" t="n"/>
       <c r="C802" s="62" t="n"/>
@@ -27094,7 +27088,7 @@
       <c r="I802" s="61" t="n"/>
       <c r="J802" s="61" t="n"/>
     </row>
-    <row r="803" ht="18" customHeight="1" s="125">
+    <row r="803" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A803" s="62" t="n"/>
       <c r="B803" s="62" t="n"/>
       <c r="C803" s="62" t="n"/>
@@ -27106,7 +27100,7 @@
       <c r="I803" s="61" t="n"/>
       <c r="J803" s="61" t="n"/>
     </row>
-    <row r="804" ht="18" customHeight="1" s="125">
+    <row r="804" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A804" s="62" t="n"/>
       <c r="B804" s="62" t="n"/>
       <c r="C804" s="62" t="n"/>
@@ -27118,7 +27112,7 @@
       <c r="I804" s="61" t="n"/>
       <c r="J804" s="61" t="n"/>
     </row>
-    <row r="805" ht="18" customHeight="1" s="125">
+    <row r="805" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A805" s="62" t="n"/>
       <c r="B805" s="62" t="n"/>
       <c r="C805" s="62" t="n"/>
@@ -27130,7 +27124,7 @@
       <c r="I805" s="61" t="n"/>
       <c r="J805" s="61" t="n"/>
     </row>
-    <row r="806" ht="18" customHeight="1" s="125">
+    <row r="806" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A806" s="62" t="n"/>
       <c r="B806" s="62" t="n"/>
       <c r="C806" s="62" t="n"/>
@@ -27142,7 +27136,7 @@
       <c r="I806" s="61" t="n"/>
       <c r="J806" s="61" t="n"/>
     </row>
-    <row r="807" ht="18" customHeight="1" s="125">
+    <row r="807" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A807" s="62" t="n"/>
       <c r="B807" s="62" t="n"/>
       <c r="C807" s="62" t="n"/>
@@ -27154,7 +27148,7 @@
       <c r="I807" s="61" t="n"/>
       <c r="J807" s="61" t="n"/>
     </row>
-    <row r="808" ht="18" customHeight="1" s="125">
+    <row r="808" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A808" s="62" t="n"/>
       <c r="B808" s="62" t="n"/>
       <c r="C808" s="62" t="n"/>
@@ -27166,7 +27160,7 @@
       <c r="I808" s="61" t="n"/>
       <c r="J808" s="61" t="n"/>
     </row>
-    <row r="809" ht="18" customHeight="1" s="125">
+    <row r="809" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A809" s="62" t="n"/>
       <c r="B809" s="62" t="n"/>
       <c r="C809" s="62" t="n"/>
@@ -27178,7 +27172,7 @@
       <c r="I809" s="61" t="n"/>
       <c r="J809" s="61" t="n"/>
     </row>
-    <row r="810" ht="18" customHeight="1" s="125">
+    <row r="810" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A810" s="62" t="n"/>
       <c r="B810" s="62" t="n"/>
       <c r="C810" s="62" t="n"/>
@@ -27190,7 +27184,7 @@
       <c r="I810" s="61" t="n"/>
       <c r="J810" s="61" t="n"/>
     </row>
-    <row r="811" ht="18" customHeight="1" s="125">
+    <row r="811" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A811" s="62" t="n"/>
       <c r="B811" s="62" t="n"/>
       <c r="C811" s="62" t="n"/>
@@ -27202,7 +27196,7 @@
       <c r="I811" s="61" t="n"/>
       <c r="J811" s="61" t="n"/>
     </row>
-    <row r="812" ht="18" customHeight="1" s="125">
+    <row r="812" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A812" s="62" t="n"/>
       <c r="B812" s="62" t="n"/>
       <c r="C812" s="62" t="n"/>
@@ -27214,7 +27208,7 @@
       <c r="I812" s="61" t="n"/>
       <c r="J812" s="61" t="n"/>
     </row>
-    <row r="813" ht="18" customHeight="1" s="125">
+    <row r="813" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A813" s="62" t="n"/>
       <c r="B813" s="62" t="n"/>
       <c r="C813" s="62" t="n"/>
@@ -27226,7 +27220,7 @@
       <c r="I813" s="61" t="n"/>
       <c r="J813" s="61" t="n"/>
     </row>
-    <row r="814" ht="18" customHeight="1" s="125">
+    <row r="814" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A814" s="62" t="n"/>
       <c r="B814" s="62" t="n"/>
       <c r="C814" s="62" t="n"/>
@@ -27238,7 +27232,7 @@
       <c r="I814" s="61" t="n"/>
       <c r="J814" s="61" t="n"/>
     </row>
-    <row r="815" ht="18" customHeight="1" s="125">
+    <row r="815" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A815" s="62" t="n"/>
       <c r="B815" s="62" t="n"/>
       <c r="C815" s="62" t="n"/>
@@ -27250,7 +27244,7 @@
       <c r="I815" s="61" t="n"/>
       <c r="J815" s="61" t="n"/>
     </row>
-    <row r="816" ht="18" customHeight="1" s="125">
+    <row r="816" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A816" s="62" t="n"/>
       <c r="B816" s="62" t="n"/>
       <c r="C816" s="62" t="n"/>
@@ -27262,7 +27256,7 @@
       <c r="I816" s="61" t="n"/>
       <c r="J816" s="61" t="n"/>
     </row>
-    <row r="817" ht="18" customHeight="1" s="125">
+    <row r="817" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A817" s="62" t="n"/>
       <c r="B817" s="62" t="n"/>
       <c r="C817" s="62" t="n"/>
@@ -27274,7 +27268,7 @@
       <c r="I817" s="61" t="n"/>
       <c r="J817" s="61" t="n"/>
     </row>
-    <row r="818" ht="18" customHeight="1" s="125">
+    <row r="818" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A818" s="62" t="n"/>
       <c r="B818" s="62" t="n"/>
       <c r="C818" s="62" t="n"/>
@@ -27286,7 +27280,7 @@
       <c r="I818" s="61" t="n"/>
       <c r="J818" s="61" t="n"/>
     </row>
-    <row r="819" ht="18" customHeight="1" s="125">
+    <row r="819" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A819" s="62" t="n"/>
       <c r="B819" s="62" t="n"/>
       <c r="C819" s="62" t="n"/>
@@ -27298,7 +27292,7 @@
       <c r="I819" s="61" t="n"/>
       <c r="J819" s="61" t="n"/>
     </row>
-    <row r="820" ht="18" customHeight="1" s="125">
+    <row r="820" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A820" s="62" t="n"/>
       <c r="B820" s="62" t="n"/>
       <c r="C820" s="62" t="n"/>
@@ -27310,7 +27304,7 @@
       <c r="I820" s="61" t="n"/>
       <c r="J820" s="61" t="n"/>
     </row>
-    <row r="821" ht="18" customHeight="1" s="125">
+    <row r="821" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A821" s="62" t="n"/>
       <c r="B821" s="62" t="n"/>
       <c r="C821" s="62" t="n"/>
@@ -27322,7 +27316,7 @@
       <c r="I821" s="61" t="n"/>
       <c r="J821" s="61" t="n"/>
     </row>
-    <row r="822" ht="18" customHeight="1" s="125">
+    <row r="822" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A822" s="62" t="n"/>
       <c r="B822" s="62" t="n"/>
       <c r="C822" s="62" t="n"/>
@@ -27334,7 +27328,7 @@
       <c r="I822" s="61" t="n"/>
       <c r="J822" s="61" t="n"/>
     </row>
-    <row r="823" ht="18" customHeight="1" s="125">
+    <row r="823" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A823" s="62" t="n"/>
       <c r="B823" s="62" t="n"/>
       <c r="C823" s="62" t="n"/>
@@ -27346,7 +27340,7 @@
       <c r="I823" s="61" t="n"/>
       <c r="J823" s="61" t="n"/>
     </row>
-    <row r="824" ht="18" customHeight="1" s="125">
+    <row r="824" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A824" s="62" t="n"/>
       <c r="B824" s="62" t="n"/>
       <c r="C824" s="62" t="n"/>
@@ -27358,7 +27352,7 @@
       <c r="I824" s="61" t="n"/>
       <c r="J824" s="61" t="n"/>
     </row>
-    <row r="825" ht="18" customHeight="1" s="125">
+    <row r="825" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A825" s="62" t="n"/>
       <c r="B825" s="62" t="n"/>
       <c r="C825" s="62" t="n"/>
@@ -27370,7 +27364,7 @@
       <c r="I825" s="61" t="n"/>
       <c r="J825" s="61" t="n"/>
     </row>
-    <row r="826" ht="18" customHeight="1" s="125">
+    <row r="826" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A826" s="62" t="n"/>
       <c r="B826" s="62" t="n"/>
       <c r="C826" s="62" t="n"/>
@@ -27382,7 +27376,7 @@
       <c r="I826" s="61" t="n"/>
       <c r="J826" s="61" t="n"/>
     </row>
-    <row r="827" ht="18" customHeight="1" s="125">
+    <row r="827" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A827" s="62" t="n"/>
       <c r="B827" s="62" t="n"/>
       <c r="C827" s="62" t="n"/>
@@ -27394,7 +27388,7 @@
       <c r="I827" s="61" t="n"/>
       <c r="J827" s="61" t="n"/>
     </row>
-    <row r="828" ht="18" customHeight="1" s="125">
+    <row r="828" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A828" s="62" t="n"/>
       <c r="B828" s="62" t="n"/>
       <c r="C828" s="62" t="n"/>
@@ -27406,7 +27400,7 @@
       <c r="I828" s="61" t="n"/>
       <c r="J828" s="61" t="n"/>
     </row>
-    <row r="829" ht="18" customHeight="1" s="125">
+    <row r="829" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A829" s="62" t="n"/>
       <c r="B829" s="62" t="n"/>
       <c r="C829" s="62" t="n"/>
@@ -27418,7 +27412,7 @@
       <c r="I829" s="61" t="n"/>
       <c r="J829" s="61" t="n"/>
     </row>
-    <row r="830" ht="18" customHeight="1" s="125">
+    <row r="830" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A830" s="62" t="n"/>
       <c r="B830" s="62" t="n"/>
       <c r="C830" s="62" t="n"/>
@@ -27430,7 +27424,7 @@
       <c r="I830" s="61" t="n"/>
       <c r="J830" s="61" t="n"/>
     </row>
-    <row r="831" ht="18" customHeight="1" s="125">
+    <row r="831" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A831" s="62" t="n"/>
       <c r="B831" s="62" t="n"/>
       <c r="C831" s="62" t="n"/>
@@ -27442,7 +27436,7 @@
       <c r="I831" s="61" t="n"/>
       <c r="J831" s="61" t="n"/>
     </row>
-    <row r="832" ht="18" customHeight="1" s="125">
+    <row r="832" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A832" s="62" t="n"/>
       <c r="B832" s="62" t="n"/>
       <c r="C832" s="62" t="n"/>
@@ -27454,7 +27448,7 @@
       <c r="I832" s="61" t="n"/>
       <c r="J832" s="61" t="n"/>
     </row>
-    <row r="833" ht="18" customHeight="1" s="125">
+    <row r="833" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A833" s="62" t="n"/>
       <c r="B833" s="62" t="n"/>
       <c r="C833" s="62" t="n"/>
@@ -27466,7 +27460,7 @@
       <c r="I833" s="61" t="n"/>
       <c r="J833" s="61" t="n"/>
     </row>
-    <row r="834" ht="18" customHeight="1" s="125">
+    <row r="834" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A834" s="62" t="n"/>
       <c r="B834" s="62" t="n"/>
       <c r="C834" s="62" t="n"/>
@@ -27478,7 +27472,7 @@
       <c r="I834" s="61" t="n"/>
       <c r="J834" s="61" t="n"/>
     </row>
-    <row r="835" ht="18" customHeight="1" s="125">
+    <row r="835" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A835" s="62" t="n"/>
       <c r="B835" s="62" t="n"/>
       <c r="C835" s="62" t="n"/>
@@ -27490,7 +27484,7 @@
       <c r="I835" s="61" t="n"/>
       <c r="J835" s="61" t="n"/>
     </row>
-    <row r="836" ht="18" customHeight="1" s="125">
+    <row r="836" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A836" s="62" t="n"/>
       <c r="B836" s="62" t="n"/>
       <c r="C836" s="62" t="n"/>
@@ -27502,7 +27496,7 @@
       <c r="I836" s="61" t="n"/>
       <c r="J836" s="61" t="n"/>
     </row>
-    <row r="837" ht="18" customHeight="1" s="125">
+    <row r="837" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A837" s="62" t="n"/>
       <c r="B837" s="62" t="n"/>
       <c r="C837" s="62" t="n"/>
@@ -27514,7 +27508,7 @@
       <c r="I837" s="61" t="n"/>
       <c r="J837" s="61" t="n"/>
     </row>
-    <row r="838" ht="18" customHeight="1" s="125">
+    <row r="838" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A838" s="62" t="n"/>
       <c r="B838" s="62" t="n"/>
       <c r="C838" s="62" t="n"/>
@@ -27526,7 +27520,7 @@
       <c r="I838" s="61" t="n"/>
       <c r="J838" s="61" t="n"/>
     </row>
-    <row r="839" ht="18" customHeight="1" s="125">
+    <row r="839" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A839" s="62" t="n"/>
       <c r="B839" s="62" t="n"/>
       <c r="C839" s="62" t="n"/>
@@ -27538,7 +27532,7 @@
       <c r="I839" s="61" t="n"/>
       <c r="J839" s="61" t="n"/>
     </row>
-    <row r="840" ht="18" customHeight="1" s="125">
+    <row r="840" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A840" s="62" t="n"/>
       <c r="B840" s="62" t="n"/>
       <c r="C840" s="62" t="n"/>
@@ -27550,7 +27544,7 @@
       <c r="I840" s="61" t="n"/>
       <c r="J840" s="61" t="n"/>
     </row>
-    <row r="841" ht="18" customHeight="1" s="125">
+    <row r="841" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A841" s="62" t="n"/>
       <c r="B841" s="62" t="n"/>
       <c r="C841" s="62" t="n"/>
@@ -27562,7 +27556,7 @@
       <c r="I841" s="61" t="n"/>
       <c r="J841" s="61" t="n"/>
     </row>
-    <row r="842" ht="18" customHeight="1" s="125">
+    <row r="842" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A842" s="62" t="n"/>
       <c r="B842" s="62" t="n"/>
       <c r="C842" s="62" t="n"/>
@@ -27574,7 +27568,7 @@
       <c r="I842" s="61" t="n"/>
       <c r="J842" s="61" t="n"/>
     </row>
-    <row r="843" ht="18" customHeight="1" s="125">
+    <row r="843" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A843" s="62" t="n"/>
       <c r="B843" s="62" t="n"/>
       <c r="C843" s="62" t="n"/>
@@ -27586,7 +27580,7 @@
       <c r="I843" s="61" t="n"/>
       <c r="J843" s="61" t="n"/>
     </row>
-    <row r="844" ht="18" customHeight="1" s="125">
+    <row r="844" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A844" s="62" t="n"/>
       <c r="B844" s="62" t="n"/>
       <c r="C844" s="62" t="n"/>
@@ -27598,7 +27592,7 @@
       <c r="I844" s="61" t="n"/>
       <c r="J844" s="61" t="n"/>
     </row>
-    <row r="845" ht="18" customHeight="1" s="125">
+    <row r="845" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A845" s="62" t="n"/>
       <c r="B845" s="62" t="n"/>
       <c r="C845" s="62" t="n"/>
@@ -27610,7 +27604,7 @@
       <c r="I845" s="61" t="n"/>
       <c r="J845" s="61" t="n"/>
     </row>
-    <row r="846" ht="18" customHeight="1" s="125">
+    <row r="846" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A846" s="62" t="n"/>
       <c r="B846" s="62" t="n"/>
       <c r="C846" s="62" t="n"/>
@@ -27622,7 +27616,7 @@
       <c r="I846" s="61" t="n"/>
       <c r="J846" s="61" t="n"/>
     </row>
-    <row r="847" ht="18" customHeight="1" s="125">
+    <row r="847" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A847" s="62" t="n"/>
       <c r="B847" s="62" t="n"/>
       <c r="C847" s="62" t="n"/>
@@ -27634,7 +27628,7 @@
       <c r="I847" s="61" t="n"/>
       <c r="J847" s="61" t="n"/>
     </row>
-    <row r="848" ht="18" customHeight="1" s="125">
+    <row r="848" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A848" s="62" t="n"/>
       <c r="B848" s="62" t="n"/>
       <c r="C848" s="62" t="n"/>
@@ -27646,7 +27640,7 @@
       <c r="I848" s="61" t="n"/>
       <c r="J848" s="61" t="n"/>
     </row>
-    <row r="849" ht="18" customHeight="1" s="125">
+    <row r="849" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A849" s="62" t="n"/>
       <c r="B849" s="62" t="n"/>
       <c r="C849" s="62" t="n"/>
@@ -27658,7 +27652,7 @@
       <c r="I849" s="61" t="n"/>
       <c r="J849" s="61" t="n"/>
     </row>
-    <row r="850" ht="18" customHeight="1" s="125">
+    <row r="850" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A850" s="62" t="n"/>
       <c r="B850" s="62" t="n"/>
       <c r="C850" s="62" t="n"/>
@@ -27670,7 +27664,7 @@
       <c r="I850" s="61" t="n"/>
       <c r="J850" s="61" t="n"/>
     </row>
-    <row r="851" ht="18" customHeight="1" s="125">
+    <row r="851" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A851" s="62" t="n"/>
       <c r="B851" s="62" t="n"/>
       <c r="C851" s="62" t="n"/>
@@ -27682,7 +27676,7 @@
       <c r="I851" s="61" t="n"/>
       <c r="J851" s="61" t="n"/>
     </row>
-    <row r="852" ht="18" customHeight="1" s="125">
+    <row r="852" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A852" s="62" t="n"/>
       <c r="B852" s="62" t="n"/>
       <c r="C852" s="62" t="n"/>
@@ -27694,7 +27688,7 @@
       <c r="I852" s="61" t="n"/>
       <c r="J852" s="61" t="n"/>
     </row>
-    <row r="853" ht="18" customHeight="1" s="125">
+    <row r="853" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A853" s="62" t="n"/>
       <c r="B853" s="62" t="n"/>
       <c r="C853" s="62" t="n"/>
@@ -27706,7 +27700,7 @@
       <c r="I853" s="61" t="n"/>
       <c r="J853" s="61" t="n"/>
     </row>
-    <row r="854" ht="18" customHeight="1" s="125">
+    <row r="854" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A854" s="62" t="n"/>
       <c r="B854" s="62" t="n"/>
       <c r="C854" s="62" t="n"/>
@@ -27718,7 +27712,7 @@
       <c r="I854" s="61" t="n"/>
       <c r="J854" s="61" t="n"/>
     </row>
-    <row r="855" ht="18" customHeight="1" s="125">
+    <row r="855" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A855" s="62" t="n"/>
       <c r="B855" s="62" t="n"/>
       <c r="C855" s="62" t="n"/>
@@ -27730,7 +27724,7 @@
       <c r="I855" s="61" t="n"/>
       <c r="J855" s="61" t="n"/>
     </row>
-    <row r="856" ht="18" customHeight="1" s="125">
+    <row r="856" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A856" s="62" t="n"/>
       <c r="B856" s="62" t="n"/>
       <c r="C856" s="62" t="n"/>
@@ -27742,7 +27736,7 @@
       <c r="I856" s="61" t="n"/>
       <c r="J856" s="61" t="n"/>
     </row>
-    <row r="857" ht="18" customHeight="1" s="125">
+    <row r="857" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A857" s="62" t="n"/>
       <c r="B857" s="62" t="n"/>
       <c r="C857" s="62" t="n"/>
@@ -27754,7 +27748,7 @@
       <c r="I857" s="61" t="n"/>
       <c r="J857" s="61" t="n"/>
     </row>
-    <row r="858" ht="18" customHeight="1" s="125">
+    <row r="858" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A858" s="62" t="n"/>
       <c r="B858" s="62" t="n"/>
       <c r="C858" s="62" t="n"/>
@@ -27766,7 +27760,7 @@
       <c r="I858" s="61" t="n"/>
       <c r="J858" s="61" t="n"/>
     </row>
-    <row r="859" ht="18" customHeight="1" s="125">
+    <row r="859" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A859" s="62" t="n"/>
       <c r="B859" s="62" t="n"/>
       <c r="C859" s="62" t="n"/>
@@ -27778,7 +27772,7 @@
       <c r="I859" s="61" t="n"/>
       <c r="J859" s="61" t="n"/>
     </row>
-    <row r="860" ht="18" customHeight="1" s="125">
+    <row r="860" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A860" s="62" t="n"/>
       <c r="B860" s="62" t="n"/>
       <c r="C860" s="62" t="n"/>
@@ -27790,7 +27784,7 @@
       <c r="I860" s="61" t="n"/>
       <c r="J860" s="61" t="n"/>
     </row>
-    <row r="861" ht="18" customHeight="1" s="125">
+    <row r="861" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A861" s="62" t="n"/>
       <c r="B861" s="62" t="n"/>
       <c r="C861" s="62" t="n"/>
@@ -27802,7 +27796,7 @@
       <c r="I861" s="61" t="n"/>
       <c r="J861" s="61" t="n"/>
     </row>
-    <row r="862" ht="18" customHeight="1" s="125">
+    <row r="862" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A862" s="62" t="n"/>
       <c r="B862" s="62" t="n"/>
       <c r="C862" s="62" t="n"/>
@@ -27814,7 +27808,7 @@
       <c r="I862" s="61" t="n"/>
       <c r="J862" s="61" t="n"/>
     </row>
-    <row r="863" ht="18" customHeight="1" s="125">
+    <row r="863" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A863" s="62" t="n"/>
       <c r="B863" s="62" t="n"/>
       <c r="C863" s="62" t="n"/>
@@ -27826,7 +27820,7 @@
       <c r="I863" s="61" t="n"/>
       <c r="J863" s="61" t="n"/>
     </row>
-    <row r="864" ht="18" customHeight="1" s="125">
+    <row r="864" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A864" s="62" t="n"/>
       <c r="B864" s="62" t="n"/>
       <c r="C864" s="62" t="n"/>
@@ -27838,7 +27832,7 @@
       <c r="I864" s="61" t="n"/>
       <c r="J864" s="61" t="n"/>
     </row>
-    <row r="865" ht="18" customHeight="1" s="125">
+    <row r="865" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A865" s="62" t="n"/>
       <c r="B865" s="62" t="n"/>
       <c r="C865" s="62" t="n"/>
@@ -27850,7 +27844,7 @@
       <c r="I865" s="61" t="n"/>
       <c r="J865" s="61" t="n"/>
     </row>
-    <row r="866" ht="18" customHeight="1" s="125">
+    <row r="866" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A866" s="62" t="n"/>
       <c r="B866" s="62" t="n"/>
       <c r="C866" s="62" t="n"/>
@@ -27862,7 +27856,7 @@
       <c r="I866" s="61" t="n"/>
       <c r="J866" s="61" t="n"/>
     </row>
-    <row r="867" ht="18" customHeight="1" s="125">
+    <row r="867" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A867" s="62" t="n"/>
       <c r="B867" s="62" t="n"/>
       <c r="C867" s="62" t="n"/>
@@ -27874,7 +27868,7 @@
       <c r="I867" s="61" t="n"/>
       <c r="J867" s="61" t="n"/>
     </row>
-    <row r="868" ht="18" customHeight="1" s="125">
+    <row r="868" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A868" s="62" t="n"/>
       <c r="B868" s="62" t="n"/>
       <c r="C868" s="62" t="n"/>
@@ -27886,7 +27880,7 @@
       <c r="I868" s="61" t="n"/>
       <c r="J868" s="61" t="n"/>
     </row>
-    <row r="869" ht="18" customHeight="1" s="125">
+    <row r="869" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A869" s="62" t="n"/>
       <c r="B869" s="62" t="n"/>
       <c r="C869" s="62" t="n"/>
@@ -27898,7 +27892,7 @@
       <c r="I869" s="61" t="n"/>
       <c r="J869" s="61" t="n"/>
     </row>
-    <row r="870" ht="18" customHeight="1" s="125">
+    <row r="870" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A870" s="62" t="n"/>
       <c r="B870" s="62" t="n"/>
       <c r="C870" s="62" t="n"/>
@@ -27910,7 +27904,7 @@
       <c r="I870" s="61" t="n"/>
       <c r="J870" s="61" t="n"/>
     </row>
-    <row r="871" ht="18" customHeight="1" s="125">
+    <row r="871" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A871" s="62" t="n"/>
       <c r="B871" s="62" t="n"/>
       <c r="C871" s="62" t="n"/>
@@ -27922,7 +27916,7 @@
       <c r="I871" s="61" t="n"/>
       <c r="J871" s="61" t="n"/>
     </row>
-    <row r="872" ht="18" customHeight="1" s="125">
+    <row r="872" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A872" s="62" t="n"/>
       <c r="B872" s="62" t="n"/>
       <c r="C872" s="62" t="n"/>
@@ -27934,7 +27928,7 @@
       <c r="I872" s="61" t="n"/>
       <c r="J872" s="61" t="n"/>
     </row>
-    <row r="873" ht="18" customHeight="1" s="125">
+    <row r="873" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A873" s="62" t="n"/>
       <c r="B873" s="62" t="n"/>
       <c r="C873" s="62" t="n"/>
@@ -27946,7 +27940,7 @@
       <c r="I873" s="61" t="n"/>
       <c r="J873" s="61" t="n"/>
     </row>
-    <row r="874" ht="18" customHeight="1" s="125">
+    <row r="874" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A874" s="62" t="n"/>
       <c r="B874" s="62" t="n"/>
       <c r="C874" s="62" t="n"/>
@@ -27958,7 +27952,7 @@
       <c r="I874" s="61" t="n"/>
       <c r="J874" s="61" t="n"/>
     </row>
-    <row r="875" ht="18" customHeight="1" s="125">
+    <row r="875" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A875" s="62" t="n"/>
       <c r="B875" s="62" t="n"/>
       <c r="C875" s="62" t="n"/>
@@ -27970,7 +27964,7 @@
       <c r="I875" s="61" t="n"/>
       <c r="J875" s="61" t="n"/>
     </row>
-    <row r="876" ht="18" customHeight="1" s="125">
+    <row r="876" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A876" s="62" t="n"/>
       <c r="B876" s="62" t="n"/>
       <c r="C876" s="62" t="n"/>
@@ -27982,7 +27976,7 @@
       <c r="I876" s="61" t="n"/>
       <c r="J876" s="61" t="n"/>
     </row>
-    <row r="877" ht="18" customHeight="1" s="125">
+    <row r="877" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A877" s="62" t="n"/>
       <c r="B877" s="62" t="n"/>
       <c r="C877" s="62" t="n"/>
@@ -27994,7 +27988,7 @@
       <c r="I877" s="61" t="n"/>
       <c r="J877" s="61" t="n"/>
     </row>
-    <row r="878" ht="18" customHeight="1" s="125">
+    <row r="878" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A878" s="62" t="n"/>
       <c r="B878" s="62" t="n"/>
       <c r="C878" s="62" t="n"/>
@@ -28006,7 +28000,7 @@
       <c r="I878" s="61" t="n"/>
       <c r="J878" s="61" t="n"/>
     </row>
-    <row r="879" ht="18" customHeight="1" s="125">
+    <row r="879" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A879" s="62" t="n"/>
       <c r="B879" s="62" t="n"/>
       <c r="C879" s="62" t="n"/>
@@ -28018,7 +28012,7 @@
       <c r="I879" s="61" t="n"/>
       <c r="J879" s="61" t="n"/>
     </row>
-    <row r="880" ht="18" customHeight="1" s="125">
+    <row r="880" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A880" s="62" t="n"/>
       <c r="B880" s="62" t="n"/>
       <c r="C880" s="62" t="n"/>
@@ -28030,7 +28024,7 @@
       <c r="I880" s="61" t="n"/>
       <c r="J880" s="61" t="n"/>
     </row>
-    <row r="881" ht="18" customHeight="1" s="125">
+    <row r="881" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A881" s="62" t="n"/>
       <c r="B881" s="62" t="n"/>
       <c r="C881" s="62" t="n"/>
@@ -28042,7 +28036,7 @@
       <c r="I881" s="61" t="n"/>
       <c r="J881" s="61" t="n"/>
     </row>
-    <row r="882" ht="18" customHeight="1" s="125">
+    <row r="882" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A882" s="62" t="n"/>
       <c r="B882" s="62" t="n"/>
       <c r="C882" s="62" t="n"/>
@@ -28054,7 +28048,7 @@
       <c r="I882" s="61" t="n"/>
       <c r="J882" s="61" t="n"/>
     </row>
-    <row r="883" ht="18" customHeight="1" s="125">
+    <row r="883" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A883" s="62" t="n"/>
       <c r="B883" s="62" t="n"/>
       <c r="C883" s="62" t="n"/>
@@ -28066,7 +28060,7 @@
       <c r="I883" s="61" t="n"/>
       <c r="J883" s="61" t="n"/>
     </row>
-    <row r="884" ht="18" customHeight="1" s="125">
+    <row r="884" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A884" s="62" t="n"/>
       <c r="B884" s="62" t="n"/>
       <c r="C884" s="62" t="n"/>
@@ -28078,7 +28072,7 @@
       <c r="I884" s="61" t="n"/>
       <c r="J884" s="61" t="n"/>
     </row>
-    <row r="885" ht="18" customHeight="1" s="125">
+    <row r="885" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A885" s="62" t="n"/>
       <c r="B885" s="62" t="n"/>
       <c r="C885" s="62" t="n"/>
@@ -28090,7 +28084,7 @@
       <c r="I885" s="61" t="n"/>
       <c r="J885" s="61" t="n"/>
     </row>
-    <row r="886" ht="18" customHeight="1" s="125">
+    <row r="886" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A886" s="62" t="n"/>
       <c r="B886" s="62" t="n"/>
       <c r="C886" s="62" t="n"/>
@@ -28102,7 +28096,7 @@
       <c r="I886" s="61" t="n"/>
       <c r="J886" s="61" t="n"/>
     </row>
-    <row r="887" ht="18" customHeight="1" s="125">
+    <row r="887" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A887" s="62" t="n"/>
       <c r="B887" s="62" t="n"/>
       <c r="C887" s="62" t="n"/>
@@ -28114,7 +28108,7 @@
       <c r="I887" s="61" t="n"/>
       <c r="J887" s="61" t="n"/>
     </row>
-    <row r="888" ht="18" customHeight="1" s="125">
+    <row r="888" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A888" s="62" t="n"/>
       <c r="B888" s="62" t="n"/>
       <c r="C888" s="62" t="n"/>
@@ -28126,7 +28120,7 @@
       <c r="I888" s="61" t="n"/>
       <c r="J888" s="61" t="n"/>
     </row>
-    <row r="889" ht="18" customHeight="1" s="125">
+    <row r="889" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A889" s="62" t="n"/>
       <c r="B889" s="62" t="n"/>
       <c r="C889" s="62" t="n"/>
@@ -28138,7 +28132,7 @@
       <c r="I889" s="61" t="n"/>
       <c r="J889" s="61" t="n"/>
     </row>
-    <row r="890" ht="18" customHeight="1" s="125">
+    <row r="890" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A890" s="62" t="n"/>
       <c r="B890" s="62" t="n"/>
       <c r="C890" s="62" t="n"/>
@@ -28150,7 +28144,7 @@
       <c r="I890" s="61" t="n"/>
       <c r="J890" s="61" t="n"/>
     </row>
-    <row r="891" ht="18" customHeight="1" s="125">
+    <row r="891" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A891" s="62" t="n"/>
       <c r="B891" s="62" t="n"/>
       <c r="C891" s="62" t="n"/>
@@ -28162,7 +28156,7 @@
       <c r="I891" s="61" t="n"/>
       <c r="J891" s="61" t="n"/>
     </row>
-    <row r="892" ht="18" customHeight="1" s="125">
+    <row r="892" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A892" s="62" t="n"/>
       <c r="B892" s="62" t="n"/>
       <c r="C892" s="62" t="n"/>
@@ -28174,7 +28168,7 @@
       <c r="I892" s="61" t="n"/>
       <c r="J892" s="61" t="n"/>
     </row>
-    <row r="893" ht="18" customHeight="1" s="125">
+    <row r="893" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A893" s="62" t="n"/>
       <c r="B893" s="62" t="n"/>
       <c r="C893" s="62" t="n"/>
@@ -28186,7 +28180,7 @@
       <c r="I893" s="61" t="n"/>
       <c r="J893" s="61" t="n"/>
     </row>
-    <row r="894" ht="18" customHeight="1" s="125">
+    <row r="894" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A894" s="62" t="n"/>
       <c r="B894" s="62" t="n"/>
       <c r="C894" s="62" t="n"/>
@@ -28198,7 +28192,7 @@
       <c r="I894" s="61" t="n"/>
       <c r="J894" s="61" t="n"/>
     </row>
-    <row r="895" ht="18" customHeight="1" s="125">
+    <row r="895" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A895" s="62" t="n"/>
       <c r="B895" s="62" t="n"/>
       <c r="C895" s="62" t="n"/>
@@ -28210,7 +28204,7 @@
       <c r="I895" s="61" t="n"/>
       <c r="J895" s="61" t="n"/>
     </row>
-    <row r="896" ht="18" customHeight="1" s="125">
+    <row r="896" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A896" s="62" t="n"/>
       <c r="B896" s="62" t="n"/>
       <c r="C896" s="62" t="n"/>
@@ -28222,7 +28216,7 @@
       <c r="I896" s="61" t="n"/>
       <c r="J896" s="61" t="n"/>
     </row>
-    <row r="897" ht="18" customHeight="1" s="125">
+    <row r="897" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A897" s="62" t="n"/>
       <c r="B897" s="62" t="n"/>
       <c r="C897" s="62" t="n"/>
@@ -28234,7 +28228,7 @@
       <c r="I897" s="61" t="n"/>
       <c r="J897" s="61" t="n"/>
     </row>
-    <row r="898" ht="18" customHeight="1" s="125">
+    <row r="898" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A898" s="62" t="n"/>
       <c r="B898" s="62" t="n"/>
       <c r="C898" s="62" t="n"/>
@@ -28246,7 +28240,7 @@
       <c r="I898" s="61" t="n"/>
       <c r="J898" s="61" t="n"/>
     </row>
-    <row r="899" ht="18" customHeight="1" s="125">
+    <row r="899" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A899" s="62" t="n"/>
       <c r="B899" s="62" t="n"/>
       <c r="C899" s="62" t="n"/>
@@ -28258,7 +28252,7 @@
       <c r="I899" s="61" t="n"/>
       <c r="J899" s="61" t="n"/>
     </row>
-    <row r="900" ht="18" customHeight="1" s="125">
+    <row r="900" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A900" s="62" t="n"/>
       <c r="B900" s="62" t="n"/>
       <c r="C900" s="62" t="n"/>
@@ -28270,7 +28264,7 @@
       <c r="I900" s="61" t="n"/>
       <c r="J900" s="61" t="n"/>
     </row>
-    <row r="901" ht="18" customHeight="1" s="125">
+    <row r="901" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A901" s="62" t="n"/>
       <c r="B901" s="62" t="n"/>
       <c r="C901" s="62" t="n"/>
@@ -28282,7 +28276,7 @@
       <c r="I901" s="61" t="n"/>
       <c r="J901" s="61" t="n"/>
     </row>
-    <row r="902" ht="18" customHeight="1" s="125">
+    <row r="902" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A902" s="62" t="n"/>
       <c r="B902" s="62" t="n"/>
       <c r="C902" s="62" t="n"/>
@@ -28294,7 +28288,7 @@
       <c r="I902" s="61" t="n"/>
       <c r="J902" s="61" t="n"/>
     </row>
-    <row r="903" ht="18" customHeight="1" s="125">
+    <row r="903" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A903" s="62" t="n"/>
       <c r="B903" s="62" t="n"/>
       <c r="C903" s="62" t="n"/>
@@ -28306,7 +28300,7 @@
       <c r="I903" s="61" t="n"/>
       <c r="J903" s="61" t="n"/>
     </row>
-    <row r="904" ht="18" customHeight="1" s="125">
+    <row r="904" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A904" s="62" t="n"/>
       <c r="B904" s="62" t="n"/>
       <c r="C904" s="62" t="n"/>
@@ -28318,7 +28312,7 @@
       <c r="I904" s="61" t="n"/>
       <c r="J904" s="61" t="n"/>
     </row>
-    <row r="905" ht="18" customHeight="1" s="125">
+    <row r="905" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A905" s="62" t="n"/>
       <c r="B905" s="62" t="n"/>
       <c r="C905" s="62" t="n"/>
@@ -28330,7 +28324,7 @@
       <c r="I905" s="61" t="n"/>
       <c r="J905" s="61" t="n"/>
     </row>
-    <row r="906" ht="18" customHeight="1" s="125">
+    <row r="906" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A906" s="62" t="n"/>
       <c r="B906" s="62" t="n"/>
       <c r="C906" s="62" t="n"/>
@@ -28342,7 +28336,7 @@
       <c r="I906" s="61" t="n"/>
       <c r="J906" s="61" t="n"/>
     </row>
-    <row r="907" ht="18" customHeight="1" s="125">
+    <row r="907" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A907" s="62" t="n"/>
       <c r="B907" s="62" t="n"/>
       <c r="C907" s="62" t="n"/>
@@ -28354,7 +28348,7 @@
       <c r="I907" s="61" t="n"/>
       <c r="J907" s="61" t="n"/>
     </row>
-    <row r="908" ht="18" customHeight="1" s="125">
+    <row r="908" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A908" s="62" t="n"/>
       <c r="B908" s="62" t="n"/>
       <c r="C908" s="62" t="n"/>
@@ -28366,7 +28360,7 @@
       <c r="I908" s="61" t="n"/>
       <c r="J908" s="61" t="n"/>
     </row>
-    <row r="909" ht="18" customHeight="1" s="125">
+    <row r="909" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A909" s="62" t="n"/>
       <c r="B909" s="62" t="n"/>
       <c r="C909" s="62" t="n"/>
@@ -28378,7 +28372,7 @@
       <c r="I909" s="61" t="n"/>
       <c r="J909" s="61" t="n"/>
     </row>
-    <row r="910" ht="18" customHeight="1" s="125">
+    <row r="910" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A910" s="62" t="n"/>
       <c r="B910" s="62" t="n"/>
       <c r="C910" s="62" t="n"/>
@@ -28390,7 +28384,7 @@
       <c r="I910" s="61" t="n"/>
       <c r="J910" s="61" t="n"/>
     </row>
-    <row r="911" ht="18" customHeight="1" s="125">
+    <row r="911" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A911" s="62" t="n"/>
       <c r="B911" s="62" t="n"/>
       <c r="C911" s="62" t="n"/>
@@ -28402,7 +28396,7 @@
       <c r="I911" s="61" t="n"/>
       <c r="J911" s="61" t="n"/>
     </row>
-    <row r="912" ht="18" customHeight="1" s="125">
+    <row r="912" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A912" s="62" t="n"/>
       <c r="B912" s="62" t="n"/>
       <c r="C912" s="62" t="n"/>
@@ -28414,7 +28408,7 @@
       <c r="I912" s="61" t="n"/>
       <c r="J912" s="61" t="n"/>
     </row>
-    <row r="913" ht="18" customHeight="1" s="125">
+    <row r="913" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A913" s="62" t="n"/>
       <c r="B913" s="62" t="n"/>
       <c r="C913" s="62" t="n"/>
@@ -28426,7 +28420,7 @@
       <c r="I913" s="61" t="n"/>
       <c r="J913" s="61" t="n"/>
     </row>
-    <row r="914" ht="18" customHeight="1" s="125">
+    <row r="914" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A914" s="62" t="n"/>
       <c r="B914" s="62" t="n"/>
       <c r="C914" s="62" t="n"/>
@@ -28438,7 +28432,7 @@
       <c r="I914" s="61" t="n"/>
       <c r="J914" s="61" t="n"/>
     </row>
-    <row r="915" ht="18" customHeight="1" s="125">
+    <row r="915" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A915" s="62" t="n"/>
       <c r="B915" s="62" t="n"/>
       <c r="C915" s="62" t="n"/>
@@ -28450,7 +28444,7 @@
       <c r="I915" s="61" t="n"/>
       <c r="J915" s="61" t="n"/>
     </row>
-    <row r="916" ht="18" customHeight="1" s="125">
+    <row r="916" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A916" s="62" t="n"/>
       <c r="B916" s="62" t="n"/>
       <c r="C916" s="62" t="n"/>
@@ -28462,7 +28456,7 @@
       <c r="I916" s="61" t="n"/>
       <c r="J916" s="61" t="n"/>
     </row>
-    <row r="917" ht="18" customHeight="1" s="125">
+    <row r="917" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A917" s="62" t="n"/>
       <c r="B917" s="62" t="n"/>
       <c r="C917" s="62" t="n"/>
@@ -28474,7 +28468,7 @@
       <c r="I917" s="61" t="n"/>
       <c r="J917" s="61" t="n"/>
     </row>
-    <row r="918" ht="18" customHeight="1" s="125">
+    <row r="918" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A918" s="62" t="n"/>
       <c r="B918" s="62" t="n"/>
       <c r="C918" s="62" t="n"/>
@@ -28486,7 +28480,7 @@
       <c r="I918" s="61" t="n"/>
       <c r="J918" s="61" t="n"/>
     </row>
-    <row r="919" ht="18" customHeight="1" s="125">
+    <row r="919" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A919" s="62" t="n"/>
       <c r="B919" s="62" t="n"/>
       <c r="C919" s="62" t="n"/>
@@ -28498,7 +28492,7 @@
       <c r="I919" s="61" t="n"/>
       <c r="J919" s="61" t="n"/>
     </row>
-    <row r="920" ht="18" customHeight="1" s="125">
+    <row r="920" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A920" s="62" t="n"/>
       <c r="B920" s="62" t="n"/>
       <c r="C920" s="62" t="n"/>
@@ -28510,7 +28504,7 @@
       <c r="I920" s="61" t="n"/>
       <c r="J920" s="61" t="n"/>
     </row>
-    <row r="921" ht="18" customHeight="1" s="125">
+    <row r="921" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A921" s="62" t="n"/>
       <c r="B921" s="62" t="n"/>
       <c r="C921" s="62" t="n"/>
@@ -28522,7 +28516,7 @@
       <c r="I921" s="61" t="n"/>
       <c r="J921" s="61" t="n"/>
     </row>
-    <row r="922" ht="18" customHeight="1" s="125">
+    <row r="922" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A922" s="62" t="n"/>
       <c r="B922" s="62" t="n"/>
       <c r="C922" s="62" t="n"/>
@@ -28534,7 +28528,7 @@
       <c r="I922" s="61" t="n"/>
       <c r="J922" s="61" t="n"/>
     </row>
-    <row r="923" ht="18" customHeight="1" s="125">
+    <row r="923" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A923" s="62" t="n"/>
       <c r="B923" s="62" t="n"/>
       <c r="C923" s="62" t="n"/>
@@ -28546,7 +28540,7 @@
       <c r="I923" s="61" t="n"/>
       <c r="J923" s="61" t="n"/>
     </row>
-    <row r="924" ht="18" customHeight="1" s="125">
+    <row r="924" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A924" s="62" t="n"/>
       <c r="B924" s="62" t="n"/>
       <c r="C924" s="62" t="n"/>
@@ -28558,7 +28552,7 @@
       <c r="I924" s="61" t="n"/>
       <c r="J924" s="61" t="n"/>
     </row>
-    <row r="925" ht="18" customHeight="1" s="125">
+    <row r="925" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A925" s="62" t="n"/>
       <c r="B925" s="62" t="n"/>
       <c r="C925" s="62" t="n"/>
@@ -28570,7 +28564,7 @@
       <c r="I925" s="61" t="n"/>
       <c r="J925" s="61" t="n"/>
     </row>
-    <row r="926" ht="18" customHeight="1" s="125">
+    <row r="926" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A926" s="62" t="n"/>
       <c r="B926" s="62" t="n"/>
       <c r="C926" s="62" t="n"/>
@@ -28582,7 +28576,7 @@
       <c r="I926" s="61" t="n"/>
       <c r="J926" s="61" t="n"/>
     </row>
-    <row r="927" ht="18" customHeight="1" s="125">
+    <row r="927" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A927" s="62" t="n"/>
       <c r="B927" s="62" t="n"/>
       <c r="C927" s="62" t="n"/>
@@ -28594,7 +28588,7 @@
       <c r="I927" s="61" t="n"/>
       <c r="J927" s="61" t="n"/>
     </row>
-    <row r="928" ht="18" customHeight="1" s="125">
+    <row r="928" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A928" s="62" t="n"/>
       <c r="B928" s="62" t="n"/>
       <c r="C928" s="62" t="n"/>
@@ -28606,7 +28600,7 @@
       <c r="I928" s="61" t="n"/>
       <c r="J928" s="61" t="n"/>
     </row>
-    <row r="929" ht="18" customHeight="1" s="125">
+    <row r="929" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A929" s="62" t="n"/>
       <c r="B929" s="62" t="n"/>
       <c r="C929" s="62" t="n"/>
@@ -28618,7 +28612,7 @@
       <c r="I929" s="61" t="n"/>
       <c r="J929" s="61" t="n"/>
     </row>
-    <row r="930" ht="18" customHeight="1" s="125">
+    <row r="930" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A930" s="62" t="n"/>
       <c r="B930" s="62" t="n"/>
       <c r="C930" s="62" t="n"/>
@@ -28630,7 +28624,7 @@
       <c r="I930" s="61" t="n"/>
       <c r="J930" s="61" t="n"/>
     </row>
-    <row r="931" ht="18" customHeight="1" s="125">
+    <row r="931" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A931" s="62" t="n"/>
       <c r="B931" s="62" t="n"/>
       <c r="C931" s="62" t="n"/>
@@ -28642,7 +28636,7 @@
       <c r="I931" s="61" t="n"/>
       <c r="J931" s="61" t="n"/>
     </row>
-    <row r="932" ht="18" customHeight="1" s="125">
+    <row r="932" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A932" s="62" t="n"/>
       <c r="B932" s="62" t="n"/>
       <c r="C932" s="62" t="n"/>
@@ -28654,7 +28648,7 @@
       <c r="I932" s="61" t="n"/>
       <c r="J932" s="61" t="n"/>
     </row>
-    <row r="933" ht="18" customHeight="1" s="125">
+    <row r="933" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A933" s="62" t="n"/>
       <c r="B933" s="62" t="n"/>
       <c r="C933" s="62" t="n"/>
@@ -28666,7 +28660,7 @@
       <c r="I933" s="61" t="n"/>
       <c r="J933" s="61" t="n"/>
     </row>
-    <row r="934" ht="18" customHeight="1" s="125">
+    <row r="934" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A934" s="62" t="n"/>
       <c r="B934" s="62" t="n"/>
       <c r="C934" s="62" t="n"/>
@@ -28678,7 +28672,7 @@
       <c r="I934" s="61" t="n"/>
       <c r="J934" s="61" t="n"/>
     </row>
-    <row r="935" ht="18" customHeight="1" s="125">
+    <row r="935" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A935" s="62" t="n"/>
       <c r="B935" s="62" t="n"/>
       <c r="C935" s="62" t="n"/>
@@ -28690,7 +28684,7 @@
       <c r="I935" s="61" t="n"/>
       <c r="J935" s="61" t="n"/>
     </row>
-    <row r="936" ht="18" customHeight="1" s="125">
+    <row r="936" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A936" s="62" t="n"/>
       <c r="B936" s="62" t="n"/>
       <c r="C936" s="62" t="n"/>
@@ -28702,7 +28696,7 @@
       <c r="I936" s="61" t="n"/>
       <c r="J936" s="61" t="n"/>
     </row>
-    <row r="937" ht="18" customHeight="1" s="125">
+    <row r="937" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A937" s="62" t="n"/>
       <c r="B937" s="62" t="n"/>
       <c r="C937" s="62" t="n"/>
@@ -28714,7 +28708,7 @@
       <c r="I937" s="61" t="n"/>
       <c r="J937" s="61" t="n"/>
     </row>
-    <row r="938" ht="18" customHeight="1" s="125">
+    <row r="938" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A938" s="62" t="n"/>
       <c r="B938" s="62" t="n"/>
       <c r="C938" s="62" t="n"/>
@@ -28726,7 +28720,7 @@
       <c r="I938" s="61" t="n"/>
       <c r="J938" s="61" t="n"/>
     </row>
-    <row r="939" ht="18" customHeight="1" s="125">
+    <row r="939" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A939" s="62" t="n"/>
       <c r="B939" s="62" t="n"/>
       <c r="C939" s="62" t="n"/>
@@ -28738,7 +28732,7 @@
       <c r="I939" s="61" t="n"/>
       <c r="J939" s="61" t="n"/>
     </row>
-    <row r="940" ht="18" customHeight="1" s="125">
+    <row r="940" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A940" s="62" t="n"/>
       <c r="B940" s="62" t="n"/>
       <c r="C940" s="62" t="n"/>
@@ -28750,7 +28744,7 @@
       <c r="I940" s="61" t="n"/>
       <c r="J940" s="61" t="n"/>
     </row>
-    <row r="941" ht="18" customHeight="1" s="125">
+    <row r="941" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A941" s="62" t="n"/>
       <c r="B941" s="62" t="n"/>
       <c r="C941" s="62" t="n"/>
@@ -28762,7 +28756,7 @@
       <c r="I941" s="61" t="n"/>
       <c r="J941" s="61" t="n"/>
     </row>
-    <row r="942" ht="18" customHeight="1" s="125">
+    <row r="942" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A942" s="62" t="n"/>
       <c r="B942" s="62" t="n"/>
       <c r="C942" s="62" t="n"/>
@@ -28774,7 +28768,7 @@
       <c r="I942" s="61" t="n"/>
       <c r="J942" s="61" t="n"/>
     </row>
-    <row r="943" ht="18" customHeight="1" s="125">
+    <row r="943" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A943" s="62" t="n"/>
       <c r="B943" s="62" t="n"/>
       <c r="C943" s="62" t="n"/>
@@ -28786,7 +28780,7 @@
       <c r="I943" s="61" t="n"/>
       <c r="J943" s="61" t="n"/>
     </row>
-    <row r="944" ht="18" customHeight="1" s="125">
+    <row r="944" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A944" s="62" t="n"/>
       <c r="B944" s="62" t="n"/>
       <c r="C944" s="62" t="n"/>
@@ -28798,7 +28792,7 @@
       <c r="I944" s="61" t="n"/>
       <c r="J944" s="61" t="n"/>
     </row>
-    <row r="945" ht="18" customHeight="1" s="125">
+    <row r="945" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A945" s="62" t="n"/>
       <c r="B945" s="62" t="n"/>
       <c r="C945" s="62" t="n"/>
@@ -28810,7 +28804,7 @@
       <c r="I945" s="61" t="n"/>
       <c r="J945" s="61" t="n"/>
     </row>
-    <row r="946" ht="18" customHeight="1" s="125">
+    <row r="946" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A946" s="62" t="n"/>
       <c r="B946" s="62" t="n"/>
       <c r="C946" s="62" t="n"/>
@@ -28822,7 +28816,7 @@
       <c r="I946" s="61" t="n"/>
       <c r="J946" s="61" t="n"/>
     </row>
-    <row r="947" ht="18" customHeight="1" s="125">
+    <row r="947" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A947" s="62" t="n"/>
       <c r="B947" s="62" t="n"/>
       <c r="C947" s="62" t="n"/>
@@ -28834,7 +28828,7 @@
       <c r="I947" s="61" t="n"/>
       <c r="J947" s="61" t="n"/>
     </row>
-    <row r="948" ht="18" customHeight="1" s="125">
+    <row r="948" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A948" s="62" t="n"/>
       <c r="B948" s="62" t="n"/>
       <c r="C948" s="62" t="n"/>
@@ -28846,7 +28840,7 @@
       <c r="I948" s="61" t="n"/>
       <c r="J948" s="61" t="n"/>
     </row>
-    <row r="949" ht="18" customHeight="1" s="125">
+    <row r="949" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A949" s="62" t="n"/>
       <c r="B949" s="62" t="n"/>
       <c r="C949" s="62" t="n"/>
@@ -28858,7 +28852,7 @@
       <c r="I949" s="61" t="n"/>
       <c r="J949" s="61" t="n"/>
     </row>
-    <row r="950" ht="18" customHeight="1" s="125">
+    <row r="950" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A950" s="62" t="n"/>
       <c r="B950" s="62" t="n"/>
       <c r="C950" s="62" t="n"/>
@@ -28870,7 +28864,7 @@
       <c r="I950" s="61" t="n"/>
       <c r="J950" s="61" t="n"/>
     </row>
-    <row r="951" ht="18" customHeight="1" s="125">
+    <row r="951" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A951" s="62" t="n"/>
       <c r="B951" s="62" t="n"/>
       <c r="C951" s="62" t="n"/>
@@ -28882,7 +28876,7 @@
       <c r="I951" s="61" t="n"/>
       <c r="J951" s="61" t="n"/>
     </row>
-    <row r="952" ht="18" customHeight="1" s="125">
+    <row r="952" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A952" s="62" t="n"/>
       <c r="B952" s="62" t="n"/>
       <c r="C952" s="62" t="n"/>
@@ -28894,7 +28888,7 @@
       <c r="I952" s="61" t="n"/>
       <c r="J952" s="61" t="n"/>
     </row>
-    <row r="953" ht="18" customHeight="1" s="125">
+    <row r="953" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A953" s="62" t="n"/>
       <c r="B953" s="62" t="n"/>
       <c r="C953" s="62" t="n"/>
@@ -28906,7 +28900,7 @@
       <c r="I953" s="61" t="n"/>
       <c r="J953" s="61" t="n"/>
     </row>
-    <row r="954" ht="18" customHeight="1" s="125">
+    <row r="954" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A954" s="62" t="n"/>
       <c r="B954" s="62" t="n"/>
       <c r="C954" s="62" t="n"/>
@@ -28918,7 +28912,7 @@
       <c r="I954" s="61" t="n"/>
       <c r="J954" s="61" t="n"/>
     </row>
-    <row r="955" ht="18" customHeight="1" s="125">
+    <row r="955" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A955" s="62" t="n"/>
       <c r="B955" s="62" t="n"/>
       <c r="C955" s="62" t="n"/>
@@ -28930,7 +28924,7 @@
       <c r="I955" s="61" t="n"/>
       <c r="J955" s="61" t="n"/>
     </row>
-    <row r="956" ht="18" customHeight="1" s="125">
+    <row r="956" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A956" s="62" t="n"/>
       <c r="B956" s="62" t="n"/>
       <c r="C956" s="62" t="n"/>
@@ -28942,7 +28936,7 @@
       <c r="I956" s="61" t="n"/>
       <c r="J956" s="61" t="n"/>
     </row>
-    <row r="957" ht="18" customHeight="1" s="125">
+    <row r="957" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A957" s="62" t="n"/>
       <c r="B957" s="62" t="n"/>
       <c r="C957" s="62" t="n"/>
@@ -28954,7 +28948,7 @@
       <c r="I957" s="61" t="n"/>
       <c r="J957" s="61" t="n"/>
     </row>
-    <row r="958" ht="18" customHeight="1" s="125">
+    <row r="958" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A958" s="62" t="n"/>
       <c r="B958" s="62" t="n"/>
       <c r="C958" s="62" t="n"/>
@@ -28966,7 +28960,7 @@
       <c r="I958" s="61" t="n"/>
       <c r="J958" s="61" t="n"/>
     </row>
-    <row r="959" ht="18" customHeight="1" s="125">
+    <row r="959" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A959" s="62" t="n"/>
       <c r="B959" s="62" t="n"/>
       <c r="C959" s="62" t="n"/>
@@ -28978,7 +28972,7 @@
       <c r="I959" s="61" t="n"/>
       <c r="J959" s="61" t="n"/>
     </row>
-    <row r="960" ht="18" customHeight="1" s="125">
+    <row r="960" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A960" s="62" t="n"/>
       <c r="B960" s="62" t="n"/>
       <c r="C960" s="62" t="n"/>
@@ -28990,7 +28984,7 @@
       <c r="I960" s="61" t="n"/>
       <c r="J960" s="61" t="n"/>
     </row>
-    <row r="961" ht="18" customHeight="1" s="125">
+    <row r="961" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A961" s="62" t="n"/>
       <c r="B961" s="62" t="n"/>
       <c r="C961" s="62" t="n"/>
@@ -29002,7 +28996,7 @@
       <c r="I961" s="61" t="n"/>
       <c r="J961" s="61" t="n"/>
     </row>
-    <row r="962" ht="18" customHeight="1" s="125">
+    <row r="962" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A962" s="62" t="n"/>
       <c r="B962" s="62" t="n"/>
       <c r="C962" s="62" t="n"/>
@@ -29014,7 +29008,7 @@
       <c r="I962" s="61" t="n"/>
       <c r="J962" s="61" t="n"/>
     </row>
-    <row r="963" ht="18" customHeight="1" s="125">
+    <row r="963" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A963" s="62" t="n"/>
       <c r="B963" s="62" t="n"/>
       <c r="C963" s="62" t="n"/>
@@ -29026,7 +29020,7 @@
       <c r="I963" s="61" t="n"/>
       <c r="J963" s="61" t="n"/>
     </row>
-    <row r="964" ht="18" customHeight="1" s="125">
+    <row r="964" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A964" s="62" t="n"/>
       <c r="B964" s="62" t="n"/>
       <c r="C964" s="62" t="n"/>
@@ -29038,7 +29032,7 @@
       <c r="I964" s="61" t="n"/>
       <c r="J964" s="61" t="n"/>
     </row>
-    <row r="965" ht="18" customHeight="1" s="125">
+    <row r="965" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A965" s="62" t="n"/>
       <c r="B965" s="62" t="n"/>
       <c r="C965" s="62" t="n"/>
@@ -29050,7 +29044,7 @@
       <c r="I965" s="61" t="n"/>
       <c r="J965" s="61" t="n"/>
     </row>
-    <row r="966" ht="18" customHeight="1" s="125">
+    <row r="966" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A966" s="62" t="n"/>
       <c r="B966" s="62" t="n"/>
       <c r="C966" s="62" t="n"/>
@@ -29062,7 +29056,7 @@
       <c r="I966" s="61" t="n"/>
       <c r="J966" s="61" t="n"/>
     </row>
-    <row r="967" ht="18" customHeight="1" s="125">
+    <row r="967" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A967" s="62" t="n"/>
       <c r="B967" s="62" t="n"/>
       <c r="C967" s="62" t="n"/>
@@ -29074,7 +29068,7 @@
       <c r="I967" s="61" t="n"/>
       <c r="J967" s="61" t="n"/>
     </row>
-    <row r="968" ht="18" customHeight="1" s="125">
+    <row r="968" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A968" s="62" t="n"/>
       <c r="B968" s="62" t="n"/>
       <c r="C968" s="62" t="n"/>
@@ -29086,7 +29080,7 @@
       <c r="I968" s="61" t="n"/>
       <c r="J968" s="61" t="n"/>
     </row>
-    <row r="969" ht="18" customHeight="1" s="125">
+    <row r="969" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A969" s="62" t="n"/>
       <c r="B969" s="62" t="n"/>
       <c r="C969" s="62" t="n"/>
@@ -29098,7 +29092,7 @@
       <c r="I969" s="61" t="n"/>
       <c r="J969" s="61" t="n"/>
     </row>
-    <row r="970" ht="18" customHeight="1" s="125">
+    <row r="970" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A970" s="62" t="n"/>
       <c r="B970" s="62" t="n"/>
       <c r="C970" s="62" t="n"/>
@@ -29110,7 +29104,7 @@
       <c r="I970" s="61" t="n"/>
       <c r="J970" s="61" t="n"/>
     </row>
-    <row r="971" ht="18" customHeight="1" s="125">
+    <row r="971" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A971" s="62" t="n"/>
       <c r="B971" s="62" t="n"/>
       <c r="C971" s="62" t="n"/>
@@ -29122,7 +29116,7 @@
       <c r="I971" s="61" t="n"/>
       <c r="J971" s="61" t="n"/>
     </row>
-    <row r="972" ht="18" customHeight="1" s="125">
+    <row r="972" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A972" s="62" t="n"/>
       <c r="B972" s="62" t="n"/>
       <c r="C972" s="62" t="n"/>
@@ -29134,7 +29128,7 @@
       <c r="I972" s="61" t="n"/>
       <c r="J972" s="61" t="n"/>
     </row>
-    <row r="973" ht="18" customHeight="1" s="125">
+    <row r="973" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A973" s="62" t="n"/>
       <c r="B973" s="62" t="n"/>
       <c r="C973" s="62" t="n"/>
@@ -29146,7 +29140,7 @@
       <c r="I973" s="61" t="n"/>
       <c r="J973" s="61" t="n"/>
     </row>
-    <row r="974" ht="18" customHeight="1" s="125">
+    <row r="974" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A974" s="62" t="n"/>
       <c r="B974" s="62" t="n"/>
       <c r="C974" s="62" t="n"/>
@@ -29158,7 +29152,7 @@
       <c r="I974" s="61" t="n"/>
       <c r="J974" s="61" t="n"/>
     </row>
-    <row r="975" ht="18" customHeight="1" s="125">
+    <row r="975" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A975" s="62" t="n"/>
       <c r="B975" s="62" t="n"/>
       <c r="C975" s="62" t="n"/>
@@ -29170,7 +29164,7 @@
       <c r="I975" s="61" t="n"/>
       <c r="J975" s="61" t="n"/>
     </row>
-    <row r="976" ht="18" customHeight="1" s="125">
+    <row r="976" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A976" s="62" t="n"/>
       <c r="B976" s="62" t="n"/>
       <c r="C976" s="62" t="n"/>
@@ -29182,7 +29176,7 @@
       <c r="I976" s="61" t="n"/>
       <c r="J976" s="61" t="n"/>
     </row>
-    <row r="977" ht="18" customHeight="1" s="125">
+    <row r="977" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A977" s="62" t="n"/>
       <c r="B977" s="62" t="n"/>
       <c r="C977" s="62" t="n"/>
@@ -29194,7 +29188,7 @@
       <c r="I977" s="61" t="n"/>
       <c r="J977" s="61" t="n"/>
     </row>
-    <row r="978" ht="18" customHeight="1" s="125">
+    <row r="978" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A978" s="62" t="n"/>
       <c r="B978" s="62" t="n"/>
       <c r="C978" s="62" t="n"/>
@@ -29206,7 +29200,7 @@
       <c r="I978" s="61" t="n"/>
       <c r="J978" s="61" t="n"/>
     </row>
-    <row r="979" ht="18" customHeight="1" s="125">
+    <row r="979" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A979" s="62" t="n"/>
       <c r="B979" s="62" t="n"/>
       <c r="C979" s="62" t="n"/>
@@ -29218,7 +29212,7 @@
       <c r="I979" s="61" t="n"/>
       <c r="J979" s="61" t="n"/>
     </row>
-    <row r="980" ht="18" customHeight="1" s="125">
+    <row r="980" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A980" s="62" t="n"/>
       <c r="B980" s="62" t="n"/>
       <c r="C980" s="62" t="n"/>
@@ -29230,7 +29224,7 @@
       <c r="I980" s="61" t="n"/>
       <c r="J980" s="61" t="n"/>
     </row>
-    <row r="981" ht="18" customHeight="1" s="125">
+    <row r="981" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A981" s="62" t="n"/>
       <c r="B981" s="62" t="n"/>
       <c r="C981" s="62" t="n"/>
@@ -29242,7 +29236,7 @@
       <c r="I981" s="61" t="n"/>
       <c r="J981" s="61" t="n"/>
     </row>
-    <row r="982" ht="18" customHeight="1" s="125">
+    <row r="982" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A982" s="62" t="n"/>
       <c r="B982" s="62" t="n"/>
       <c r="C982" s="62" t="n"/>
@@ -29254,7 +29248,7 @@
       <c r="I982" s="61" t="n"/>
       <c r="J982" s="61" t="n"/>
     </row>
-    <row r="983" ht="18" customHeight="1" s="125">
+    <row r="983" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A983" s="62" t="n"/>
       <c r="B983" s="62" t="n"/>
       <c r="C983" s="62" t="n"/>
@@ -29266,7 +29260,7 @@
       <c r="I983" s="61" t="n"/>
       <c r="J983" s="61" t="n"/>
     </row>
-    <row r="984" ht="18" customHeight="1" s="125">
+    <row r="984" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A984" s="62" t="n"/>
       <c r="B984" s="62" t="n"/>
       <c r="C984" s="62" t="n"/>
@@ -29278,7 +29272,7 @@
       <c r="I984" s="61" t="n"/>
       <c r="J984" s="61" t="n"/>
     </row>
-    <row r="985" ht="18" customHeight="1" s="125">
+    <row r="985" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A985" s="62" t="n"/>
       <c r="B985" s="62" t="n"/>
       <c r="C985" s="62" t="n"/>
@@ -29290,7 +29284,7 @@
       <c r="I985" s="61" t="n"/>
       <c r="J985" s="61" t="n"/>
     </row>
-    <row r="986" ht="18" customHeight="1" s="125">
+    <row r="986" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A986" s="62" t="n"/>
       <c r="B986" s="62" t="n"/>
       <c r="C986" s="62" t="n"/>
@@ -29302,7 +29296,7 @@
       <c r="I986" s="61" t="n"/>
       <c r="J986" s="61" t="n"/>
     </row>
-    <row r="987" ht="18" customHeight="1" s="125">
+    <row r="987" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A987" s="62" t="n"/>
       <c r="B987" s="62" t="n"/>
       <c r="C987" s="62" t="n"/>
@@ -29314,7 +29308,7 @@
       <c r="I987" s="61" t="n"/>
       <c r="J987" s="61" t="n"/>
     </row>
-    <row r="988" ht="18" customHeight="1" s="125">
+    <row r="988" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A988" s="62" t="n"/>
       <c r="B988" s="62" t="n"/>
       <c r="C988" s="62" t="n"/>
@@ -29326,7 +29320,7 @@
       <c r="I988" s="61" t="n"/>
       <c r="J988" s="61" t="n"/>
     </row>
-    <row r="989" ht="18" customHeight="1" s="125">
+    <row r="989" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A989" s="62" t="n"/>
       <c r="B989" s="62" t="n"/>
       <c r="C989" s="62" t="n"/>
@@ -29338,7 +29332,7 @@
       <c r="I989" s="61" t="n"/>
       <c r="J989" s="61" t="n"/>
     </row>
-    <row r="990" ht="18" customHeight="1" s="125">
+    <row r="990" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A990" s="62" t="n"/>
       <c r="B990" s="62" t="n"/>
       <c r="C990" s="62" t="n"/>
@@ -29350,7 +29344,7 @@
       <c r="I990" s="61" t="n"/>
       <c r="J990" s="61" t="n"/>
     </row>
-    <row r="991" ht="18" customHeight="1" s="125">
+    <row r="991" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A991" s="62" t="n"/>
       <c r="B991" s="62" t="n"/>
       <c r="C991" s="62" t="n"/>
@@ -29362,7 +29356,7 @@
       <c r="I991" s="61" t="n"/>
       <c r="J991" s="61" t="n"/>
     </row>
-    <row r="992" ht="18" customHeight="1" s="125">
+    <row r="992" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A992" s="62" t="n"/>
       <c r="B992" s="62" t="n"/>
       <c r="C992" s="62" t="n"/>
@@ -29374,7 +29368,7 @@
       <c r="I992" s="61" t="n"/>
       <c r="J992" s="61" t="n"/>
     </row>
-    <row r="993" ht="18" customHeight="1" s="125">
+    <row r="993" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A993" s="62" t="n"/>
       <c r="B993" s="62" t="n"/>
       <c r="C993" s="62" t="n"/>
@@ -29386,7 +29380,7 @@
       <c r="I993" s="61" t="n"/>
       <c r="J993" s="61" t="n"/>
     </row>
-    <row r="994" ht="18" customHeight="1" s="125">
+    <row r="994" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A994" s="62" t="n"/>
       <c r="B994" s="62" t="n"/>
       <c r="C994" s="62" t="n"/>
@@ -29398,7 +29392,7 @@
       <c r="I994" s="61" t="n"/>
       <c r="J994" s="61" t="n"/>
     </row>
-    <row r="995" ht="18" customHeight="1" s="125">
+    <row r="995" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A995" s="62" t="n"/>
       <c r="B995" s="62" t="n"/>
       <c r="C995" s="62" t="n"/>
@@ -29410,7 +29404,7 @@
       <c r="I995" s="61" t="n"/>
       <c r="J995" s="61" t="n"/>
     </row>
-    <row r="996" ht="18" customHeight="1" s="125">
+    <row r="996" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A996" s="62" t="n"/>
       <c r="B996" s="62" t="n"/>
       <c r="C996" s="62" t="n"/>
@@ -29422,7 +29416,7 @@
       <c r="I996" s="61" t="n"/>
       <c r="J996" s="61" t="n"/>
     </row>
-    <row r="997" ht="18" customHeight="1" s="125">
+    <row r="997" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A997" s="62" t="n"/>
       <c r="B997" s="62" t="n"/>
       <c r="C997" s="62" t="n"/>
@@ -29434,7 +29428,7 @@
       <c r="I997" s="61" t="n"/>
       <c r="J997" s="61" t="n"/>
     </row>
-    <row r="998" ht="18" customHeight="1" s="125">
+    <row r="998" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A998" s="62" t="n"/>
       <c r="B998" s="62" t="n"/>
       <c r="C998" s="62" t="n"/>
@@ -29446,7 +29440,7 @@
       <c r="I998" s="61" t="n"/>
       <c r="J998" s="61" t="n"/>
     </row>
-    <row r="999" ht="18" customHeight="1" s="125">
+    <row r="999" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A999" s="62" t="n"/>
       <c r="B999" s="62" t="n"/>
       <c r="C999" s="62" t="n"/>
@@ -29458,7 +29452,7 @@
       <c r="I999" s="61" t="n"/>
       <c r="J999" s="61" t="n"/>
     </row>
-    <row r="1000" ht="18" customHeight="1" s="125">
+    <row r="1000" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A1000" s="62" t="n"/>
       <c r="B1000" s="62" t="n"/>
       <c r="C1000" s="62" t="n"/>
@@ -29470,7 +29464,7 @@
       <c r="I1000" s="61" t="n"/>
       <c r="J1000" s="61" t="n"/>
     </row>
-    <row r="1001" ht="18" customHeight="1" s="125">
+    <row r="1001" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A1001" s="62" t="n"/>
       <c r="B1001" s="62" t="n"/>
       <c r="C1001" s="62" t="n"/>
@@ -29482,7 +29476,7 @@
       <c r="I1001" s="61" t="n"/>
       <c r="J1001" s="61" t="n"/>
     </row>
-    <row r="1002" ht="18" customHeight="1" s="125">
+    <row r="1002" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A1002" s="62" t="n"/>
       <c r="B1002" s="62" t="n"/>
       <c r="C1002" s="62" t="n"/>
@@ -29494,7 +29488,7 @@
       <c r="I1002" s="61" t="n"/>
       <c r="J1002" s="61" t="n"/>
     </row>
-    <row r="1003" ht="18" customHeight="1" s="125">
+    <row r="1003" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A1003" s="62" t="n"/>
       <c r="B1003" s="62" t="n"/>
       <c r="C1003" s="62" t="n"/>
@@ -29506,7 +29500,7 @@
       <c r="I1003" s="61" t="n"/>
       <c r="J1003" s="61" t="n"/>
     </row>
-    <row r="1004" ht="15.75" customHeight="1" s="125">
+    <row r="1004" hidden="1" ht="15.75" customHeight="1" s="125">
       <c r="A1004" s="5" t="n"/>
       <c r="B1004" s="6" t="n"/>
       <c r="C1004" s="7" t="n"/>
@@ -29779,25 +29773,25 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="125">
-      <c r="A1" s="110" t="inlineStr">
+      <c r="A1" s="117" t="inlineStr">
         <is>
           <t>📊  ASF C3-CHECK — WORK PACKAGE DASHBOARD</t>
         </is>
       </c>
-      <c r="I1" s="104">
+      <c r="I1" s="112">
         <f>"Day "&amp;TEXT(MAX(1,MIN(TODAY()-DATE(2026,6,8)+1,36)),"0")&amp;"/36"</f>
         <v/>
       </c>
     </row>
     <row r="2" ht="13.9" customHeight="1" s="125">
-      <c r="A2" s="118" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>All figures update automatically from ASF Tracker</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" s="125">
-      <c r="A3" s="112" t="inlineStr">
+      <c r="A3" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">  STATUS OVERVIEW</t>
         </is>
@@ -29865,7 +29859,7 @@
     </row>
     <row r="8" ht="4.15" customHeight="1" s="125"/>
     <row r="9" ht="18" customHeight="1" s="125">
-      <c r="A9" s="114" t="inlineStr">
+      <c r="A9" s="120" t="inlineStr">
         <is>
           <t xml:space="preserve">  PRIORITY ALERTS</t>
         </is>
@@ -29903,7 +29897,7 @@
     </row>
     <row r="12" ht="4.15" customHeight="1" s="125"/>
     <row r="13" ht="18" customHeight="1" s="125">
-      <c r="A13" s="112" t="inlineStr">
+      <c r="A13" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">  PARTS REQUIREMENTS  (count of WOs with each status)</t>
         </is>
@@ -29971,7 +29965,7 @@
     </row>
     <row r="18" ht="4.15" customHeight="1" s="125"/>
     <row r="19" ht="18" customHeight="1" s="125">
-      <c r="A19" s="112" t="inlineStr">
+      <c r="A19" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">  BY CATEGORY</t>
         </is>
@@ -30008,17 +30002,17 @@
       </c>
     </row>
     <row r="22" ht="14.45" customHeight="1" s="125">
-      <c r="B22" s="108">
+      <c r="B22" s="115">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TASK CARD",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TASK CARD"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="C22" s="128" t="n"/>
-      <c r="E22" s="117">
+      <c r="E22" s="106">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"LAVATORY",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"LAVATORY"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="F22" s="128" t="n"/>
-      <c r="H22" s="120">
+      <c r="H22" s="109">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"GALLEY",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"GALLEY"),"0%"),"-")</f>
         <v/>
       </c>
@@ -30059,17 +30053,17 @@
       </c>
     </row>
     <row r="25" ht="14.45" customHeight="1" s="125">
-      <c r="B25" s="106">
+      <c r="B25" s="111">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$D$4:$D$1004,"GENERAL CABIN",'ASF Tracker'!$E$4:$E$1004,"Closed",'ASF Tracker'!$B$4:$B$1004,"&lt;&gt;")/COUNTIFS('ASF Tracker'!$D$4:$D$1004,"GENERAL CABIN",'ASF Tracker'!$B$4:$B$1004,"&lt;&gt;"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="C25" s="128" t="n"/>
-      <c r="E25" s="105">
+      <c r="E25" s="113">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TEDLAR/SIDEWALL",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TEDLAR/SIDEWALL"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="F25" s="128" t="n"/>
-      <c r="H25" s="109">
+      <c r="H25" s="116">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX SEAT",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX SEAT"),"0%"),"-")</f>
         <v/>
       </c>
@@ -30110,17 +30104,17 @@
       </c>
     </row>
     <row r="28" ht="14.45" customHeight="1" s="125">
-      <c r="B28" s="119">
+      <c r="B28" s="108">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX DOORS",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX DOORS"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="C28" s="128" t="n"/>
-      <c r="E28" s="115">
+      <c r="E28" s="121">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"F/A SEAT",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"F/A SEAT"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="F28" s="128" t="n"/>
-      <c r="H28" s="121">
+      <c r="H28" s="110">
         <f>IFERROR("Completion: "&amp;TEXT(((COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$E$4:$E$1004,"Closed")-(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TASK CARD",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"LAVATORY",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"GALLEY",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"GENERAL CABIN",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TEDLAR/SIDEWALL",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX SEAT",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX DOORS",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"F/A SEAT",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"OFAR/OFCR",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"FLIGHT DECK",'ASF Tracker'!$E$4:$E$1004,"Closed"))))/((COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;")-(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TASK CARD")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"LAVATORY")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"GALLEY")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"GENERAL CABIN")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TEDLAR/SIDEWALL")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX SEAT")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX DOORS")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"F/A SEAT")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"OFAR/OFCR")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"FLIGHT DECK")))),"0%"),"-")</f>
         <v/>
       </c>
@@ -30142,7 +30136,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="109">
+      <c r="B31" s="116">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"FLIGHT DECK",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"FLIGHT DECK"),"0%"),"-")</f>
         <v/>
       </c>
@@ -30150,7 +30144,7 @@
     </row>
     <row r="32" ht="4.15" customHeight="1" s="125"/>
     <row r="33" ht="18" customHeight="1" s="125">
-      <c r="A33" s="112" t="inlineStr">
+      <c r="A33" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">  SPECIALTY</t>
         </is>
@@ -30187,17 +30181,17 @@
       </c>
     </row>
     <row r="36" ht="14.45" customHeight="1" s="125">
-      <c r="B36" s="117">
+      <c r="B36" s="106">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"CAB",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"CAB"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="C36" s="128" t="n"/>
-      <c r="E36" s="119">
+      <c r="E36" s="108">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"SEAT",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"SEAT"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="F36" s="128" t="n"/>
-      <c r="H36" s="106">
+      <c r="H36" s="111">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"AV",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"AV"),"0%"),"-")</f>
         <v/>
       </c>
@@ -30238,17 +30232,17 @@
       </c>
     </row>
     <row r="39" ht="14.45" customHeight="1" s="125">
-      <c r="B39" s="105">
+      <c r="B39" s="113">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"S/W",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"S/W"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="C39" s="128" t="n"/>
-      <c r="E39" s="111">
+      <c r="E39" s="118">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"S/M",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"S/M"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="F39" s="128" t="n"/>
-      <c r="H39" s="113">
+      <c r="H39" s="119">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"PAINT",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"PAINT"),"0%"),"-")</f>
         <v/>
       </c>
@@ -30289,17 +30283,17 @@
       </c>
     </row>
     <row r="42" ht="14.45" customHeight="1" s="125">
-      <c r="B42" s="111">
+      <c r="B42" s="118">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"JOINT",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"JOINT"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="C42" s="128" t="n"/>
-      <c r="E42" s="107">
+      <c r="E42" s="114">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"INSP",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"INSP"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="F42" s="128" t="n"/>
-      <c r="H42" s="116">
+      <c r="H42" s="104">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"AP",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"AP"),"0%"),"-")</f>
         <v/>
       </c>

--- a/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
+++ b/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
@@ -1246,34 +1246,13 @@
     <xf numFmtId="0" fontId="71" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="34" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="23" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="24" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="22" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="32" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="64" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="26" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="25" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="28" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1291,6 +1270,9 @@
     <xf numFmtId="0" fontId="56" fillId="27" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="56" fillId="33" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1298,6 +1280,24 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="34" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="23" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="24" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="22" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="32" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2770,6 +2770,7 @@
       <filters>
         <filter val="CAB"/>
         <filter val="JOINT"/>
+        <filter val="S/M"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3033,7 +3034,7 @@
     <row r="2" ht="19.9" customHeight="1" s="125">
       <c r="A2" s="103" t="inlineStr">
         <is>
-          <t xml:space="preserve">UPDATED: 07 JULY -- DAY SHIFT </t>
+          <t xml:space="preserve">UPDATED: 08 JULY -- DAY SHIFT </t>
         </is>
       </c>
       <c r="B2" s="126" t="n"/>
@@ -3223,7 +3224,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -3249,7 +3250,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" s="125">
+    <row r="7" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A7" s="68" t="n">
         <v>24</v>
       </c>
@@ -3406,7 +3407,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1" s="125">
+    <row r="10" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A10" s="68" t="n">
         <v>27</v>
       </c>
@@ -3482,7 +3483,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -3502,7 +3503,7 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>I/W</t>
+          <t>TO BE CLOSED</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
@@ -3866,7 +3867,7 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
@@ -3880,7 +3881,11 @@
         </is>
       </c>
       <c r="H19" s="10" t="n"/>
-      <c r="I19" s="9" t="n"/>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>TO BE CLOSED</t>
+        </is>
+      </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -4038,7 +4043,7 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
@@ -4052,7 +4057,11 @@
         </is>
       </c>
       <c r="H23" s="10" t="n"/>
-      <c r="I23" s="9" t="n"/>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>TO BE CLOSED</t>
+        </is>
+      </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5268,7 +5277,7 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr">
@@ -6157,7 +6166,7 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
@@ -6173,7 +6182,7 @@
       <c r="H72" s="10" t="n"/>
       <c r="I72" s="9" t="inlineStr">
         <is>
-          <t>R/R FROM CATRION</t>
+          <t>TO BE CLOSED</t>
         </is>
       </c>
       <c r="J72" s="9" t="inlineStr">
@@ -6715,7 +6724,7 @@
       </c>
       <c r="K84" s="9" t="n"/>
     </row>
-    <row r="85" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="85" ht="18" customHeight="1" s="125">
       <c r="A85" s="68" t="n">
         <v>341</v>
       </c>
@@ -6734,7 +6743,7 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
@@ -6820,7 +6829,7 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
@@ -6918,7 +6927,11 @@
         </is>
       </c>
       <c r="H89" s="10" t="n"/>
-      <c r="I89" s="9" t="n"/>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>TO BE CLOSED</t>
+        </is>
+      </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -7039,7 +7052,7 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
@@ -7700,7 +7713,7 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr">
@@ -7720,7 +7733,7 @@
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
-          <t>P/S 4467481</t>
+          <t>TO BE CLOSED</t>
         </is>
       </c>
       <c r="J107" s="9" t="inlineStr">
@@ -7755,7 +7768,7 @@
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr">
@@ -7771,7 +7784,7 @@
       <c r="H108" s="10" t="n"/>
       <c r="I108" s="9" t="inlineStr">
         <is>
-          <t>I/W</t>
+          <t>TO BE CLOSED</t>
         </is>
       </c>
       <c r="J108" s="9" t="inlineStr">
@@ -9055,7 +9068,7 @@
         </is>
       </c>
     </row>
-    <row r="137" hidden="1" ht="15.6" customHeight="1" s="125">
+    <row r="137" ht="15.6" customHeight="1" s="125">
       <c r="A137" s="68" t="inlineStr">
         <is>
           <t>506</t>
@@ -9127,7 +9140,7 @@
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr">
@@ -9143,7 +9156,7 @@
       <c r="H138" s="10" t="n"/>
       <c r="I138" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">S/M REPAIR C/W </t>
+          <t>TO DO</t>
         </is>
       </c>
       <c r="J138" s="9" t="inlineStr">
@@ -9315,7 +9328,7 @@
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr">
@@ -9344,7 +9357,7 @@
       <c r="B143" s="63" t="n">
         <v>32395971</v>
       </c>
-      <c r="C143" s="7" t="inlineStr">
+      <c r="C143" s="81" t="inlineStr">
         <is>
           <t>CCC-32S (03) / A32S CABIN CRITICAL CHECK</t>
         </is>
@@ -9385,7 +9398,7 @@
       <c r="B144" s="63" t="n">
         <v>32349954</v>
       </c>
-      <c r="C144" s="7" t="inlineStr">
+      <c r="C144" s="81" t="inlineStr">
         <is>
           <t>DCC-32S (11) / DCC A32S DAILY CABIN CHECK</t>
         </is>
@@ -9508,7 +9521,7 @@
       <c r="B147" s="63" t="n">
         <v>32258914</v>
       </c>
-      <c r="C147" s="7" t="inlineStr">
+      <c r="C147" s="81" t="inlineStr">
         <is>
           <t>W_N/WEEKLY CHECK</t>
         </is>
@@ -9551,7 +9564,7 @@
           <t>ISC-32S</t>
         </is>
       </c>
-      <c r="C148" s="7" t="inlineStr">
+      <c r="C148" s="81" t="inlineStr">
         <is>
           <t>ISC-32S (13) / 32S IN-SERVEICE-CHECK (ISC)</t>
         </is>
@@ -9653,7 +9666,7 @@
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr">
@@ -9827,7 +9840,7 @@
           <t>WEEKLY-32S</t>
         </is>
       </c>
-      <c r="C154" s="7" t="inlineStr">
+      <c r="C154" s="81" t="inlineStr">
         <is>
           <t>WEEKLY-32S (04) / WEEKLY 32S CHECK</t>
         </is>
@@ -10170,7 +10183,7 @@
       </c>
       <c r="E161" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F161" s="9" t="inlineStr">
@@ -12878,7 +12891,7 @@
       </c>
       <c r="E217" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F217" s="9" t="inlineStr">
@@ -12919,7 +12932,7 @@
       </c>
       <c r="E218" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F218" s="9" t="inlineStr">
@@ -12968,7 +12981,7 @@
       </c>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F219" s="9" t="inlineStr">
@@ -13017,7 +13030,7 @@
       </c>
       <c r="E220" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F220" s="9" t="inlineStr">
@@ -13066,7 +13079,7 @@
       </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F221" s="9" t="inlineStr">
@@ -13409,7 +13422,7 @@
       </c>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F228" s="9" t="inlineStr">
@@ -13458,7 +13471,7 @@
       </c>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
@@ -13507,7 +13520,7 @@
       </c>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F230" s="9" t="inlineStr">
@@ -13556,7 +13569,7 @@
       </c>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr">
@@ -13605,7 +13618,7 @@
       </c>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F232" s="9" t="inlineStr">
@@ -13654,7 +13667,7 @@
       </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F233" s="9" t="inlineStr">
@@ -13703,7 +13716,7 @@
       </c>
       <c r="E234" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F234" s="9" t="inlineStr">
@@ -13752,7 +13765,7 @@
       </c>
       <c r="E235" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F235" s="9" t="inlineStr">
@@ -13801,7 +13814,7 @@
       </c>
       <c r="E236" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F236" s="9" t="inlineStr">
@@ -13850,7 +13863,7 @@
       </c>
       <c r="E237" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F237" s="9" t="inlineStr">
@@ -13948,7 +13961,7 @@
       </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F239" s="9" t="inlineStr">
@@ -14552,7 +14565,7 @@
       </c>
       <c r="E251" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F251" s="9" t="inlineStr">
@@ -14736,7 +14749,7 @@
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F255" s="9" t="inlineStr">
@@ -15422,7 +15435,7 @@
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
@@ -15475,7 +15488,7 @@
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
@@ -15581,7 +15594,7 @@
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
@@ -15634,7 +15647,7 @@
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
@@ -16527,7 +16540,7 @@
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
@@ -16947,7 +16960,7 @@
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
@@ -17388,7 +17401,7 @@
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
@@ -17433,7 +17446,7 @@
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
@@ -17562,7 +17575,7 @@
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
@@ -17906,7 +17919,7 @@
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
@@ -18193,7 +18206,7 @@
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F326" s="9" t="inlineStr">
@@ -18234,7 +18247,7 @@
       </c>
       <c r="E327" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F327" s="9" t="inlineStr">
@@ -18275,7 +18288,7 @@
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F328" s="9" t="inlineStr">
@@ -18648,7 +18661,7 @@
       </c>
       <c r="E337" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F337" s="9" t="inlineStr">
@@ -18959,7 +18972,7 @@
       </c>
       <c r="E344" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F344" s="9" t="inlineStr">
@@ -19086,7 +19099,7 @@
       </c>
       <c r="E347" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F347" s="9" t="inlineStr">
@@ -19102,7 +19115,7 @@
       <c r="H347" s="10" t="n"/>
       <c r="I347" s="9" t="inlineStr">
         <is>
-          <t>OPS AND CLOSE UP TO DO (AVIO)</t>
+          <t>TO BE CLOSED</t>
         </is>
       </c>
       <c r="J347" s="9" t="inlineStr">
@@ -19937,7 +19950,7 @@
       </c>
       <c r="E366" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F366" s="9" t="inlineStr">
@@ -19994,7 +20007,11 @@
           <t>N/R</t>
         </is>
       </c>
-      <c r="I367" s="9" t="n"/>
+      <c r="I367" s="9" t="inlineStr">
+        <is>
+          <t>INSP</t>
+        </is>
+      </c>
       <c r="J367" s="9" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -20133,7 +20150,7 @@
       </c>
       <c r="I370" s="9" t="inlineStr">
         <is>
-          <t>DAY SHIFT</t>
+          <t>INSP</t>
         </is>
       </c>
       <c r="J370" s="9" t="inlineStr">
@@ -20301,7 +20318,7 @@
       </c>
       <c r="E374" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F374" s="9" t="inlineStr">
@@ -20321,7 +20338,7 @@
       </c>
       <c r="I374" s="9" t="inlineStr">
         <is>
-          <t>TORQUE AND OPS</t>
+          <t>TO BE CLOSED</t>
         </is>
       </c>
       <c r="J374" s="9" t="inlineStr">
@@ -20657,7 +20674,7 @@
       </c>
       <c r="E382" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F382" s="9" t="inlineStr">
@@ -20673,7 +20690,7 @@
       <c r="H382" s="10" t="n"/>
       <c r="I382" s="9" t="inlineStr">
         <is>
-          <t>OPS AND CLOSE UP TO DO (AVIO)</t>
+          <t>TO BE CLOSED</t>
         </is>
       </c>
       <c r="J382" s="9" t="inlineStr">
@@ -20702,7 +20719,7 @@
       </c>
       <c r="E383" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F383" s="9" t="inlineStr">
@@ -20718,7 +20735,7 @@
       <c r="H383" s="10" t="n"/>
       <c r="I383" s="9" t="inlineStr">
         <is>
-          <t>OPS AND CLOSE UP TO DO (AVIO)</t>
+          <t>TO BE CLOSED</t>
         </is>
       </c>
       <c r="J383" s="9" t="inlineStr">
@@ -20788,7 +20805,7 @@
       </c>
       <c r="E385" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F385" s="9" t="inlineStr">
@@ -20829,7 +20846,7 @@
       </c>
       <c r="E386" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F386" s="9" t="inlineStr">
@@ -20847,8 +20864,16 @@
           <t>Requested - CR</t>
         </is>
       </c>
-      <c r="I386" s="9" t="n"/>
-      <c r="J386" s="9" t="n"/>
+      <c r="I386" s="9" t="inlineStr">
+        <is>
+          <t>TO BE CLOSED</t>
+        </is>
+      </c>
+      <c r="J386" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K386" s="9" t="n"/>
     </row>
     <row r="387" hidden="1" ht="18" customHeight="1" s="125">
@@ -29773,25 +29798,25 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="125">
-      <c r="A1" s="117" t="inlineStr">
+      <c r="A1" s="110" t="inlineStr">
         <is>
           <t>📊  ASF C3-CHECK — WORK PACKAGE DASHBOARD</t>
         </is>
       </c>
-      <c r="I1" s="112">
+      <c r="I1" s="104">
         <f>"Day "&amp;TEXT(MAX(1,MIN(TODAY()-DATE(2026,6,8)+1,36)),"0")&amp;"/36"</f>
         <v/>
       </c>
     </row>
     <row r="2" ht="13.9" customHeight="1" s="125">
-      <c r="A2" s="107" t="inlineStr">
+      <c r="A2" s="118" t="inlineStr">
         <is>
           <t>All figures update automatically from ASF Tracker</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" s="125">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="A3" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  STATUS OVERVIEW</t>
         </is>
@@ -29859,7 +29884,7 @@
     </row>
     <row r="8" ht="4.15" customHeight="1" s="125"/>
     <row r="9" ht="18" customHeight="1" s="125">
-      <c r="A9" s="120" t="inlineStr">
+      <c r="A9" s="114" t="inlineStr">
         <is>
           <t xml:space="preserve">  PRIORITY ALERTS</t>
         </is>
@@ -29897,7 +29922,7 @@
     </row>
     <row r="12" ht="4.15" customHeight="1" s="125"/>
     <row r="13" ht="18" customHeight="1" s="125">
-      <c r="A13" s="105" t="inlineStr">
+      <c r="A13" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  PARTS REQUIREMENTS  (count of WOs with each status)</t>
         </is>
@@ -29965,7 +29990,7 @@
     </row>
     <row r="18" ht="4.15" customHeight="1" s="125"/>
     <row r="19" ht="18" customHeight="1" s="125">
-      <c r="A19" s="105" t="inlineStr">
+      <c r="A19" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  BY CATEGORY</t>
         </is>
@@ -30002,17 +30027,17 @@
       </c>
     </row>
     <row r="22" ht="14.45" customHeight="1" s="125">
-      <c r="B22" s="115">
+      <c r="B22" s="108">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TASK CARD",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TASK CARD"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="C22" s="128" t="n"/>
-      <c r="E22" s="106">
+      <c r="E22" s="117">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"LAVATORY",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"LAVATORY"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="F22" s="128" t="n"/>
-      <c r="H22" s="109">
+      <c r="H22" s="120">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"GALLEY",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"GALLEY"),"0%"),"-")</f>
         <v/>
       </c>
@@ -30053,17 +30078,17 @@
       </c>
     </row>
     <row r="25" ht="14.45" customHeight="1" s="125">
-      <c r="B25" s="111">
+      <c r="B25" s="106">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$D$4:$D$1004,"GENERAL CABIN",'ASF Tracker'!$E$4:$E$1004,"Closed",'ASF Tracker'!$B$4:$B$1004,"&lt;&gt;")/COUNTIFS('ASF Tracker'!$D$4:$D$1004,"GENERAL CABIN",'ASF Tracker'!$B$4:$B$1004,"&lt;&gt;"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="C25" s="128" t="n"/>
-      <c r="E25" s="113">
+      <c r="E25" s="105">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TEDLAR/SIDEWALL",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TEDLAR/SIDEWALL"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="F25" s="128" t="n"/>
-      <c r="H25" s="116">
+      <c r="H25" s="109">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX SEAT",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX SEAT"),"0%"),"-")</f>
         <v/>
       </c>
@@ -30104,17 +30129,17 @@
       </c>
     </row>
     <row r="28" ht="14.45" customHeight="1" s="125">
-      <c r="B28" s="108">
+      <c r="B28" s="119">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX DOORS",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX DOORS"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="C28" s="128" t="n"/>
-      <c r="E28" s="121">
+      <c r="E28" s="115">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"F/A SEAT",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"F/A SEAT"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="F28" s="128" t="n"/>
-      <c r="H28" s="110">
+      <c r="H28" s="121">
         <f>IFERROR("Completion: "&amp;TEXT(((COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$E$4:$E$1004,"Closed")-(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TASK CARD",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"LAVATORY",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"GALLEY",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"GENERAL CABIN",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TEDLAR/SIDEWALL",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX SEAT",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX DOORS",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"F/A SEAT",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"OFAR/OFCR",'ASF Tracker'!$E$4:$E$1004,"Closed")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"FLIGHT DECK",'ASF Tracker'!$E$4:$E$1004,"Closed"))))/((COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;")-(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TASK CARD")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"LAVATORY")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"GALLEY")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"GENERAL CABIN")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TEDLAR/SIDEWALL")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX SEAT")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"PAX DOORS")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"F/A SEAT")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"OFAR/OFCR")+COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"FLIGHT DECK")))),"0%"),"-")</f>
         <v/>
       </c>
@@ -30136,7 +30161,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="116">
+      <c r="B31" s="109">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"FLIGHT DECK",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"FLIGHT DECK"),"0%"),"-")</f>
         <v/>
       </c>
@@ -30144,7 +30169,7 @@
     </row>
     <row r="32" ht="4.15" customHeight="1" s="125"/>
     <row r="33" ht="18" customHeight="1" s="125">
-      <c r="A33" s="105" t="inlineStr">
+      <c r="A33" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  SPECIALTY</t>
         </is>
@@ -30181,17 +30206,17 @@
       </c>
     </row>
     <row r="36" ht="14.45" customHeight="1" s="125">
-      <c r="B36" s="106">
+      <c r="B36" s="117">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"CAB",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"CAB"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="C36" s="128" t="n"/>
-      <c r="E36" s="108">
+      <c r="E36" s="119">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"SEAT",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"SEAT"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="F36" s="128" t="n"/>
-      <c r="H36" s="111">
+      <c r="H36" s="106">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"AV",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"AV"),"0%"),"-")</f>
         <v/>
       </c>
@@ -30232,17 +30257,17 @@
       </c>
     </row>
     <row r="39" ht="14.45" customHeight="1" s="125">
-      <c r="B39" s="113">
+      <c r="B39" s="105">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"S/W",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"S/W"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="C39" s="128" t="n"/>
-      <c r="E39" s="118">
+      <c r="E39" s="111">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"S/M",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"S/M"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="F39" s="128" t="n"/>
-      <c r="H39" s="119">
+      <c r="H39" s="113">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"PAINT",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"PAINT"),"0%"),"-")</f>
         <v/>
       </c>
@@ -30283,17 +30308,17 @@
       </c>
     </row>
     <row r="42" ht="14.45" customHeight="1" s="125">
-      <c r="B42" s="118">
+      <c r="B42" s="111">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"JOINT",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"JOINT"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="C42" s="128" t="n"/>
-      <c r="E42" s="114">
+      <c r="E42" s="107">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"INSP",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"INSP"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="F42" s="128" t="n"/>
-      <c r="H42" s="104">
+      <c r="H42" s="116">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"AP",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"AP"),"0%"),"-")</f>
         <v/>
       </c>
@@ -30308,8 +30333,8 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="E39:F39"/>
+    <mergeCell ref="A19:J19"/>
     <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A19:J19"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="H39:I39"/>
     <mergeCell ref="H25:I25"/>

--- a/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
+++ b/uploads/ASF_CABIN_WP_TRACKER_updated.xlsx
@@ -1267,13 +1267,13 @@
     <xf numFmtId="0" fontId="59" fillId="32" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="64" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="26" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="25" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="28" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1316,7 +1316,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="104">
+  <dxfs count="105">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1623,12 +1623,12 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="FFB71C1C"/>
+        <color rgb="FFE65100"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFCDD2"/>
+          <bgColor rgb="FFFFE0B2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1642,19 +1642,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFCDD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <b val="1"/>
-        <color rgb="FFE65100"/>
-        <sz val="10"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE0B2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1740,6 +1727,19 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
+        <color rgb="FFE65100"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE0B2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
         <color rgb="FFB71C1C"/>
         <sz val="10"/>
       </font>
@@ -1772,19 +1772,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFCDD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <b val="1"/>
-        <color rgb="FFE65100"/>
-        <sz val="10"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE0B2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1987,12 +1974,38 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
+        <color rgb="FF1B5E20"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
         <color rgb="FFFFFFFF"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF607D8B"/>
+          <bgColor rgb="FF7B1FA2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="FF0D47A1"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBBDEFB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2013,38 +2026,12 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="FF0D47A1"/>
-        <sz val="10"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFBBDEFB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <b val="1"/>
         <color rgb="FFFFFFFF"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF7B1FA2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <b val="1"/>
-        <color rgb="FF1B5E20"/>
-        <sz val="10"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC8E6C9"/>
+          <bgColor rgb="FF607D8B"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2088,6 +2075,19 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="FFB71C1C"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCDD2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border outline="0">
         <left style="thin">
           <color rgb="FFDDDDDD"/>
@@ -2103,6 +2103,17 @@
           <color rgb="FFDDDDDD"/>
         </right>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFE65100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFE0B2"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2256,13 +2267,25 @@
     <dxf>
       <font>
         <b val="1"/>
+        <color rgb="FFE65100"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF4E342E"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
         <color rgb="FF2E7D32"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="FF4E342E"/>
+        <color rgb="FF37474F"/>
       </font>
     </dxf>
     <dxf>
@@ -2275,18 +2298,6 @@
       <font>
         <b val="1"/>
         <color rgb="FF1565C0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF37474F"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FFE65100"/>
       </font>
     </dxf>
     <dxf>
@@ -2361,16 +2372,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFE65100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF3E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="1"/>
         <color rgb="FFE65100"/>
       </font>
@@ -2418,6 +2419,16 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFF5F5F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFE65100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF3E0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2610,22 +2621,22 @@
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="FFB71C1C"/>
+        <color rgb="FFE65100"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFCDD2"/>
+          <bgColor rgb="FFFFE0B2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="FFE65100"/>
+        <color rgb="FFB71C1C"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFE0B2"/>
+          <bgColor rgb="FFFFCDD2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2752,15 +2763,6 @@
     <filterColumn colId="4" hiddenButton="0" showButton="1">
       <filters>
         <filter val="Open"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="6" hiddenButton="0" showButton="1">
-      <filters blank="1">
-        <filter val="CAB"/>
-        <filter val="JOINT"/>
-        <filter val="PAINT"/>
-        <filter val="S/M"/>
-        <filter val="SEAT"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3024,7 +3026,7 @@
     <row r="2" ht="19.9" customHeight="1" s="125">
       <c r="A2" s="103" t="inlineStr">
         <is>
-          <t xml:space="preserve">UPDATED: 08 JULY -- DAY SHIFT </t>
+          <t xml:space="preserve">UPDATED: 12 JULY -- DAY SHIFT </t>
         </is>
       </c>
       <c r="B2" s="126" t="n"/>
@@ -3101,7 +3103,7 @@
         </is>
       </c>
     </row>
-    <row r="4" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="4" ht="18" customHeight="1" s="125">
       <c r="A4" s="68" t="n">
         <v>1</v>
       </c>
@@ -3146,7 +3148,7 @@
         </is>
       </c>
     </row>
-    <row r="5" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="5" ht="18" customHeight="1" s="125">
       <c r="A5" s="68" t="n">
         <v>2</v>
       </c>
@@ -5166,7 +5168,7 @@
       </c>
       <c r="K48" s="9" t="n"/>
     </row>
-    <row r="49" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="49" ht="18" customHeight="1" s="125">
       <c r="A49" s="68" t="n">
         <v>274</v>
       </c>
@@ -5494,7 +5496,7 @@
       </c>
       <c r="K56" s="9" t="n"/>
     </row>
-    <row r="57" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="57" ht="18" customHeight="1" s="125">
       <c r="A57" s="68" t="n">
         <v>287</v>
       </c>
@@ -5535,7 +5537,7 @@
       </c>
       <c r="K57" s="9" t="n"/>
     </row>
-    <row r="58" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="58" ht="18" customHeight="1" s="125">
       <c r="A58" s="68" t="n">
         <v>296</v>
       </c>
@@ -6096,7 +6098,7 @@
       </c>
       <c r="K70" s="9" t="n"/>
     </row>
-    <row r="71" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="71" ht="18" customHeight="1" s="125">
       <c r="A71" s="68" t="n">
         <v>316</v>
       </c>
@@ -6205,7 +6207,7 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
@@ -6219,11 +6221,7 @@
         </is>
       </c>
       <c r="H73" s="10" t="n"/>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>REF TO WO 32788809 CW</t>
-        </is>
-      </c>
+      <c r="I73" s="9" t="n"/>
       <c r="J73" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6327,7 +6325,7 @@
       </c>
       <c r="K75" s="9" t="n"/>
     </row>
-    <row r="76" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="76" ht="18" customHeight="1" s="125">
       <c r="A76" s="68" t="n">
         <v>323</v>
       </c>
@@ -6362,7 +6360,11 @@
         </is>
       </c>
       <c r="H76" s="10" t="n"/>
-      <c r="I76" s="9" t="n"/>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>C/W CHECK W/HPC</t>
+        </is>
+      </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6370,7 +6372,7 @@
       </c>
       <c r="K76" s="9" t="n"/>
     </row>
-    <row r="77" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="77" ht="18" customHeight="1" s="125">
       <c r="A77" s="68" t="n">
         <v>324</v>
       </c>
@@ -6413,7 +6415,7 @@
       </c>
       <c r="K77" s="9" t="n"/>
     </row>
-    <row r="78" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="78" ht="18" customHeight="1" s="125">
       <c r="A78" s="68" t="n">
         <v>325</v>
       </c>
@@ -6499,7 +6501,7 @@
       </c>
       <c r="K79" s="9" t="n"/>
     </row>
-    <row r="80" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="80" ht="18" customHeight="1" s="125">
       <c r="A80" s="68" t="n">
         <v>327</v>
       </c>
@@ -6585,7 +6587,7 @@
       </c>
       <c r="K81" s="9" t="n"/>
     </row>
-    <row r="82" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="82" ht="18" customHeight="1" s="125">
       <c r="A82" s="68" t="n">
         <v>329</v>
       </c>
@@ -6649,7 +6651,7 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr">
@@ -6671,7 +6673,7 @@
       </c>
       <c r="K83" s="9" t="n"/>
     </row>
-    <row r="84" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="84" ht="18" customHeight="1" s="125">
       <c r="A84" s="68" t="n">
         <v>339</v>
       </c>
@@ -6800,7 +6802,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1" s="125">
+    <row r="87" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A87" s="68" t="n">
         <v>343</v>
       </c>
@@ -6882,7 +6884,7 @@
       </c>
       <c r="K88" s="9" t="n"/>
     </row>
-    <row r="89" ht="18" customHeight="1" s="125">
+    <row r="89" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A89" s="68" t="n">
         <v>354</v>
       </c>
@@ -8418,7 +8420,7 @@
       </c>
       <c r="K122" s="9" t="n"/>
     </row>
-    <row r="123" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="123" ht="18" customHeight="1" s="125">
       <c r="A123" s="68" t="n">
         <v>454</v>
       </c>
@@ -8439,7 +8441,7 @@
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr">
@@ -8600,7 +8602,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="18" customHeight="1" s="125">
+    <row r="127" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A127" s="68" t="n">
         <v>499</v>
       </c>
@@ -8739,7 +8741,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="15.6" customHeight="1" s="125">
+    <row r="130" hidden="1" ht="15.6" customHeight="1" s="125">
       <c r="A130" s="68" t="inlineStr">
         <is>
           <t>501</t>
@@ -9058,7 +9060,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="15.6" customHeight="1" s="125">
+    <row r="137" hidden="1" ht="15.6" customHeight="1" s="125">
       <c r="A137" s="68" t="inlineStr">
         <is>
           <t>506</t>
@@ -9195,7 +9197,7 @@
       </c>
       <c r="I139" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDD 11/07/2026 </t>
+          <t>C/O</t>
         </is>
       </c>
       <c r="J139" s="9" t="inlineStr">
@@ -9400,7 +9402,7 @@
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr">
@@ -9422,7 +9424,7 @@
       </c>
       <c r="K144" s="9" t="n"/>
     </row>
-    <row r="145" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="145" ht="18" customHeight="1" s="125">
       <c r="A145" s="68" t="n">
         <v>567</v>
       </c>
@@ -9463,7 +9465,7 @@
       </c>
       <c r="K145" s="9" t="n"/>
     </row>
-    <row r="146" hidden="1" ht="18" customHeight="1" s="125">
+    <row r="146" ht="18" customHeight="1" s="125">
       <c r="A146" s="68" t="n">
         <v>570</v>
       </c>
@@ -9607,7 +9609,7 @@
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr">
@@ -9623,7 +9625,7 @@
       <c r="H149" s="10" t="n"/>
       <c r="I149" s="9" t="inlineStr">
         <is>
-          <t>FROM CATRION</t>
+          <t>INSP</t>
         </is>
       </c>
       <c r="J149" s="9" t="inlineStr">
@@ -10836,7 +10838,7 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="18" customHeight="1" s="125">
+    <row r="175" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A175" s="68" t="n">
         <v>611</v>
       </c>
@@ -11092,7 +11094,7 @@
       </c>
       <c r="E180" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F180" s="9" t="inlineStr">
@@ -11108,7 +11110,7 @@
       <c r="H180" s="10" t="n"/>
       <c r="I180" s="9" t="inlineStr">
         <is>
-          <t>HANDED TO PNT</t>
+          <t xml:space="preserve">REQ PNT ACTION </t>
         </is>
       </c>
       <c r="J180" s="9" t="inlineStr">
@@ -12881,7 +12883,7 @@
       </c>
       <c r="E217" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F217" s="9" t="inlineStr">
@@ -12895,7 +12897,11 @@
         </is>
       </c>
       <c r="H217" s="10" t="n"/>
-      <c r="I217" s="9" t="n"/>
+      <c r="I217" s="9" t="inlineStr">
+        <is>
+          <t>REQ RE-ISNP</t>
+        </is>
+      </c>
       <c r="J217" s="9" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -12903,7 +12909,7 @@
       </c>
       <c r="K217" s="9" t="n"/>
     </row>
-    <row r="218" ht="18" customHeight="1" s="125">
+    <row r="218" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A218" s="68" t="n">
         <v>688</v>
       </c>
@@ -12971,7 +12977,7 @@
       </c>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F219" s="9" t="inlineStr">
@@ -12989,9 +12995,9 @@
           <t>Requested - R</t>
         </is>
       </c>
-      <c r="I219" s="82" t="inlineStr">
-        <is>
-          <t>C/W</t>
+      <c r="I219" s="9" t="inlineStr">
+        <is>
+          <t>C/W CHECK W/HPC</t>
         </is>
       </c>
       <c r="J219" s="9" t="inlineStr">
@@ -13001,7 +13007,7 @@
       </c>
       <c r="K219" s="9" t="n"/>
     </row>
-    <row r="220" ht="18" customHeight="1" s="125">
+    <row r="220" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A220" s="68" t="n">
         <v>690</v>
       </c>
@@ -13069,7 +13075,7 @@
       </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F221" s="9" t="inlineStr">
@@ -13087,9 +13093,9 @@
           <t>Requested - R</t>
         </is>
       </c>
-      <c r="I221" s="82" t="inlineStr">
-        <is>
-          <t>C/W</t>
+      <c r="I221" s="9" t="inlineStr">
+        <is>
+          <t>C/W CHECK W/HPC</t>
         </is>
       </c>
       <c r="J221" s="9" t="inlineStr">
@@ -13393,7 +13399,7 @@
       </c>
       <c r="K227" s="9" t="n"/>
     </row>
-    <row r="228" ht="18" customHeight="1" s="125">
+    <row r="228" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A228" s="68" t="n">
         <v>699</v>
       </c>
@@ -13442,7 +13448,7 @@
       </c>
       <c r="K228" s="9" t="n"/>
     </row>
-    <row r="229" ht="18" customHeight="1" s="125">
+    <row r="229" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A229" s="68" t="n">
         <v>700</v>
       </c>
@@ -13491,7 +13497,7 @@
       </c>
       <c r="K229" s="9" t="n"/>
     </row>
-    <row r="230" ht="18" customHeight="1" s="125">
+    <row r="230" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A230" s="68" t="n">
         <v>701</v>
       </c>
@@ -13540,7 +13546,7 @@
       </c>
       <c r="K230" s="9" t="n"/>
     </row>
-    <row r="231" ht="18" customHeight="1" s="125">
+    <row r="231" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A231" s="68" t="n">
         <v>702</v>
       </c>
@@ -13589,7 +13595,7 @@
       </c>
       <c r="K231" s="9" t="n"/>
     </row>
-    <row r="232" ht="18" customHeight="1" s="125">
+    <row r="232" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A232" s="68" t="n">
         <v>703</v>
       </c>
@@ -13638,7 +13644,7 @@
       </c>
       <c r="K232" s="9" t="n"/>
     </row>
-    <row r="233" ht="18" customHeight="1" s="125">
+    <row r="233" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A233" s="68" t="n">
         <v>704</v>
       </c>
@@ -13687,7 +13693,7 @@
       </c>
       <c r="K233" s="9" t="n"/>
     </row>
-    <row r="234" ht="18" customHeight="1" s="125">
+    <row r="234" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A234" s="68" t="n">
         <v>705</v>
       </c>
@@ -13736,7 +13742,7 @@
       </c>
       <c r="K234" s="9" t="n"/>
     </row>
-    <row r="235" ht="18" customHeight="1" s="125">
+    <row r="235" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A235" s="68" t="n">
         <v>706</v>
       </c>
@@ -13785,7 +13791,7 @@
       </c>
       <c r="K235" s="9" t="n"/>
     </row>
-    <row r="236" ht="18" customHeight="1" s="125">
+    <row r="236" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A236" s="68" t="n">
         <v>707</v>
       </c>
@@ -13834,7 +13840,7 @@
       </c>
       <c r="K236" s="9" t="n"/>
     </row>
-    <row r="237" ht="18" customHeight="1" s="125">
+    <row r="237" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A237" s="68" t="n">
         <v>708</v>
       </c>
@@ -13932,7 +13938,7 @@
       </c>
       <c r="K238" s="9" t="n"/>
     </row>
-    <row r="239" ht="18" customHeight="1" s="125">
+    <row r="239" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A239" s="68" t="n">
         <v>710</v>
       </c>
@@ -14355,7 +14361,7 @@
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F247" s="9" t="inlineStr">
@@ -14371,7 +14377,7 @@
       <c r="H247" s="10" t="n"/>
       <c r="I247" s="9" t="inlineStr">
         <is>
-          <t>F/UP WITH S/M</t>
+          <t>C/W CHECK W/HPC</t>
         </is>
       </c>
       <c r="J247" s="9" t="inlineStr">
@@ -14536,7 +14542,7 @@
         </is>
       </c>
     </row>
-    <row r="251" ht="18" customHeight="1" s="125">
+    <row r="251" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A251" s="68" t="n">
         <v>722</v>
       </c>
@@ -14720,7 +14726,7 @@
         </is>
       </c>
     </row>
-    <row r="255" ht="18" customHeight="1" s="125">
+    <row r="255" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A255" s="68" t="n">
         <v>726</v>
       </c>
@@ -17074,7 +17080,7 @@
         </is>
       </c>
     </row>
-    <row r="301" ht="18" customHeight="1" s="125">
+    <row r="301" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A301" s="68" t="inlineStr">
         <is>
           <t>839</t>
@@ -17293,7 +17299,7 @@
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
@@ -17505,7 +17511,7 @@
       </c>
       <c r="K309" s="9" t="n"/>
     </row>
-    <row r="310" ht="18" customHeight="1" s="125">
+    <row r="310" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A310" s="68" t="n">
         <v>870</v>
       </c>
@@ -19649,7 +19655,7 @@
       </c>
       <c r="I359" s="9" t="inlineStr">
         <is>
-          <t>EDD:</t>
+          <t>NEF</t>
         </is>
       </c>
       <c r="J359" s="9" t="inlineStr">
@@ -19979,7 +19985,7 @@
       </c>
       <c r="E367" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F367" s="9" t="inlineStr">
@@ -19999,7 +20005,7 @@
       </c>
       <c r="I367" s="9" t="inlineStr">
         <is>
-          <t>INSP</t>
+          <t>C/W CHECK W/HPC</t>
         </is>
       </c>
       <c r="J367" s="9" t="inlineStr">
@@ -20099,7 +20105,7 @@
       </c>
       <c r="K369" s="9" t="n"/>
     </row>
-    <row r="370" ht="18" customHeight="1" s="125">
+    <row r="370" hidden="1" ht="18" customHeight="1" s="125">
       <c r="A370" s="68" t="n">
         <v>995</v>
       </c>
@@ -20402,7 +20408,7 @@
       </c>
       <c r="E376" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F376" s="9" t="inlineStr">
@@ -20418,7 +20424,7 @@
       <c r="H376" s="10" t="n"/>
       <c r="I376" s="9" t="inlineStr">
         <is>
-          <t>IW</t>
+          <t>C/W CHECK W/HPC</t>
         </is>
       </c>
       <c r="J376" s="9" t="inlineStr">
@@ -20867,12 +20873,25 @@
       <c r="K386" s="9" t="n"/>
     </row>
     <row r="387" ht="18" customHeight="1" s="125">
-      <c r="A387" s="5" t="n"/>
-      <c r="B387" s="6" t="n"/>
-      <c r="D387" s="8" t="n"/>
+      <c r="A387" s="68" t="n">
+        <v>1049</v>
+      </c>
+      <c r="B387" s="63" t="n">
+        <v>32952652</v>
+      </c>
+      <c r="C387" s="7" t="inlineStr">
+        <is>
+          <t>PAINT - NO CALL BACK LAV D  SIDE WALL REQ PNT</t>
+        </is>
+      </c>
+      <c r="D387" s="8" t="inlineStr">
+        <is>
+          <t>LAVATORY</t>
+        </is>
+      </c>
       <c r="E387" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F387" s="9" t="inlineStr">
@@ -20880,20 +20899,36 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="G387" s="8" t="n"/>
+      <c r="G387" s="8" t="inlineStr">
+        <is>
+          <t>PAINT</t>
+        </is>
+      </c>
       <c r="H387" s="10" t="n"/>
       <c r="I387" s="9" t="n"/>
       <c r="J387" s="9" t="n"/>
       <c r="K387" s="9" t="n"/>
     </row>
     <row r="388" ht="18" customHeight="1" s="125">
-      <c r="A388" s="5" t="n"/>
-      <c r="B388" s="6" t="n"/>
-      <c r="C388" s="7" t="n"/>
-      <c r="D388" s="8" t="n"/>
+      <c r="A388" s="68" t="n">
+        <v>1050</v>
+      </c>
+      <c r="B388" s="63" t="n">
+        <v>32956184</v>
+      </c>
+      <c r="C388" s="7" t="inlineStr">
+        <is>
+          <t>CAB - NO CALLBACK - LAV A "LAVATORY A" TOILET VACUUM ASSEMBLY WITH LEAKING.</t>
+        </is>
+      </c>
+      <c r="D388" s="8" t="inlineStr">
+        <is>
+          <t>LAVATORY</t>
+        </is>
+      </c>
       <c r="E388" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F388" s="9" t="inlineStr">
@@ -20901,8 +20936,16 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="G388" s="8" t="n"/>
-      <c r="H388" s="10" t="n"/>
+      <c r="G388" s="8" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="H388" s="10" t="inlineStr">
+        <is>
+          <t>Requested - R</t>
+        </is>
+      </c>
       <c r="I388" s="9" t="n"/>
       <c r="J388" s="9" t="n"/>
       <c r="K388" s="9" t="n"/>
@@ -29536,197 +29579,202 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:B375 A377:A1004">
-    <cfRule type="expression" priority="153" dxfId="78">
+    <cfRule type="expression" priority="154" dxfId="50">
       <formula>$F4="Critical"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A377:A1004">
-    <cfRule type="expression" priority="44" dxfId="79">
+    <cfRule type="expression" priority="45" dxfId="79">
       <formula>$F377="AOG"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:B376">
-    <cfRule type="expression" priority="3" dxfId="79">
+    <cfRule type="expression" priority="4" dxfId="79">
       <formula>$F4="AOG"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A376:C376">
-    <cfRule type="expression" priority="38" dxfId="78">
+    <cfRule type="expression" priority="39" dxfId="50">
       <formula>$F376="Critical"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B377:B1004">
-    <cfRule type="expression" priority="154" dxfId="78">
+    <cfRule type="expression" priority="49" dxfId="79">
+      <formula>$F377="AOG"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="155" dxfId="50">
       <formula>$F377="Critical"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="48" dxfId="79">
-      <formula>$F377="AOG"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C375 C388:C1004">
-    <cfRule type="expression" priority="155" dxfId="78">
+    <cfRule type="expression" priority="156" dxfId="50">
       <formula>$F4="Critical"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C252:C346">
-    <cfRule type="expression" priority="50" dxfId="79">
+    <cfRule type="expression" priority="51" dxfId="79">
       <formula>$F252="AOG"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C377:C386">
-    <cfRule type="expression" priority="1" dxfId="78">
+    <cfRule type="expression" priority="2" dxfId="50">
       <formula>$F377="Critical"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D1004">
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="33">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="32">
       <formula>"GENERAL CABIN"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="32">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="31">
       <formula>"GALLEY"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="31">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="30">
       <formula>"LAVATORY"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="30">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="29">
       <formula>"PAX DOORS"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="29">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="28">
       <formula>"F/A SEAT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="28">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="27">
       <formula>"PAX SEAT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="27">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="26">
       <formula>"FLIGHT DECK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="26">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="25">
       <formula>"OFAR/OFCR"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="25">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="24">
       <formula>"TEDLAR/SIDEWALL"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="24">
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="23">
       <formula>"PAINT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="84">
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="85">
       <formula>"TASK CARD"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E1004">
-    <cfRule type="cellIs" priority="94" operator="equal" dxfId="83">
+    <cfRule type="cellIs" priority="95" operator="equal" dxfId="84">
       <formula>"Open"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="98" operator="equal" dxfId="82">
+    <cfRule type="cellIs" priority="96" operator="equal" dxfId="83">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="99" operator="equal" dxfId="82">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="156" operator="equal" dxfId="81">
+    <cfRule type="cellIs" priority="157" operator="equal" dxfId="81">
       <formula>"Closed"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="156" operator="equal" dxfId="80">
+    <cfRule type="cellIs" priority="157" operator="equal" dxfId="80">
       <formula>"On Hold"</formula>
     </cfRule>
-    <cfRule type="expression" priority="156" dxfId="79">
+    <cfRule type="expression" priority="157" dxfId="79">
       <formula>$F4="AOG"</formula>
     </cfRule>
-    <cfRule type="expression" priority="156" dxfId="78">
+    <cfRule type="expression" priority="157" dxfId="50">
       <formula>$F4="Critical"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="95" operator="equal" dxfId="77">
-      <formula>"In Progress"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="156" operator="equal" dxfId="76">
+    <cfRule type="cellIs" priority="157" operator="equal" dxfId="77">
       <formula>"Deferred"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F1004">
-    <cfRule type="cellIs" priority="99" operator="equal" dxfId="75">
+    <cfRule type="cellIs" priority="100" operator="equal" dxfId="76">
       <formula>"AOG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="100" operator="equal" dxfId="74">
+    <cfRule type="cellIs" priority="101" operator="equal" dxfId="75">
       <formula>"Critical"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="101" operator="equal" dxfId="73">
+    <cfRule type="cellIs" priority="102" operator="equal" dxfId="74">
       <formula>"High"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="102" operator="equal" dxfId="72">
+    <cfRule type="cellIs" priority="103" operator="equal" dxfId="73">
       <formula>"Normal"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="103" operator="equal" dxfId="71">
+    <cfRule type="cellIs" priority="104" operator="equal" dxfId="72">
       <formula>"Low"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G1004">
-    <cfRule type="cellIs" priority="35" operator="equal" dxfId="70">
+    <cfRule type="cellIs" priority="31" operator="equal" dxfId="71">
+      <formula>"CAB"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="32" operator="equal" dxfId="70">
+      <formula>"SEAT"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="33" operator="equal" dxfId="69">
+      <formula>"AV"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="34" operator="equal" dxfId="68">
+      <formula>"S/W"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="35" operator="equal" dxfId="67">
+      <formula>"S/M"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="36" operator="equal" dxfId="66">
       <formula>"PAINT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="32" operator="equal" dxfId="69">
-      <formula>"AV"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="30" operator="equal" dxfId="68">
-      <formula>"CAB"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="31" operator="equal" dxfId="67">
-      <formula>"SEAT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="34" operator="equal" dxfId="66">
-      <formula>"S/M"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="33" operator="equal" dxfId="65">
-      <formula>"S/W"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="36" operator="equal" dxfId="64">
+    <cfRule type="cellIs" priority="37" operator="equal" dxfId="65">
       <formula>"JOINT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="37" operator="equal" dxfId="63">
+    <cfRule type="cellIs" priority="38" operator="equal" dxfId="64">
       <formula>"INSP"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H1004">
-    <cfRule type="cellIs" priority="24" operator="equal" dxfId="62">
+    <cfRule type="cellIs" priority="25" operator="equal" dxfId="63">
       <formula>"N/R"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="25" operator="equal" dxfId="61">
+    <cfRule type="cellIs" priority="26" operator="equal" dxfId="62">
       <formula>"Requested"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="26" operator="equal" dxfId="60">
+    <cfRule type="cellIs" priority="27" operator="equal" dxfId="61">
       <formula>"Requested - R"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="27" operator="equal" dxfId="59">
+    <cfRule type="cellIs" priority="28" operator="equal" dxfId="60">
       <formula>"Requested - CR"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="28" operator="equal" dxfId="58">
+    <cfRule type="cellIs" priority="29" operator="equal" dxfId="59">
       <formula>"Pending EVAL"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="29" operator="equal" dxfId="57">
+    <cfRule type="cellIs" priority="30" operator="equal" dxfId="58">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I1004">
-    <cfRule type="expression" priority="125" dxfId="56">
+    <cfRule type="expression" priority="126" dxfId="57">
       <formula>OR(TRIM(I4)="C/W",TRIM(I4)="CW")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J1004">
-    <cfRule type="cellIs" priority="150" operator="equal" dxfId="53">
+    <cfRule type="cellIs" priority="151" operator="equal" dxfId="54">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="151" operator="equal" dxfId="53">
+    <cfRule type="cellIs" priority="152" operator="equal" dxfId="54">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="152" operator="equal" dxfId="53">
+    <cfRule type="cellIs" priority="153" operator="equal" dxfId="54">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K1004">
-    <cfRule type="cellIs" priority="121" operator="equal" dxfId="52">
+    <cfRule type="cellIs" priority="122" operator="equal" dxfId="53">
       <formula>"FWD"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="122" operator="equal" dxfId="51">
+    <cfRule type="cellIs" priority="123" operator="equal" dxfId="52">
       <formula>"AFT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="123" operator="equal" dxfId="50">
+    <cfRule type="cellIs" priority="124" operator="equal" dxfId="51">
       <formula>"JOINT"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C387">
+    <cfRule type="expression" priority="1" dxfId="50">
+      <formula>$F387="Critical"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
@@ -29788,7 +29836,7 @@
           <t>📊  ASF C3-CHECK — WORK PACKAGE DASHBOARD</t>
         </is>
       </c>
-      <c r="I1" s="112">
+      <c r="I1" s="111">
         <f>"Day "&amp;TEXT(MAX(1,MIN(TODAY()-DATE(2026,6,8)+1,36)),"0")&amp;"/36"</f>
         <v/>
       </c>
@@ -30063,12 +30111,12 @@
       </c>
     </row>
     <row r="25" ht="14.45" customHeight="1" s="125">
-      <c r="B25" s="111">
+      <c r="B25" s="113">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$D$4:$D$1004,"GENERAL CABIN",'ASF Tracker'!$E$4:$E$1004,"Closed",'ASF Tracker'!$B$4:$B$1004,"&lt;&gt;")/COUNTIFS('ASF Tracker'!$D$4:$D$1004,"GENERAL CABIN",'ASF Tracker'!$B$4:$B$1004,"&lt;&gt;"),"0%"),"-")</f>
         <v/>
       </c>
       <c r="C25" s="128" t="n"/>
-      <c r="E25" s="113">
+      <c r="E25" s="112">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TEDLAR/SIDEWALL",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$D$4:$D$1004,"TEDLAR/SIDEWALL"),"0%"),"-")</f>
         <v/>
       </c>
@@ -30201,7 +30249,7 @@
         <v/>
       </c>
       <c r="F36" s="128" t="n"/>
-      <c r="H36" s="111">
+      <c r="H36" s="113">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"AV",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"AV"),"0%"),"-")</f>
         <v/>
       </c>
@@ -30242,7 +30290,7 @@
       </c>
     </row>
     <row r="39" ht="14.45" customHeight="1" s="125">
-      <c r="B39" s="113">
+      <c r="B39" s="112">
         <f>IFERROR("Completion: "&amp;TEXT(COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"S/W",'ASF Tracker'!$E$4:$E$1004,"Closed")/COUNTIFS('ASF Tracker'!$B$4:$B$1004,"&lt;&gt;",'ASF Tracker'!$G$4:$G$1004,"S/W"),"0%"),"-")</f>
         <v/>
       </c>
@@ -35866,131 +35914,131 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:C4 A5:A156 A157:G657 G4:K99 G116:K157 H100:K115">
-    <cfRule type="expression" priority="224" dxfId="13">
+    <cfRule type="expression" priority="223" dxfId="12">
+      <formula>#REF!="AOG"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="224" dxfId="11">
       <formula>#REF!="Critical"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="223" dxfId="11">
-      <formula>#REF!="AOG"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B156">
-    <cfRule type="expression" priority="23" dxfId="11">
+    <cfRule type="expression" priority="23" dxfId="12">
       <formula>#REF!="AOG"</formula>
     </cfRule>
-    <cfRule type="expression" priority="24" dxfId="13">
+    <cfRule type="expression" priority="24" dxfId="11">
       <formula>#REF!="Critical"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157:B657">
-    <cfRule type="cellIs" priority="215" operator="equal" dxfId="29">
+    <cfRule type="cellIs" priority="211" operator="equal" dxfId="32">
+      <formula>"GENERAL CABIN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="212" operator="equal" dxfId="31">
+      <formula>"GALLEY"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="213" operator="equal" dxfId="30">
+      <formula>"LAVATORY"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="214" operator="equal" dxfId="29">
+      <formula>"PAX DOORS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="215" operator="equal" dxfId="28">
       <formula>"F/A SEAT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="214" operator="equal" dxfId="30">
-      <formula>"PAX DOORS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="213" operator="equal" dxfId="31">
-      <formula>"LAVATORY"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="212" operator="equal" dxfId="32">
-      <formula>"GALLEY"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="211" operator="equal" dxfId="33">
-      <formula>"GENERAL CABIN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="216" operator="equal" dxfId="28">
+    <cfRule type="cellIs" priority="216" operator="equal" dxfId="27">
       <formula>"PAX SEAT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="217" operator="equal" dxfId="27">
+    <cfRule type="cellIs" priority="217" operator="equal" dxfId="26">
       <formula>"FLIGHT DECK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="218" operator="equal" dxfId="26">
+    <cfRule type="cellIs" priority="218" operator="equal" dxfId="25">
       <formula>"OFAR/OFCR"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="219" operator="equal" dxfId="25">
+    <cfRule type="cellIs" priority="219" operator="equal" dxfId="24">
       <formula>"TEDLAR/SIDEWALL"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="220" operator="equal" dxfId="24">
+    <cfRule type="cellIs" priority="220" operator="equal" dxfId="23">
       <formula>"PAINT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C157">
-    <cfRule type="cellIs" priority="27" operator="equal" dxfId="33">
+    <cfRule type="cellIs" priority="27" operator="equal" dxfId="32">
       <formula>"GENERAL CABIN"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="28" operator="equal" dxfId="32">
+    <cfRule type="cellIs" priority="28" operator="equal" dxfId="31">
       <formula>"GALLEY"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="29" operator="equal" dxfId="31">
+    <cfRule type="cellIs" priority="29" operator="equal" dxfId="30">
       <formula>"LAVATORY"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="30" operator="equal" dxfId="30">
+    <cfRule type="cellIs" priority="30" operator="equal" dxfId="29">
       <formula>"PAX DOORS"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="31" operator="equal" dxfId="29">
+    <cfRule type="cellIs" priority="31" operator="equal" dxfId="28">
       <formula>"F/A SEAT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="32" operator="equal" dxfId="28">
+    <cfRule type="cellIs" priority="32" operator="equal" dxfId="27">
       <formula>"PAX SEAT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="33" operator="equal" dxfId="27">
+    <cfRule type="cellIs" priority="33" operator="equal" dxfId="26">
       <formula>"FLIGHT DECK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="34" operator="equal" dxfId="26">
+    <cfRule type="cellIs" priority="34" operator="equal" dxfId="25">
       <formula>"OFAR/OFCR"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="35" operator="equal" dxfId="25">
+    <cfRule type="cellIs" priority="35" operator="equal" dxfId="24">
       <formula>"TEDLAR/SIDEWALL"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="36" operator="equal" dxfId="24">
+    <cfRule type="cellIs" priority="36" operator="equal" dxfId="23">
       <formula>"PAINT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:C65">
-    <cfRule type="expression" priority="38" dxfId="13">
+    <cfRule type="expression" priority="37" dxfId="12">
+      <formula>#REF!="AOG"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="38" dxfId="11">
       <formula>#REF!="Critical"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="37" dxfId="11">
-      <formula>#REF!="AOG"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C156">
-    <cfRule type="expression" priority="4" dxfId="13">
+    <cfRule type="expression" priority="3" dxfId="12">
+      <formula>#REF!="AOG"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="11">
       <formula>#REF!="Critical"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="11">
-      <formula>#REF!="AOG"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D66">
-    <cfRule type="expression" priority="207" dxfId="11">
+    <cfRule type="expression" priority="207" dxfId="12">
       <formula>#REF!="AOG"</formula>
     </cfRule>
-    <cfRule type="expression" priority="208" dxfId="13">
+    <cfRule type="expression" priority="208" dxfId="11">
       <formula>#REF!="Critical"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113:D156">
-    <cfRule type="expression" priority="7" dxfId="11">
+    <cfRule type="expression" priority="7" dxfId="12">
       <formula>#REF!="AOG"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="13">
+    <cfRule type="expression" priority="8" dxfId="11">
       <formula>#REF!="Critical"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F157">
-    <cfRule type="expression" priority="209" dxfId="11">
+    <cfRule type="expression" priority="209" dxfId="12">
       <formula>#REF!="AOG"</formula>
     </cfRule>
-    <cfRule type="expression" priority="210" dxfId="13">
+    <cfRule type="expression" priority="210" dxfId="11">
       <formula>#REF!="Critical"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G100:G115">
-    <cfRule type="expression" priority="2" dxfId="13">
+    <cfRule type="expression" priority="1" dxfId="12">
+      <formula>#REF!="AOG"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="11">
       <formula>#REF!="Critical"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="1" dxfId="11">
-      <formula>#REF!="AOG"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E157:E657 H4:H157">
